--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C60EE73-7D9D-42A4-B403-8311D994D4EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7A839D-21A5-488F-9DBB-2D57F629408B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="46">
   <si>
     <t>S.No.</t>
   </si>
@@ -164,6 +164,15 @@
   </si>
   <si>
     <t>Send - DSE</t>
+  </si>
+  <si>
+    <t>607529-022-0022692</t>
+  </si>
+  <si>
+    <t>ASAD ULLAH GANAIE / 9596329586</t>
+  </si>
+  <si>
+    <t>607095-004-0322882</t>
   </si>
 </sst>
 </file>
@@ -265,6 +274,73 @@
   </cellStyles>
   <dxfs count="24">
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -284,73 +360,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -561,8 +570,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="I2:O8" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
-  <autoFilter ref="I2:O8" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="I2:O11" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
+  <autoFilter ref="I2:O11" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="21">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
@@ -586,26 +595,26 @@
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="0"/>
-    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date" dataDxfId="10"/>
-    <tableColumn id="8" xr3:uid="{F5CBE4CC-BED9-4546-922A-2AD753A3BA13}" name="Channel" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{F5CBE4CC-BED9-4546-922A-2AD753A3BA13}" name="Channel" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}" name="Table1" displayName="Table1" ref="A1:E31" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}" name="Table1" displayName="Table1" ref="A1:E31" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A1:E31" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{1D31F252-7F75-4ACE-8E4E-970F96D5D0FB}" name="S.No." dataDxfId="5">
+    <tableColumn id="1" xr3:uid="{1D31F252-7F75-4ACE-8E4E-970F96D5D0FB}" name="S.No." dataDxfId="4">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{5C2AFA5C-CFD5-43A7-83E2-31A9A1E8AA6E}" name="NAME" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{194B191E-FB6F-4E26-9A5A-32D004AC4649}" name="DESIGNATION" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{C758F67A-2E84-46C0-BF1E-17717F5D79AC}" name="CONTACT" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{6C0116B5-2941-4E11-AD47-2ECED03BE947}" name="LOCATION" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{5C2AFA5C-CFD5-43A7-83E2-31A9A1E8AA6E}" name="NAME" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{194B191E-FB6F-4E26-9A5A-32D004AC4649}" name="DESIGNATION" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{C758F67A-2E84-46C0-BF1E-17717F5D79AC}" name="CONTACT" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{6C0116B5-2941-4E11-AD47-2ECED03BE947}" name="LOCATION" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1217,6 +1226,28 @@
       <c r="D9" s="5"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
+      <c r="I9" s="4">
+        <f>ROW()-2</f>
+        <v>7</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M9" s="4">
+        <v>29</v>
+      </c>
+      <c r="N9" s="5">
+        <v>46018</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="10" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
@@ -1228,6 +1259,28 @@
       <c r="D10" s="5"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
+      <c r="I10" s="4">
+        <f>ROW()-2</f>
+        <v>8</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M10" s="4">
+        <v>1</v>
+      </c>
+      <c r="N10" s="5">
+        <v>46018</v>
+      </c>
+      <c r="O10" s="4" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="11" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
@@ -1239,6 +1292,16 @@
       <c r="D11" s="5"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
+      <c r="I11" s="4">
+        <f>ROW()-2</f>
+        <v>9</v>
+      </c>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
     </row>
     <row r="12" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="4">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7A839D-21A5-488F-9DBB-2D57F629408B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F73DFD3A-0882-4BBF-A39B-A0607721B33A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="49">
   <si>
     <t>S.No.</t>
   </si>
@@ -173,6 +173,15 @@
   </si>
   <si>
     <t>607095-004-0322882</t>
+  </si>
+  <si>
+    <t>607095-004-0323201</t>
+  </si>
+  <si>
+    <t>607095-004-0323300</t>
+  </si>
+  <si>
+    <t>Manzoor Sir</t>
   </si>
 </sst>
 </file>
@@ -572,6 +581,9 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="I2:O11" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
   <autoFilter ref="I2:O11" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="I3:O11">
+    <sortCondition ref="N2:N11"/>
+  </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="21">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
@@ -590,6 +602,9 @@
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:F16" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
   <autoFilter ref="A2:F16" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:F16">
+    <sortCondition ref="D2:D16"/>
+  </sortState>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="12">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
@@ -1002,15 +1017,15 @@
     </row>
     <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
-        <f t="shared" ref="A3:A16" si="0">ROW()-2</f>
+        <f>ROW()-2</f>
         <v>1</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4">
-        <v>75</v>
+        <v>245</v>
       </c>
       <c r="D3" s="5">
-        <v>46014</v>
+        <v>45983</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>30</v>
@@ -1023,52 +1038,54 @@
         <v>1</v>
       </c>
       <c r="J3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="6" t="s">
-        <v>24</v>
-      </c>
       <c r="L3" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M3" s="4">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="N3" s="5">
         <v>45985</v>
       </c>
-      <c r="O3" s="4"/>
+      <c r="O3" s="4" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="4" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
-        <f t="shared" si="0"/>
+        <f>ROW()-2</f>
         <v>2</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4">
-        <v>5</v>
+        <v>250</v>
       </c>
       <c r="D4" s="5">
-        <v>46012</v>
+        <v>45983</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I4" s="4">
-        <f t="shared" ref="I4:I8" si="1">ROW()-2</f>
+        <f>ROW()-2</f>
         <v>2</v>
       </c>
       <c r="J4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="6" t="s">
-        <v>27</v>
-      </c>
       <c r="L4" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M4" s="4">
         <v>100</v>
@@ -1080,90 +1097,102 @@
     </row>
     <row r="5" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
-        <f t="shared" si="0"/>
+        <f>ROW()-2</f>
         <v>3</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4">
-        <v>250</v>
+        <v>5</v>
       </c>
       <c r="D5" s="5">
-        <v>45983</v>
+        <v>46012</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I5" s="4">
-        <f t="shared" si="1"/>
+        <f>ROW()-2</f>
         <v>3</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M5" s="4">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="N5" s="5">
         <v>45985</v>
       </c>
-      <c r="O5" s="4" t="s">
-        <v>19</v>
-      </c>
+      <c r="O5" s="4"/>
     </row>
     <row r="6" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
-        <f t="shared" si="0"/>
+        <f>ROW()-2</f>
         <v>4</v>
       </c>
       <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="4"/>
+      <c r="C6" s="4">
+        <v>75</v>
+      </c>
+      <c r="D6" s="5">
+        <v>46014</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="I6" s="4">
-        <f t="shared" si="1"/>
+        <f>ROW()-2</f>
         <v>4</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="L6" s="4" t="s">
         <v>17</v>
       </c>
       <c r="M6" s="4">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="N6" s="5">
         <v>45985</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <f t="shared" si="0"/>
+        <f>ROW()-2</f>
         <v>5</v>
       </c>
       <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="4"/>
+      <c r="C7" s="4">
+        <v>75</v>
+      </c>
+      <c r="D7" s="5">
+        <v>46014</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="F7" s="4"/>
       <c r="I7" s="4">
-        <f t="shared" si="1"/>
+        <f>ROW()-2</f>
         <v>5</v>
       </c>
       <c r="J7" s="6" t="s">
@@ -1185,7 +1214,7 @@
     </row>
     <row r="8" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
-        <f t="shared" si="0"/>
+        <f>ROW()-2</f>
         <v>6</v>
       </c>
       <c r="B8" s="4"/>
@@ -1194,7 +1223,7 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="I8" s="4">
-        <f t="shared" si="1"/>
+        <f>ROW()-2</f>
         <v>6</v>
       </c>
       <c r="J8" s="6" t="s">
@@ -1218,7 +1247,7 @@
     </row>
     <row r="9" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
-        <f t="shared" si="0"/>
+        <f>ROW()-2</f>
         <v>7</v>
       </c>
       <c r="B9" s="4"/>
@@ -1231,16 +1260,16 @@
         <v>7</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="L9" s="4" t="s">
         <v>16</v>
       </c>
       <c r="M9" s="4">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="N9" s="5">
         <v>46018</v>
@@ -1251,7 +1280,7 @@
     </row>
     <row r="10" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
-        <f t="shared" si="0"/>
+        <f>ROW()-2</f>
         <v>8</v>
       </c>
       <c r="B10" s="4"/>
@@ -1264,16 +1293,16 @@
         <v>8</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="L10" s="4" t="s">
         <v>16</v>
       </c>
       <c r="M10" s="4">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="N10" s="5">
         <v>46018</v>
@@ -1284,7 +1313,7 @@
     </row>
     <row r="11" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
-        <f t="shared" si="0"/>
+        <f>ROW()-2</f>
         <v>9</v>
       </c>
       <c r="B11" s="4"/>
@@ -1296,16 +1325,26 @@
         <f>ROW()-2</f>
         <v>9</v>
       </c>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
+      <c r="J11" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M11" s="4">
+        <v>100</v>
+      </c>
       <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
+      <c r="O11" s="4" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="12" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
-        <f t="shared" si="0"/>
+        <f>ROW()-2</f>
         <v>10</v>
       </c>
       <c r="B12" s="4"/>
@@ -1316,7 +1355,7 @@
     </row>
     <row r="13" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
-        <f t="shared" si="0"/>
+        <f>ROW()-2</f>
         <v>11</v>
       </c>
       <c r="B13" s="4"/>
@@ -1327,7 +1366,7 @@
     </row>
     <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
-        <f t="shared" si="0"/>
+        <f>ROW()-2</f>
         <v>12</v>
       </c>
       <c r="B14" s="4"/>
@@ -1338,7 +1377,7 @@
     </row>
     <row r="15" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
-        <f t="shared" si="0"/>
+        <f>ROW()-2</f>
         <v>13</v>
       </c>
       <c r="B15" s="4"/>
@@ -1349,7 +1388,7 @@
     </row>
     <row r="16" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
-        <f t="shared" si="0"/>
+        <f>ROW()-2</f>
         <v>14</v>
       </c>
       <c r="B16" s="4"/>

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F73DFD3A-0882-4BBF-A39B-A0607721B33A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39376770-2BFC-4E80-B7A5-112C5788F51D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="51">
   <si>
     <t>S.No.</t>
   </si>
@@ -182,6 +182,12 @@
   </si>
   <si>
     <t>Manzoor Sir</t>
+  </si>
+  <si>
+    <t>78001-78250</t>
+  </si>
+  <si>
+    <t>767751-77000</t>
   </si>
 </sst>
 </file>
@@ -1017,7 +1023,7 @@
     </row>
     <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" ref="A3:A16" si="0">ROW()-2</f>
         <v>1</v>
       </c>
       <c r="B3" s="4"/>
@@ -1034,7 +1040,7 @@
         <v>41</v>
       </c>
       <c r="I3" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" ref="I3:I11" si="1">ROW()-2</f>
         <v>1</v>
       </c>
       <c r="J3" s="6" t="s">
@@ -1058,7 +1064,7 @@
     </row>
     <row r="4" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="B4" s="4"/>
@@ -1075,7 +1081,7 @@
         <v>41</v>
       </c>
       <c r="I4" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="J4" s="6" t="s">
@@ -1097,7 +1103,7 @@
     </row>
     <row r="5" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B5" s="4"/>
@@ -1114,7 +1120,7 @@
         <v>42</v>
       </c>
       <c r="I5" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="J5" s="6" t="s">
@@ -1136,7 +1142,7 @@
     </row>
     <row r="6" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B6" s="4"/>
@@ -1153,7 +1159,7 @@
         <v>41</v>
       </c>
       <c r="I6" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="J6" s="6" t="s">
@@ -1177,7 +1183,7 @@
     </row>
     <row r="7" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B7" s="4"/>
@@ -1192,7 +1198,7 @@
       </c>
       <c r="F7" s="4"/>
       <c r="I7" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="J7" s="6" t="s">
@@ -1214,16 +1220,20 @@
     </row>
     <row r="8" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
+      <c r="B8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="4">
+        <v>250</v>
+      </c>
       <c r="D8" s="5"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="I8" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="J8" s="6" t="s">
@@ -1247,16 +1257,20 @@
     </row>
     <row r="9" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
+      <c r="B9" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="4">
+        <v>250</v>
+      </c>
       <c r="D9" s="5"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="I9" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="J9" s="6" t="s">
@@ -1280,7 +1294,7 @@
     </row>
     <row r="10" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B10" s="4"/>
@@ -1289,7 +1303,7 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="I10" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="J10" s="6" t="s">
@@ -1313,7 +1327,7 @@
     </row>
     <row r="11" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B11" s="4"/>
@@ -1322,7 +1336,7 @@
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="I11" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="J11" s="6" t="s">
@@ -1344,7 +1358,7 @@
     </row>
     <row r="12" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B12" s="4"/>
@@ -1355,7 +1369,7 @@
     </row>
     <row r="13" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B13" s="4"/>
@@ -1366,7 +1380,7 @@
     </row>
     <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B14" s="4"/>
@@ -1377,7 +1391,7 @@
     </row>
     <row r="15" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B15" s="4"/>
@@ -1388,7 +1402,7 @@
     </row>
     <row r="16" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B16" s="4"/>

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39376770-2BFC-4E80-B7A5-112C5788F51D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{296D950D-D12F-48BE-A758-CB1C43570D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="58">
   <si>
     <t>S.No.</t>
   </si>
@@ -188,6 +188,27 @@
   </si>
   <si>
     <t>767751-77000</t>
+  </si>
+  <si>
+    <t>78150 - 78250</t>
+  </si>
+  <si>
+    <t>Send - Harjeet</t>
+  </si>
+  <si>
+    <t>607095-004-0418200</t>
+  </si>
+  <si>
+    <t>607095-004-0418100</t>
+  </si>
+  <si>
+    <t>Send - Harjeet / 9149756683</t>
+  </si>
+  <si>
+    <t>607095-004-0418400</t>
+  </si>
+  <si>
+    <t>607095-004-0418305</t>
   </si>
 </sst>
 </file>
@@ -585,8 +606,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="I2:O11" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
-  <autoFilter ref="I2:O11" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="I2:O16" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
+  <autoFilter ref="I2:O16" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="I3:O11">
     <sortCondition ref="N2:N11"/>
   </sortState>
@@ -1040,7 +1061,7 @@
         <v>41</v>
       </c>
       <c r="I3" s="4">
-        <f t="shared" ref="I3:I11" si="1">ROW()-2</f>
+        <f t="shared" ref="I3:I16" si="1">ROW()-2</f>
         <v>1</v>
       </c>
       <c r="J3" s="6" t="s">
@@ -1297,11 +1318,21 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
+      <c r="B10" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="4">
+        <v>100</v>
+      </c>
+      <c r="D10" s="5">
+        <v>46025</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>52</v>
+      </c>
       <c r="I10" s="4">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -1366,6 +1397,28 @@
       <c r="D12" s="5"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
+      <c r="I12" s="4">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M12" s="4">
+        <v>100</v>
+      </c>
+      <c r="N12" s="5">
+        <v>46025</v>
+      </c>
+      <c r="O12" s="4" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="13" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
@@ -1377,6 +1430,20 @@
       <c r="D13" s="5"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
+      <c r="I13" s="4">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
     </row>
     <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
@@ -1388,6 +1455,16 @@
       <c r="D14" s="5"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
+      <c r="I14" s="4">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
     </row>
     <row r="15" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
@@ -1399,6 +1476,16 @@
       <c r="D15" s="5"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
+      <c r="I15" s="4">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
     </row>
     <row r="16" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
@@ -1410,6 +1497,16 @@
       <c r="D16" s="5"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
+      <c r="I16" s="4">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{296D950D-D12F-48BE-A758-CB1C43570D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{332986DB-6078-40A6-A2FA-F2FCE2BECE9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="70">
   <si>
     <t>S.No.</t>
   </si>
@@ -208,7 +208,43 @@
     <t>607095-004-0418400</t>
   </si>
   <si>
-    <t>607095-004-0418305</t>
+    <t>607095-004-0418301</t>
+  </si>
+  <si>
+    <t>304 missing</t>
+  </si>
+  <si>
+    <t>607529-020-0114603</t>
+  </si>
+  <si>
+    <t>607529-020-0114652</t>
+  </si>
+  <si>
+    <t>607095-004-0418500</t>
+  </si>
+  <si>
+    <t>607095-004-0418401</t>
+  </si>
+  <si>
+    <t>15,16 , missing</t>
+  </si>
+  <si>
+    <t>607095-004-0418501</t>
+  </si>
+  <si>
+    <t>607095-004-0417282</t>
+  </si>
+  <si>
+    <t>607095-004-0417285</t>
+  </si>
+  <si>
+    <t>Order</t>
+  </si>
+  <si>
+    <t>Order 1</t>
+  </si>
+  <si>
+    <t>Order 2</t>
   </si>
 </sst>
 </file>
@@ -308,74 +344,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="25">
     <dxf>
       <font>
         <b val="0"/>
@@ -393,6 +362,93 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -606,57 +662,58 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="I2:O16" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
-  <autoFilter ref="I2:O16" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="I3:O11">
-    <sortCondition ref="N2:N11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="I2:P17" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23">
+  <autoFilter ref="I2:P17" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="I3:P11">
+    <sortCondition ref="O2:O11"/>
   </sortState>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="21">
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="22">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:F16" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:F16" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
   <autoFilter ref="A2:F16" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:F16">
     <sortCondition ref="D2:D16"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="12">
+    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="13">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{F5CBE4CC-BED9-4546-922A-2AD753A3BA13}" name="Channel" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{F5CBE4CC-BED9-4546-922A-2AD753A3BA13}" name="Channel" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}" name="Table1" displayName="Table1" ref="A1:E31" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}" name="Table1" displayName="Table1" ref="A1:E31" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
   <autoFilter ref="A1:E31" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{1D31F252-7F75-4ACE-8E4E-970F96D5D0FB}" name="S.No." dataDxfId="4">
+    <tableColumn id="1" xr3:uid="{1D31F252-7F75-4ACE-8E4E-970F96D5D0FB}" name="S.No." dataDxfId="5">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{5C2AFA5C-CFD5-43A7-83E2-31A9A1E8AA6E}" name="NAME" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{194B191E-FB6F-4E26-9A5A-32D004AC4649}" name="DESIGNATION" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{C758F67A-2E84-46C0-BF1E-17717F5D79AC}" name="CONTACT" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{6C0116B5-2941-4E11-AD47-2ECED03BE947}" name="LOCATION" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{5C2AFA5C-CFD5-43A7-83E2-31A9A1E8AA6E}" name="NAME" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{194B191E-FB6F-4E26-9A5A-32D004AC4649}" name="DESIGNATION" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{C758F67A-2E84-46C0-BF1E-17717F5D79AC}" name="CONTACT" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{6C0116B5-2941-4E11-AD47-2ECED03BE947}" name="LOCATION" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -959,7 +1016,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7916C5D2-EBF3-44BC-AD33-13F607DA9441}">
-  <dimension ref="A1:W16"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -969,20 +1027,20 @@
     <col min="6" max="6" width="21.42578125" customWidth="1"/>
     <col min="9" max="9" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="26.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="34" style="2" customWidth="1"/>
-    <col min="12" max="12" width="31" customWidth="1"/>
-    <col min="13" max="13" width="21.7109375" customWidth="1"/>
-    <col min="14" max="14" width="21.42578125" customWidth="1"/>
-    <col min="15" max="15" width="35.28515625" customWidth="1"/>
-    <col min="17" max="17" width="10.28515625" customWidth="1"/>
-    <col min="18" max="18" width="26.85546875" customWidth="1"/>
-    <col min="19" max="19" width="17.140625" customWidth="1"/>
-    <col min="20" max="20" width="25.140625" customWidth="1"/>
-    <col min="21" max="23" width="15.5703125" style="3" customWidth="1"/>
-    <col min="24" max="24" width="19.5703125" customWidth="1"/>
+    <col min="11" max="12" width="34" style="2" customWidth="1"/>
+    <col min="13" max="13" width="31" customWidth="1"/>
+    <col min="14" max="14" width="21.7109375" customWidth="1"/>
+    <col min="15" max="15" width="21.42578125" customWidth="1"/>
+    <col min="16" max="16" width="35.28515625" customWidth="1"/>
+    <col min="18" max="18" width="10.28515625" customWidth="1"/>
+    <col min="19" max="19" width="26.85546875" customWidth="1"/>
+    <col min="20" max="20" width="17.140625" customWidth="1"/>
+    <col min="21" max="21" width="25.140625" customWidth="1"/>
+    <col min="22" max="24" width="15.5703125" style="3" customWidth="1"/>
+    <col min="25" max="25" width="19.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="8" t="s">
         <v>37</v>
       </c>
@@ -1000,8 +1058,9 @@
       <c r="M1" s="7"/>
       <c r="N1" s="7"/>
       <c r="O1" s="7"/>
-    </row>
-    <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P1" s="7"/>
+    </row>
+    <row r="2" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -1029,20 +1088,23 @@
       <c r="K2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="M2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="O2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="P2" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <f t="shared" ref="A3:A16" si="0">ROW()-2</f>
         <v>1</v>
@@ -1061,7 +1123,7 @@
         <v>41</v>
       </c>
       <c r="I3" s="4">
-        <f t="shared" ref="I3:I16" si="1">ROW()-2</f>
+        <f t="shared" ref="I3:I17" si="1">ROW()-2</f>
         <v>1</v>
       </c>
       <c r="J3" s="6" t="s">
@@ -1070,20 +1132,23 @@
       <c r="K3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="M3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="M3" s="4">
+      <c r="N3" s="4">
         <v>20</v>
       </c>
-      <c r="N3" s="5">
+      <c r="O3" s="5">
         <v>45985</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="P3" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -1111,18 +1176,21 @@
       <c r="K4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="L4" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="M4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="M4" s="4">
+      <c r="N4" s="4">
         <v>100</v>
       </c>
-      <c r="N4" s="5">
+      <c r="O4" s="5">
         <v>45985</v>
       </c>
-      <c r="O4" s="4"/>
-    </row>
-    <row r="5" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P4" s="4"/>
+    </row>
+    <row r="5" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1150,18 +1218,21 @@
       <c r="K5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="M5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="M5" s="4">
+      <c r="N5" s="4">
         <v>100</v>
       </c>
-      <c r="N5" s="5">
+      <c r="O5" s="5">
         <v>45985</v>
       </c>
-      <c r="O5" s="4"/>
-    </row>
-    <row r="6" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P5" s="4"/>
+    </row>
+    <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1189,20 +1260,23 @@
       <c r="K6" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="L6" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="M6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="M6" s="4">
+      <c r="N6" s="4">
         <v>30</v>
       </c>
-      <c r="N6" s="5">
+      <c r="O6" s="5">
         <v>45985</v>
       </c>
-      <c r="O6" s="4" t="s">
+      <c r="P6" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1228,18 +1302,21 @@
       <c r="K7" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="L7" s="4" t="s">
+      <c r="L7" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="M7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="M7" s="4">
+      <c r="N7" s="4">
         <v>100</v>
       </c>
-      <c r="N7" s="5">
+      <c r="O7" s="5">
         <v>45986</v>
       </c>
-      <c r="O7" s="4"/>
-    </row>
-    <row r="8" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P7" s="4"/>
+    </row>
+    <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1263,20 +1340,23 @@
       <c r="K8" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="L8" s="4" t="s">
+      <c r="L8" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="M8" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="M8" s="4">
+      <c r="N8" s="4">
         <v>10</v>
       </c>
-      <c r="N8" s="5">
+      <c r="O8" s="5">
         <v>46013</v>
       </c>
-      <c r="O8" s="4" t="s">
+      <c r="P8" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1300,20 +1380,23 @@
       <c r="K9" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="4" t="s">
+      <c r="L9" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="M9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="M9" s="4">
+      <c r="N9" s="4">
         <v>1</v>
       </c>
-      <c r="N9" s="5">
+      <c r="O9" s="5">
         <v>46018</v>
       </c>
-      <c r="O9" s="4" t="s">
+      <c r="P9" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1343,20 +1426,23 @@
       <c r="K10" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="L10" s="4" t="s">
+      <c r="L10" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="M10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="M10" s="4">
+      <c r="N10" s="4">
         <v>29</v>
       </c>
-      <c r="N10" s="5">
+      <c r="O10" s="5">
         <v>46018</v>
       </c>
-      <c r="O10" s="4" t="s">
+      <c r="P10" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1377,17 +1463,20 @@
         <v>47</v>
       </c>
       <c r="L11" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="M11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="M11" s="4">
+      <c r="N11" s="4">
         <v>100</v>
       </c>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4" t="s">
+      <c r="O11" s="4"/>
+      <c r="P11" s="4" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1408,19 +1497,22 @@
         <v>53</v>
       </c>
       <c r="L12" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="M12" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="M12" s="4">
+      <c r="N12" s="4">
         <v>100</v>
       </c>
-      <c r="N12" s="5">
+      <c r="O12" s="5">
         <v>46025</v>
       </c>
-      <c r="O12" s="4" t="s">
+      <c r="P12" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1440,12 +1532,23 @@
       <c r="K13" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-    </row>
-    <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="L13" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="N13" s="4">
+        <v>99</v>
+      </c>
+      <c r="O13" s="5">
+        <v>46026</v>
+      </c>
+      <c r="P13" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1459,14 +1562,23 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="4"/>
+      <c r="J14" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>69</v>
+      </c>
       <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
+      <c r="N14" s="4">
+        <v>50</v>
+      </c>
       <c r="O14" s="4"/>
-    </row>
-    <row r="15" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P14" s="4"/>
+    </row>
+    <row r="15" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1480,14 +1592,25 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="4"/>
+      <c r="J15" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>69</v>
+      </c>
       <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
+      <c r="N15" s="4">
+        <v>98</v>
+      </c>
       <c r="O15" s="4"/>
-    </row>
-    <row r="16" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P15" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1501,16 +1624,46 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="4"/>
+      <c r="J16" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>69</v>
+      </c>
       <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
+      <c r="N16" s="4">
+        <v>50</v>
+      </c>
       <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+    </row>
+    <row r="17" spans="9:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I17" s="4">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4">
+        <v>4</v>
+      </c>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="I1:P1"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -1525,6 +1678,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4093ECB5-009B-4A95-948D-B5418A73B4F4}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{332986DB-6078-40A6-A2FA-F2FCE2BECE9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2B2D7F8-4588-4575-9B58-1C456801C890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="72">
   <si>
     <t>S.No.</t>
   </si>
@@ -245,6 +245,12 @@
   </si>
   <si>
     <t>Order 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anantnag </t>
+  </si>
+  <si>
+    <t>2 TAGS</t>
   </si>
 </sst>
 </file>
@@ -346,6 +352,212 @@
   </cellStyles>
   <dxfs count="25">
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -363,212 +575,6 @@
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -673,47 +679,47 @@
     </tableColumn>
     <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="21"/>
     <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="0"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="17"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:F16" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:F16" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
   <autoFilter ref="A2:F16" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:F16">
     <sortCondition ref="D2:D16"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="13">
+    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="12">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date" dataDxfId="10"/>
-    <tableColumn id="8" xr3:uid="{F5CBE4CC-BED9-4546-922A-2AD753A3BA13}" name="Channel" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{F5CBE4CC-BED9-4546-922A-2AD753A3BA13}" name="Channel" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}" name="Table1" displayName="Table1" ref="A1:E31" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}" name="Table1" displayName="Table1" ref="A1:E31" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A1:E31" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{1D31F252-7F75-4ACE-8E4E-970F96D5D0FB}" name="S.No." dataDxfId="5">
+    <tableColumn id="1" xr3:uid="{1D31F252-7F75-4ACE-8E4E-970F96D5D0FB}" name="S.No." dataDxfId="4">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{5C2AFA5C-CFD5-43A7-83E2-31A9A1E8AA6E}" name="NAME" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{194B191E-FB6F-4E26-9A5A-32D004AC4649}" name="DESIGNATION" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{C758F67A-2E84-46C0-BF1E-17717F5D79AC}" name="CONTACT" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{6C0116B5-2941-4E11-AD47-2ECED03BE947}" name="LOCATION" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{5C2AFA5C-CFD5-43A7-83E2-31A9A1E8AA6E}" name="NAME" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{194B191E-FB6F-4E26-9A5A-32D004AC4649}" name="DESIGNATION" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{C758F67A-2E84-46C0-BF1E-17717F5D79AC}" name="CONTACT" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{6C0116B5-2941-4E11-AD47-2ECED03BE947}" name="LOCATION" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1601,11 +1607,15 @@
       <c r="L15" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="M15" s="4"/>
+      <c r="M15" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="N15" s="4">
         <v>98</v>
       </c>
-      <c r="O15" s="4"/>
+      <c r="O15" s="5">
+        <v>46032</v>
+      </c>
       <c r="P15" s="4" t="s">
         <v>63</v>
       </c>
@@ -1654,12 +1664,18 @@
       <c r="L17" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="M17" s="4"/>
+      <c r="M17" s="4" t="s">
+        <v>70</v>
+      </c>
       <c r="N17" s="4">
         <v>4</v>
       </c>
-      <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
+      <c r="O17" s="5">
+        <v>46032</v>
+      </c>
+      <c r="P17" s="4" t="s">
+        <v>71</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2B2D7F8-4588-4575-9B58-1C456801C890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50094662-423D-457A-A18A-373CADE09E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="75">
   <si>
     <t>S.No.</t>
   </si>
@@ -184,15 +184,9 @@
     <t>Manzoor Sir</t>
   </si>
   <si>
-    <t>78001-78250</t>
-  </si>
-  <si>
     <t>767751-77000</t>
   </si>
   <si>
-    <t>78150 - 78250</t>
-  </si>
-  <si>
     <t>Send - Harjeet</t>
   </si>
   <si>
@@ -251,6 +245,21 @@
   </si>
   <si>
     <t>2 TAGS</t>
+  </si>
+  <si>
+    <t>nexa</t>
+  </si>
+  <si>
+    <t>NEXA</t>
+  </si>
+  <si>
+    <t>78001-78150</t>
+  </si>
+  <si>
+    <t>Yawar</t>
+  </si>
+  <si>
+    <t>78151 - 78250</t>
   </si>
 </sst>
 </file>
@@ -1095,7 +1104,7 @@
         <v>10</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M2" s="4" t="s">
         <v>11</v>
@@ -1123,7 +1132,7 @@
         <v>45983</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>41</v>
@@ -1139,7 +1148,7 @@
         <v>23</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="M3" s="4" t="s">
         <v>17</v>
@@ -1183,7 +1192,7 @@
         <v>24</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>13</v>
@@ -1225,7 +1234,7 @@
         <v>27</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="M5" s="4" t="s">
         <v>16</v>
@@ -1267,7 +1276,7 @@
         <v>29</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="M6" s="4" t="s">
         <v>17</v>
@@ -1309,7 +1318,7 @@
         <v>28</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="M7" s="4" t="s">
         <v>17</v>
@@ -1328,14 +1337,20 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="C8" s="4">
-        <v>250</v>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
+        <v>150</v>
+      </c>
+      <c r="D8" s="5">
+        <v>46025</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>73</v>
+      </c>
       <c r="I8" s="4">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -1347,7 +1362,7 @@
         <v>36</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="M8" s="4" t="s">
         <v>32</v>
@@ -1368,13 +1383,17 @@
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C9" s="4">
         <v>250</v>
       </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="4"/>
+      <c r="D9" s="5">
+        <v>46027</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="F9" s="4"/>
       <c r="I9" s="4">
         <f t="shared" si="1"/>
@@ -1387,7 +1406,7 @@
         <v>45</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="M9" s="4" t="s">
         <v>16</v>
@@ -1408,7 +1427,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="C10" s="4">
         <v>100</v>
@@ -1420,7 +1439,7 @@
         <v>16</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I10" s="4">
         <f t="shared" si="1"/>
@@ -1433,7 +1452,7 @@
         <v>29</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="M10" s="4" t="s">
         <v>16</v>
@@ -1469,7 +1488,7 @@
         <v>47</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="M11" s="6" t="s">
         <v>16</v>
@@ -1497,13 +1516,13 @@
         <v>10</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>16</v>
@@ -1515,7 +1534,7 @@
         <v>46025</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -1533,13 +1552,13 @@
         <v>11</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M13" s="4" t="s">
         <v>17</v>
@@ -1551,7 +1570,7 @@
         <v>46026</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -1569,13 +1588,13 @@
         <v>12</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M14" s="4"/>
       <c r="N14" s="4">
@@ -1599,13 +1618,13 @@
         <v>13</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M15" s="4" t="s">
         <v>16</v>
@@ -1617,7 +1636,7 @@
         <v>46032</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -1635,13 +1654,13 @@
         <v>14</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M16" s="4"/>
       <c r="N16" s="4">
@@ -1656,16 +1675,16 @@
         <v>15</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N17" s="4">
         <v>4</v>
@@ -1674,7 +1693,7 @@
         <v>46032</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50094662-423D-457A-A18A-373CADE09E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3368284-4DC0-4C0A-B8D5-235275398B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="75">
   <si>
     <t>S.No.</t>
   </si>
@@ -1386,7 +1386,7 @@
         <v>49</v>
       </c>
       <c r="C9" s="4">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="D9" s="5">
         <v>46027</v>
@@ -1473,9 +1473,15 @@
         <v>9</v>
       </c>
       <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="4"/>
+      <c r="C11" s="4">
+        <v>40</v>
+      </c>
+      <c r="D11" s="5">
+        <v>46034</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="F11" s="4"/>
       <c r="I11" s="4">
         <f t="shared" si="1"/>
@@ -1507,9 +1513,15 @@
         <v>10</v>
       </c>
       <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="4"/>
+      <c r="C12" s="4">
+        <v>60</v>
+      </c>
+      <c r="D12" s="5">
+        <v>46037</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="F12" s="4"/>
       <c r="I12" s="4">
         <f t="shared" si="1"/>

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3368284-4DC0-4C0A-B8D5-235275398B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CBAF4ED-F1F2-4D7E-9833-A2952AB7464B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
-    <sheet name="RC-FASTags" sheetId="2" r:id="rId1"/>
-    <sheet name="Contacts" sheetId="1" r:id="rId2"/>
+    <sheet name="RC" sheetId="2" r:id="rId1"/>
+    <sheet name="FASTTAGS" sheetId="4" r:id="rId2"/>
+    <sheet name="Contacts" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="77">
   <si>
     <t>S.No.</t>
   </si>
@@ -260,13 +261,19 @@
   </si>
   <si>
     <t>78151 - 78250</t>
+  </si>
+  <si>
+    <t>RTO Rc Rec</t>
+  </si>
+  <si>
+    <t>Date2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -303,6 +310,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -330,7 +345,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -355,157 +370,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="27">
     <dxf>
       <font>
         <strike val="0"/>
@@ -663,6 +535,194 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -677,58 +737,58 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="I2:P17" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23">
-  <autoFilter ref="I2:P17" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="I3:P11">
-    <sortCondition ref="O2:O11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:H16" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:H16">
+    <sortCondition ref="G2:G16"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="22">
+    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="24">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="15"/>
+    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="22"/>
+    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:F16" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
-  <autoFilter ref="A2:F16" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:F16">
-    <sortCondition ref="D2:D16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H17" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:H11">
+    <sortCondition ref="G2:G11"/>
   </sortState>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="12">
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="7">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{F5CBE4CC-BED9-4546-922A-2AD753A3BA13}" name="Channel" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}" name="Table1" displayName="Table1" ref="A1:E31" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}" name="Table1" displayName="Table1" ref="A1:E31" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <autoFilter ref="A1:E31" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{1D31F252-7F75-4ACE-8E4E-970F96D5D0FB}" name="S.No." dataDxfId="4">
+    <tableColumn id="1" xr3:uid="{1D31F252-7F75-4ACE-8E4E-970F96D5D0FB}" name="S.No." dataDxfId="17">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{5C2AFA5C-CFD5-43A7-83E2-31A9A1E8AA6E}" name="NAME" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{194B191E-FB6F-4E26-9A5A-32D004AC4649}" name="DESIGNATION" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{C758F67A-2E84-46C0-BF1E-17717F5D79AC}" name="CONTACT" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{6C0116B5-2941-4E11-AD47-2ECED03BE947}" name="LOCATION" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{5C2AFA5C-CFD5-43A7-83E2-31A9A1E8AA6E}" name="NAME" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{194B191E-FB6F-4E26-9A5A-32D004AC4649}" name="DESIGNATION" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{C758F67A-2E84-46C0-BF1E-17717F5D79AC}" name="CONTACT" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{6C0116B5-2941-4E11-AD47-2ECED03BE947}" name="LOCATION" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1032,698 +1092,815 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7916C5D2-EBF3-44BC-AD33-13F607DA9441}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:X17"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="34.42578125" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="21.42578125" customWidth="1"/>
-    <col min="9" max="9" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="26.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="34" style="2" customWidth="1"/>
-    <col min="13" max="13" width="31" customWidth="1"/>
-    <col min="14" max="14" width="21.7109375" customWidth="1"/>
-    <col min="15" max="15" width="21.42578125" customWidth="1"/>
-    <col min="16" max="16" width="35.28515625" customWidth="1"/>
-    <col min="18" max="18" width="10.28515625" customWidth="1"/>
-    <col min="19" max="19" width="26.85546875" customWidth="1"/>
-    <col min="20" max="20" width="17.140625" customWidth="1"/>
-    <col min="21" max="21" width="25.140625" customWidth="1"/>
-    <col min="22" max="24" width="15.5703125" style="3" customWidth="1"/>
-    <col min="25" max="25" width="19.5703125" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="4" max="4" width="34.42578125" customWidth="1"/>
+    <col min="5" max="6" width="32.5703125" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" customWidth="1"/>
+    <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="34" style="2" customWidth="1"/>
+    <col min="15" max="15" width="31" customWidth="1"/>
+    <col min="16" max="16" width="21.7109375" customWidth="1"/>
+    <col min="17" max="17" width="21.42578125" customWidth="1"/>
+    <col min="18" max="18" width="35.28515625" customWidth="1"/>
+    <col min="20" max="20" width="10.28515625" customWidth="1"/>
+    <col min="21" max="21" width="26.85546875" customWidth="1"/>
+    <col min="22" max="22" width="17.140625" customWidth="1"/>
+    <col min="23" max="23" width="25.140625" customWidth="1"/>
+    <col min="24" max="26" width="15.5703125" style="3" customWidth="1"/>
+    <col min="27" max="27" width="19.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:8" ht="33.75" x14ac:dyDescent="0.5">
       <c r="A1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
       <c r="F1" s="9"/>
-      <c r="I1" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-    </row>
-    <row r="2" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J2" s="6" t="s">
+    </row>
+    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <f>ROW()-2</f>
+        <v>1</v>
+      </c>
+      <c r="B3" s="4">
+        <v>750</v>
+      </c>
+      <c r="C3" s="5">
+        <v>46039</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4">
+        <v>250</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="5">
+        <v>45983</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <f>ROW()-2</f>
+        <v>2</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4">
+        <v>245</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" s="5">
+        <v>45983</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <f>ROW()-2</f>
+        <v>3</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4">
+        <v>5</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="5">
+        <v>46012</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <f>ROW()-2</f>
+        <v>4</v>
+      </c>
+      <c r="B6" s="4">
+        <v>250</v>
+      </c>
+      <c r="C6" s="5">
+        <v>45983</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4">
+        <v>75</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="5">
+        <v>46014</v>
+      </c>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <f>ROW()-2</f>
+        <v>5</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4">
+        <v>75</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="5">
+        <v>46014</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <f>ROW()-2</f>
+        <v>6</v>
+      </c>
+      <c r="B8" s="4">
+        <v>250</v>
+      </c>
+      <c r="C8" s="5">
+        <v>45983</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" s="4">
+        <v>100</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="5">
+        <v>46025</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <f>ROW()-2</f>
+        <v>7</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="4">
+        <v>150</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="5">
+        <v>46025</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <f>ROW()-2</f>
+        <v>8</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="4">
+        <v>150</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" s="5">
+        <v>46027</v>
+      </c>
+      <c r="H10" s="4"/>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <f>ROW()-2</f>
         <v>9</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="B11" s="4">
+        <v>250</v>
+      </c>
+      <c r="C11" s="5">
+        <v>46014</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4">
+        <v>40</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="5">
+        <v>46034</v>
+      </c>
+      <c r="H11" s="4"/>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <f>ROW()-2</f>
         <v>10</v>
       </c>
-      <c r="L2" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <f t="shared" ref="A3:A16" si="0">ROW()-2</f>
-        <v>1</v>
-      </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4">
-        <v>245</v>
-      </c>
-      <c r="D3" s="5">
-        <v>45983</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="I3" s="4">
-        <f t="shared" ref="I3:I17" si="1">ROW()-2</f>
-        <v>1</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="N3" s="4">
-        <v>20</v>
-      </c>
-      <c r="O3" s="5">
-        <v>45985</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4">
-        <v>250</v>
-      </c>
-      <c r="D4" s="5">
-        <v>45983</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="I4" s="4">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="N4" s="4">
-        <v>100</v>
-      </c>
-      <c r="O4" s="5">
-        <v>45985</v>
-      </c>
-      <c r="P4" s="4"/>
-    </row>
-    <row r="5" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4">
-        <v>5</v>
-      </c>
-      <c r="D5" s="5">
-        <v>46012</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5" s="4">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="M5" s="4" t="s">
+      <c r="B12" s="4">
+        <v>500</v>
+      </c>
+      <c r="C12" s="5">
+        <v>46025</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4">
+        <v>60</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="N5" s="4">
-        <v>100</v>
-      </c>
-      <c r="O5" s="5">
-        <v>45985</v>
-      </c>
-      <c r="P5" s="4"/>
-    </row>
-    <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4">
-        <v>75</v>
-      </c>
-      <c r="D6" s="5">
-        <v>46014</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="I6" s="4">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="N6" s="4">
-        <v>30</v>
-      </c>
-      <c r="O6" s="5">
-        <v>45985</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4">
-        <v>75</v>
-      </c>
-      <c r="D7" s="5">
-        <v>46014</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="4"/>
-      <c r="I7" s="4">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="L7" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="N7" s="4">
-        <v>100</v>
-      </c>
-      <c r="O7" s="5">
-        <v>45986</v>
-      </c>
-      <c r="P7" s="4"/>
-    </row>
-    <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" s="4">
-        <v>150</v>
-      </c>
-      <c r="D8" s="5">
-        <v>46025</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="I8" s="4">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N8" s="4">
-        <v>10</v>
-      </c>
-      <c r="O8" s="5">
-        <v>46013</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="4">
-        <v>150</v>
-      </c>
-      <c r="D9" s="5">
-        <v>46027</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F9" s="4"/>
-      <c r="I9" s="4">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="N9" s="4">
-        <v>1</v>
-      </c>
-      <c r="O9" s="5">
-        <v>46018</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" s="4">
-        <v>100</v>
-      </c>
-      <c r="D10" s="5">
-        <v>46025</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I10" s="4">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="L10" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="N10" s="4">
-        <v>29</v>
-      </c>
-      <c r="O10" s="5">
-        <v>46018</v>
-      </c>
-      <c r="P10" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4">
-        <v>40</v>
-      </c>
-      <c r="D11" s="5">
-        <v>46034</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" s="4"/>
-      <c r="I11" s="4">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="K11" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="M11" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="N11" s="4">
-        <v>100</v>
-      </c>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4">
-        <v>60</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="G12" s="5">
         <v>46037</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" s="4"/>
-      <c r="I12" s="4">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="M12" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="N12" s="4">
-        <v>100</v>
-      </c>
-      <c r="O12" s="5">
-        <v>46025</v>
-      </c>
-      <c r="P12" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
-        <f t="shared" si="0"/>
+        <f>ROW()-2</f>
         <v>11</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="5"/>
+      <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
-      <c r="I13" s="4">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="N13" s="4">
-        <v>99</v>
-      </c>
-      <c r="O13" s="5">
-        <v>46026</v>
-      </c>
-      <c r="P13" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G13" s="5"/>
+      <c r="H13" s="4"/>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
-        <f t="shared" si="0"/>
+        <f>ROW()-2</f>
         <v>12</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="5"/>
+      <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
-      <c r="I14" s="4">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4">
-        <v>50</v>
-      </c>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
-    </row>
-    <row r="15" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G14" s="5"/>
+      <c r="H14" s="4"/>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
-        <f t="shared" si="0"/>
+        <f>ROW()-2</f>
         <v>13</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="5"/>
+      <c r="D15" s="4"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
-      <c r="I15" s="4">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="K15" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="L15" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="M15" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="N15" s="4">
-        <v>98</v>
-      </c>
-      <c r="O15" s="5">
-        <v>46032</v>
-      </c>
-      <c r="P15" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="5"/>
+      <c r="H15" s="4"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
-        <f t="shared" si="0"/>
+        <f>ROW()-2</f>
         <v>14</v>
       </c>
-      <c r="B16" s="4"/>
+      <c r="B16" s="10">
+        <f>SUM(B3:B15)</f>
+        <v>2000</v>
+      </c>
       <c r="C16" s="4"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="10">
+        <f>SUM(E3:E15)</f>
+        <v>1150</v>
+      </c>
       <c r="F16" s="4"/>
-      <c r="I16" s="4">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="K16" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="L16" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="M16" s="4"/>
-      <c r="N16" s="4">
-        <v>50</v>
-      </c>
-      <c r="O16" s="4"/>
-      <c r="P16" s="4"/>
-    </row>
-    <row r="17" spans="9:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="I17" s="4">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="K17" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="L17" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="M17" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="N17" s="4">
-        <v>4</v>
-      </c>
-      <c r="O17" s="5">
-        <v>46032</v>
-      </c>
-      <c r="P17" s="4" t="s">
-        <v>69</v>
-      </c>
+      <c r="G16" s="5"/>
+      <c r="H16" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="I1:P1"/>
-    <mergeCell ref="A1:F1"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-  <tableParts count="2">
+  <tableParts count="1">
     <tablePart r:id="rId2"/>
-    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56B532C1-7F8B-4592-901A-51A1E632DC96}">
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr defaultColWidth="37.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.140625" customWidth="1"/>
+    <col min="6" max="6" width="17.5703125" customWidth="1"/>
+    <col min="7" max="7" width="26.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <f>ROW()-2</f>
+        <v>1</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="4">
+        <v>20</v>
+      </c>
+      <c r="G3" s="5">
+        <v>45985</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <f>ROW()-2</f>
+        <v>2</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="4">
+        <v>100</v>
+      </c>
+      <c r="G4" s="5">
+        <v>45985</v>
+      </c>
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <f>ROW()-2</f>
+        <v>3</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="4">
+        <v>100</v>
+      </c>
+      <c r="G5" s="5">
+        <v>45985</v>
+      </c>
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <f>ROW()-2</f>
+        <v>4</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="4">
+        <v>30</v>
+      </c>
+      <c r="G6" s="5">
+        <v>45985</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <f>ROW()-2</f>
+        <v>5</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="4">
+        <v>100</v>
+      </c>
+      <c r="G7" s="5">
+        <v>45986</v>
+      </c>
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <f>ROW()-2</f>
+        <v>6</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="4">
+        <v>10</v>
+      </c>
+      <c r="G8" s="5">
+        <v>46013</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <f>ROW()-2</f>
+        <v>7</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="4">
+        <v>1</v>
+      </c>
+      <c r="G9" s="5">
+        <v>46018</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <f>ROW()-2</f>
+        <v>8</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="4">
+        <v>29</v>
+      </c>
+      <c r="G10" s="5">
+        <v>46018</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <f>ROW()-2</f>
+        <v>9</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="4">
+        <v>100</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <f>ROW()-2</f>
+        <v>10</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="4">
+        <v>100</v>
+      </c>
+      <c r="G12" s="5">
+        <v>46025</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <f>ROW()-2</f>
+        <v>11</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="4">
+        <v>99</v>
+      </c>
+      <c r="G13" s="5">
+        <v>46026</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <f>ROW()-2</f>
+        <v>12</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4">
+        <v>50</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <f>ROW()-2</f>
+        <v>13</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="4">
+        <v>98</v>
+      </c>
+      <c r="G15" s="5">
+        <v>46032</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <f>ROW()-2</f>
+        <v>14</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4">
+        <v>50</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <f>ROW()-2</f>
+        <v>15</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F17" s="4">
+        <v>4</v>
+      </c>
+      <c r="G17" s="5">
+        <v>46032</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4093ECB5-009B-4A95-948D-B5418A73B4F4}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:E31"/>

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CBAF4ED-F1F2-4D7E-9833-A2952AB7464B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39E709CC-E0E1-4207-87BD-09DE611FAE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
     <sheet name="RC" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="82">
   <si>
     <t>S.No.</t>
   </si>
@@ -267,6 +267,21 @@
   </si>
   <si>
     <t>Date2</t>
+  </si>
+  <si>
+    <t>Asif Afzal</t>
+  </si>
+  <si>
+    <t>145751-146000</t>
+  </si>
+  <si>
+    <t>YAWAR</t>
+  </si>
+  <si>
+    <t>607529-020-0114627</t>
+  </si>
+  <si>
+    <t>607529-020-0114628</t>
   </si>
 </sst>
 </file>
@@ -361,8 +376,8 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -370,14 +385,35 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="27">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -537,11 +573,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -552,6 +584,22 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -593,27 +641,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -626,22 +653,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -665,7 +676,11 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -738,6 +753,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:H16" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
+  <autoFilter ref="A2:H16" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:H16">
     <sortCondition ref="G2:G16"/>
   </sortState>
@@ -745,50 +761,50 @@
     <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="24">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="22"/>
-    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="20"/>
+    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="23"/>
+    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="20"/>
+    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H17" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H19" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:H11">
     <sortCondition ref="G2:G11"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="7">
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="14">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}" name="Table1" displayName="Table1" ref="A1:E31" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}" name="Table1" displayName="Table1" ref="A1:E31" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A1:E31" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{1D31F252-7F75-4ACE-8E4E-970F96D5D0FB}" name="S.No." dataDxfId="17">
+    <tableColumn id="1" xr3:uid="{1D31F252-7F75-4ACE-8E4E-970F96D5D0FB}" name="S.No." dataDxfId="4">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{5C2AFA5C-CFD5-43A7-83E2-31A9A1E8AA6E}" name="NAME" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{194B191E-FB6F-4E26-9A5A-32D004AC4649}" name="DESIGNATION" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{C758F67A-2E84-46C0-BF1E-17717F5D79AC}" name="CONTACT" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{6C0116B5-2941-4E11-AD47-2ECED03BE947}" name="LOCATION" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{5C2AFA5C-CFD5-43A7-83E2-31A9A1E8AA6E}" name="NAME" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{194B191E-FB6F-4E26-9A5A-32D004AC4649}" name="DESIGNATION" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{C758F67A-2E84-46C0-BF1E-17717F5D79AC}" name="CONTACT" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{6C0116B5-2941-4E11-AD47-2ECED03BE947}" name="LOCATION" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1157,7 +1173,7 @@
     </row>
     <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" ref="A3:A16" si="0">ROW()-2</f>
         <v>1</v>
       </c>
       <c r="B3" s="4">
@@ -1182,7 +1198,7 @@
     </row>
     <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="B4" s="4"/>
@@ -1203,7 +1219,7 @@
     </row>
     <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B5" s="4"/>
@@ -1224,7 +1240,7 @@
     </row>
     <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B6" s="4">
@@ -1247,7 +1263,7 @@
     </row>
     <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B7" s="4"/>
@@ -1268,7 +1284,7 @@
     </row>
     <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B8" s="4">
@@ -1295,7 +1311,7 @@
     </row>
     <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B9" s="4"/>
@@ -1318,7 +1334,7 @@
     </row>
     <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B10" s="4"/>
@@ -1339,7 +1355,7 @@
     </row>
     <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B11" s="4">
@@ -1362,7 +1378,7 @@
     </row>
     <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B12" s="4">
@@ -1385,20 +1401,30 @@
     </row>
     <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="4"/>
+      <c r="D13" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E13" s="4">
+        <v>250</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="5">
+        <v>46042</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B14" s="4"/>
@@ -1411,7 +1437,7 @@
     </row>
     <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B15" s="4"/>
@@ -1424,18 +1450,18 @@
     </row>
     <row r="16" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="7">
         <f>SUM(B3:B15)</f>
         <v>2000</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
-      <c r="E16" s="10">
+      <c r="E16" s="7">
         <f>SUM(E3:E15)</f>
-        <v>1150</v>
+        <v>1400</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="5"/>
@@ -1456,7 +1482,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56B532C1-7F8B-4592-901A-51A1E632DC96}">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultColWidth="37.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -1467,16 +1493,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -1506,7 +1532,7 @@
     </row>
     <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" ref="A3:A19" si="0">ROW()-2</f>
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
@@ -1533,7 +1559,7 @@
     </row>
     <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -1558,7 +1584,7 @@
     </row>
     <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
@@ -1583,7 +1609,7 @@
     </row>
     <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B6" s="6" t="s">
@@ -1610,7 +1636,7 @@
     </row>
     <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B7" s="6" t="s">
@@ -1635,7 +1661,7 @@
     </row>
     <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B8" s="6" t="s">
@@ -1662,7 +1688,7 @@
     </row>
     <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B9" s="6" t="s">
@@ -1689,7 +1715,7 @@
     </row>
     <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -1716,7 +1742,7 @@
     </row>
     <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -1741,7 +1767,7 @@
     </row>
     <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B12" s="6" t="s">
@@ -1768,7 +1794,7 @@
     </row>
     <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B13" s="6" t="s">
@@ -1795,28 +1821,34 @@
     </row>
     <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>57</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="4"/>
+      <c r="E14" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F14" s="4">
-        <v>50</v>
-      </c>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
+        <v>25</v>
+      </c>
+      <c r="G14" s="5">
+        <v>46042</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B15" s="6" t="s">
@@ -1843,7 +1875,7 @@
     </row>
     <row r="16" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B16" s="6" t="s">
@@ -1855,16 +1887,22 @@
       <c r="D16" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E16" s="4"/>
+      <c r="E16" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F16" s="4">
         <v>50</v>
       </c>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
+      <c r="G16" s="5">
+        <v>46042</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B17" s="6" t="s">
@@ -1888,6 +1926,36 @@
       <c r="H17" s="4" t="s">
         <v>69</v>
       </c>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="6"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39E709CC-E0E1-4207-87BD-09DE611FAE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45672D10-F312-4F86-A41C-E5B7202C36FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="84">
   <si>
     <t>S.No.</t>
   </si>
@@ -282,6 +282,12 @@
   </si>
   <si>
     <t>607529-020-0114628</t>
+  </si>
+  <si>
+    <t>607095-004-0418201</t>
+  </si>
+  <si>
+    <t>607095-004-0418300</t>
   </si>
 </sst>
 </file>
@@ -774,10 +780,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H19" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:H11">
-    <sortCondition ref="G2:G11"/>
-  </sortState>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H20" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A2:H20" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="14">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
@@ -1482,7 +1486,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56B532C1-7F8B-4592-901A-51A1E632DC96}">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="37.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -1532,7 +1536,7 @@
     </row>
     <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
-        <f t="shared" ref="A3:A19" si="0">ROW()-2</f>
+        <f t="shared" ref="A3:A20" si="0">ROW()-2</f>
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
@@ -1794,29 +1798,29 @@
     </row>
     <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
-        <f t="shared" si="0"/>
+        <f>ROW()-2</f>
         <v>11</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>17</v>
+      <c r="E13" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="F13" s="4">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G13" s="5">
-        <v>46026</v>
+        <v>46027</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -1825,25 +1829,25 @@
         <v>12</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>67</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F14" s="4">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="G14" s="5">
-        <v>46042</v>
+        <v>46026</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -1852,25 +1856,25 @@
         <v>13</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>67</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F15" s="4">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="G15" s="5">
-        <v>46032</v>
+        <v>46042</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -1879,25 +1883,25 @@
         <v>14</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>67</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F16" s="4">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="G16" s="5">
-        <v>46042</v>
+        <v>46032</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -1906,25 +1910,25 @@
         <v>15</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>67</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="F17" s="4">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="G17" s="5">
-        <v>46032</v>
+        <v>46042</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -1933,29 +1937,58 @@
         <v>16</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
+        <v>64</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F18" s="4">
+        <v>4</v>
+      </c>
+      <c r="G18" s="5">
+        <v>46032</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
+      <c r="B19" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>67</v>
+      </c>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45672D10-F312-4F86-A41C-E5B7202C36FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1321C0DC-AC02-4485-A9F3-602B8DE5EDFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="86">
   <si>
     <t>S.No.</t>
   </si>
@@ -288,6 +288,12 @@
   </si>
   <si>
     <t>607095-004-0418300</t>
+  </si>
+  <si>
+    <t>607529-020-0114630</t>
+  </si>
+  <si>
+    <t>607529-020-0114639</t>
   </si>
 </sst>
 </file>
@@ -780,8 +786,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H20" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="A2:H20" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H21" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A2:H21" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="14">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
@@ -1486,7 +1492,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56B532C1-7F8B-4592-901A-51A1E632DC96}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultColWidth="37.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -1982,13 +1988,40 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
+      <c r="B20" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="4">
+        <v>10</v>
+      </c>
+      <c r="G20" s="5">
+        <v>46062</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
+        <f>ROW()-2</f>
+        <v>19</v>
+      </c>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1321C0DC-AC02-4485-A9F3-602B8DE5EDFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B3AD120-7BF3-4557-89CD-6EA7B6FE3D32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="93">
   <si>
     <t>S.No.</t>
   </si>
@@ -294,6 +294,27 @@
   </si>
   <si>
     <t>607529-020-0114639</t>
+  </si>
+  <si>
+    <t>Order 3</t>
+  </si>
+  <si>
+    <t>607529-020-0178303</t>
+  </si>
+  <si>
+    <t>607529-020-0178403</t>
+  </si>
+  <si>
+    <t>607529-020-0178103</t>
+  </si>
+  <si>
+    <t>607529-020-0178302</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>145501-145600</t>
   </si>
 </sst>
 </file>
@@ -786,8 +807,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H21" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="A2:H21" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H23" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A2:H23" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="14">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
@@ -1186,12 +1207,8 @@
         <f t="shared" ref="A3:A16" si="0">ROW()-2</f>
         <v>1</v>
       </c>
-      <c r="B3" s="4">
-        <v>750</v>
-      </c>
-      <c r="C3" s="5">
-        <v>46039</v>
-      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4">
         <v>250</v>
@@ -1324,8 +1341,12 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
+      <c r="B9" s="4">
+        <v>250</v>
+      </c>
+      <c r="C9" s="5">
+        <v>46014</v>
+      </c>
       <c r="D9" s="4" t="s">
         <v>72</v>
       </c>
@@ -1347,8 +1368,12 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
+      <c r="B10" s="4">
+        <v>500</v>
+      </c>
+      <c r="C10" s="5">
+        <v>46025</v>
+      </c>
       <c r="D10" s="4" t="s">
         <v>49</v>
       </c>
@@ -1369,10 +1394,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="4">
-        <v>250</v>
+        <v>750</v>
       </c>
       <c r="C11" s="5">
-        <v>46014</v>
+        <v>46039</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4">
@@ -1391,12 +1416,8 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B12" s="4">
-        <v>500</v>
-      </c>
-      <c r="C12" s="5">
-        <v>46025</v>
-      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4">
         <v>60</v>
@@ -1439,10 +1460,18 @@
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="5"/>
+      <c r="D14" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E14" s="4">
+        <v>100</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" s="5">
+        <v>46065</v>
+      </c>
       <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -1464,14 +1493,14 @@
         <v>14</v>
       </c>
       <c r="B16" s="7">
-        <f>SUM(B3:B15)</f>
+        <f>SUM(B4:B15)</f>
         <v>2000</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="7">
         <f>SUM(E3:E15)</f>
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="5"/>
@@ -1492,7 +1521,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56B532C1-7F8B-4592-901A-51A1E632DC96}">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr defaultColWidth="37.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2015,13 +2044,68 @@
         <f>ROW()-2</f>
         <v>19</v>
       </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
+      <c r="B21" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="4">
+        <v>100</v>
+      </c>
+      <c r="G21" s="5">
+        <v>46065</v>
+      </c>
       <c r="H21" s="4"/>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
+        <f t="shared" ref="A22:A23" si="1">ROW()-2</f>
+        <v>20</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="4">
+        <v>200</v>
+      </c>
+      <c r="G22" s="5">
+        <v>46065</v>
+      </c>
+      <c r="H22" s="4"/>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="4">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C29" t="s">
+        <v>91</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B3AD120-7BF3-4557-89CD-6EA7B6FE3D32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEED9A74-1AAE-4D37-BD83-474A2ACF0EE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
     <sheet name="RC" sheetId="2" r:id="rId1"/>
-    <sheet name="FASTTAGS" sheetId="4" r:id="rId2"/>
+    <sheet name="FASTag" sheetId="4" r:id="rId2"/>
     <sheet name="Contacts" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="95">
   <si>
     <t>S.No.</t>
   </si>
@@ -311,10 +311,16 @@
     <t>607529-020-0178302</t>
   </si>
   <si>
-    <t>.</t>
-  </si>
-  <si>
     <t>145501-145600</t>
+  </si>
+  <si>
+    <t>607529-020-0174626</t>
+  </si>
+  <si>
+    <t>607529-020-0178427</t>
+  </si>
+  <si>
+    <t>607529-020-0178404</t>
   </si>
 </sst>
 </file>
@@ -412,13 +418,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -445,6 +451,173 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -604,173 +777,6 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -785,41 +791,41 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:H16" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:H16" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
   <autoFilter ref="A2:H16" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:H16">
     <sortCondition ref="G2:G16"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="24">
+    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="14">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="23"/>
-    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="20"/>
-    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="17"/>
+    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H23" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="A2:H23" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H28" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
+  <autoFilter ref="A2:H28" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="14">
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="24">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="22"/>
+    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1165,16 +1171,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -1461,7 +1467,7 @@
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E14" s="4">
         <v>100</v>
@@ -1521,7 +1527,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56B532C1-7F8B-4592-901A-51A1E632DC96}">
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultColWidth="37.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -1532,16 +1538,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -2007,9 +2013,15 @@
       <c r="D19" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
+      <c r="E19" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="4">
+        <v>25</v>
+      </c>
+      <c r="G19" s="5">
+        <v>46031</v>
+      </c>
       <c r="H19" s="4"/>
     </row>
     <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -2066,7 +2078,7 @@
     </row>
     <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
-        <f t="shared" ref="A22:A23" si="1">ROW()-2</f>
+        <f t="shared" ref="A22:A28" si="1">ROW()-2</f>
         <v>20</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -2094,18 +2106,102 @@
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
+      <c r="B23" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" s="4">
+        <v>1</v>
+      </c>
+      <c r="G23" s="5">
+        <v>46070</v>
+      </c>
       <c r="H23" s="4"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C29" t="s">
-        <v>91</v>
-      </c>
+    <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" s="4">
+        <v>24</v>
+      </c>
+      <c r="G24" s="5">
+        <v>46070</v>
+      </c>
+      <c r="H24" s="4"/>
+    </row>
+    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+    </row>
+    <row r="26" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+    </row>
+    <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="4">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+    </row>
+    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="4">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEED9A74-1AAE-4D37-BD83-474A2ACF0EE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01E70B64-BD30-4C4D-AC99-5BD6BAB4EB48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="97">
   <si>
     <t>S.No.</t>
   </si>
@@ -321,6 +321,12 @@
   </si>
   <si>
     <t>607529-020-0178404</t>
+  </si>
+  <si>
+    <t>607095-004-0462140</t>
+  </si>
+  <si>
+    <t>607095-004-0462189</t>
   </si>
 </sst>
 </file>
@@ -2156,12 +2162,24 @@
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
+      <c r="B25" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F25" s="4">
+        <v>50</v>
+      </c>
+      <c r="G25" s="5">
+        <v>46081</v>
+      </c>
       <c r="H25" s="4"/>
     </row>
     <row r="26" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01E70B64-BD30-4C4D-AC99-5BD6BAB4EB48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFA2C199-8AB7-4D45-A1F6-CC3056CBF3C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFA2C199-8AB7-4D45-A1F6-CC3056CBF3C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C160F21-F35A-4F24-B3B5-D49DC3B0EB77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
     <sheet name="RC" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="100">
   <si>
     <t>S.No.</t>
   </si>
@@ -327,6 +327,15 @@
   </si>
   <si>
     <t>607095-004-0462189</t>
+  </si>
+  <si>
+    <t>Serial</t>
+  </si>
+  <si>
+    <t>58001 - 58250</t>
+  </si>
+  <si>
+    <t>JK0145501 - JK0146250</t>
   </si>
 </sst>
 </file>
@@ -437,7 +446,26 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="28">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -797,57 +825,58 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:H16" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="A2:H16" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:H16">
-    <sortCondition ref="G2:G16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I16" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+  <autoFilter ref="A2:I16" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I16">
+    <sortCondition ref="H2:H16"/>
   </sortState>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="14">
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="15">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="10"/>
-    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="0"/>
+    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="14"/>
+    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H28" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H28" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
   <autoFilter ref="A2:H28" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="24">
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="25">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="22"/>
-    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="18"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}" name="Table1" displayName="Table1" ref="A1:E31" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}" name="Table1" displayName="Table1" ref="A1:E31" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
   <autoFilter ref="A1:E31" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{1D31F252-7F75-4ACE-8E4E-970F96D5D0FB}" name="S.No." dataDxfId="4">
+    <tableColumn id="1" xr3:uid="{1D31F252-7F75-4ACE-8E4E-970F96D5D0FB}" name="S.No." dataDxfId="5">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{5C2AFA5C-CFD5-43A7-83E2-31A9A1E8AA6E}" name="NAME" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{194B191E-FB6F-4E26-9A5A-32D004AC4649}" name="DESIGNATION" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{C758F67A-2E84-46C0-BF1E-17717F5D79AC}" name="CONTACT" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{6C0116B5-2941-4E11-AD47-2ECED03BE947}" name="LOCATION" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{5C2AFA5C-CFD5-43A7-83E2-31A9A1E8AA6E}" name="NAME" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{194B191E-FB6F-4E26-9A5A-32D004AC4649}" name="DESIGNATION" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{C758F67A-2E84-46C0-BF1E-17717F5D79AC}" name="CONTACT" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{6C0116B5-2941-4E11-AD47-2ECED03BE947}" name="LOCATION" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1151,70 +1180,75 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7916C5D2-EBF3-44BC-AD33-13F607DA9441}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:AA16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" customWidth="1"/>
-    <col min="4" max="4" width="34.42578125" customWidth="1"/>
-    <col min="5" max="6" width="32.5703125" customWidth="1"/>
-    <col min="7" max="7" width="16.5703125" customWidth="1"/>
-    <col min="8" max="8" width="21.42578125" customWidth="1"/>
-    <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="26.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="34" style="2" customWidth="1"/>
-    <col min="15" max="15" width="31" customWidth="1"/>
-    <col min="16" max="16" width="21.7109375" customWidth="1"/>
-    <col min="17" max="17" width="21.42578125" customWidth="1"/>
-    <col min="18" max="18" width="35.28515625" customWidth="1"/>
-    <col min="20" max="20" width="10.28515625" customWidth="1"/>
-    <col min="21" max="21" width="26.85546875" customWidth="1"/>
-    <col min="22" max="22" width="17.140625" customWidth="1"/>
-    <col min="23" max="23" width="25.140625" customWidth="1"/>
-    <col min="24" max="26" width="15.5703125" style="3" customWidth="1"/>
-    <col min="27" max="27" width="19.5703125" customWidth="1"/>
+    <col min="2" max="2" width="36.5703125" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" customWidth="1"/>
+    <col min="5" max="5" width="34.42578125" customWidth="1"/>
+    <col min="6" max="7" width="32.5703125" customWidth="1"/>
+    <col min="8" max="8" width="16.5703125" customWidth="1"/>
+    <col min="9" max="9" width="21.42578125" customWidth="1"/>
+    <col min="12" max="12" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="26.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="34" style="2" customWidth="1"/>
+    <col min="16" max="16" width="31" customWidth="1"/>
+    <col min="17" max="17" width="21.7109375" customWidth="1"/>
+    <col min="18" max="18" width="21.42578125" customWidth="1"/>
+    <col min="19" max="19" width="35.28515625" customWidth="1"/>
+    <col min="21" max="21" width="10.28515625" customWidth="1"/>
+    <col min="22" max="22" width="26.85546875" customWidth="1"/>
+    <col min="23" max="23" width="17.140625" customWidth="1"/>
+    <col min="24" max="24" width="25.140625" customWidth="1"/>
+    <col min="25" max="27" width="15.5703125" style="3" customWidth="1"/>
+    <col min="28" max="28" width="19.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="33.75" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:9" ht="33.75" x14ac:dyDescent="0.5">
       <c r="A1" s="9" t="s">
         <v>37</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
-      <c r="D1" s="10"/>
+      <c r="D1" s="9"/>
       <c r="E1" s="10"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
-    </row>
-    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I1" s="10"/>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <f t="shared" ref="A3:A16" si="0">ROW()-2</f>
         <v>1</v>
@@ -1222,20 +1256,21 @@
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
-      <c r="E3" s="4">
+      <c r="E3" s="4"/>
+      <c r="F3" s="4">
         <v>250</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="5">
+      <c r="H3" s="5">
         <v>45983</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -1243,20 +1278,21 @@
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
-      <c r="E4" s="4">
+      <c r="E4" s="4"/>
+      <c r="F4" s="4">
         <v>245</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="G4" s="5">
+      <c r="H4" s="5">
         <v>45983</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1264,43 +1300,45 @@
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
-      <c r="E5" s="4">
+      <c r="E5" s="4"/>
+      <c r="F5" s="4">
         <v>5</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="5">
+      <c r="H5" s="5">
         <v>46012</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="I5" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="4"/>
+      <c r="C6" s="4">
         <v>250</v>
       </c>
-      <c r="C6" s="5">
+      <c r="D6" s="5">
         <v>45983</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4">
+      <c r="E6" s="4"/>
+      <c r="F6" s="4">
         <v>75</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="5">
+      <c r="H6" s="5">
         <v>46014</v>
       </c>
-      <c r="H6" s="4"/>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I6" s="4"/>
+    </row>
+    <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1308,122 +1346,129 @@
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
-      <c r="E7" s="4">
+      <c r="E7" s="4"/>
+      <c r="F7" s="4">
         <v>75</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="G7" s="5">
+      <c r="H7" s="5">
         <v>46014</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="I7" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="4"/>
+      <c r="C8" s="4">
         <v>250</v>
       </c>
-      <c r="C8" s="5">
+      <c r="D8" s="5">
         <v>45983</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E8" s="4">
+      <c r="F8" s="4">
         <v>100</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="5">
+      <c r="H8" s="5">
         <v>46025</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="I8" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="4"/>
+      <c r="C9" s="4">
         <v>250</v>
       </c>
-      <c r="C9" s="5">
+      <c r="D9" s="5">
         <v>46014</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="E9" s="4">
+      <c r="F9" s="4">
         <v>150</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="5">
+      <c r="H9" s="5">
         <v>46025</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="I9" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="4"/>
+      <c r="C10" s="4">
         <v>500</v>
       </c>
-      <c r="C10" s="5">
+      <c r="D10" s="5">
         <v>46025</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="4">
+      <c r="F10" s="4">
         <v>150</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="G10" s="5">
+      <c r="H10" s="5">
         <v>46027</v>
       </c>
-      <c r="H10" s="4"/>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I10" s="4"/>
+    </row>
+    <row r="11" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" s="4">
         <v>750</v>
       </c>
-      <c r="C11" s="5">
+      <c r="D11" s="5">
         <v>46039</v>
       </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4">
+      <c r="E11" s="4"/>
+      <c r="F11" s="4">
         <v>40</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="5">
+      <c r="H11" s="5">
         <v>46034</v>
       </c>
-      <c r="H11" s="4"/>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I11" s="4"/>
+    </row>
+    <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1431,96 +1476,107 @@
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="4">
+      <c r="E12" s="4"/>
+      <c r="F12" s="4">
         <v>60</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="G12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="5">
+      <c r="H12" s="5">
         <v>46037</v>
       </c>
-      <c r="H12" s="4"/>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I12" s="4"/>
+    </row>
+    <row r="13" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="4"/>
+      <c r="E13" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E13" s="4">
+      <c r="F13" s="4">
         <v>250</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="G13" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G13" s="5">
+      <c r="H13" s="5">
         <v>46042</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="I13" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="4"/>
+      <c r="E14" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="E14" s="4">
+      <c r="F14" s="4">
         <v>100</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="G14" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="G14" s="5">
+      <c r="H14" s="5">
         <v>46065</v>
       </c>
-      <c r="H14" s="4"/>
-    </row>
-    <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I14" s="4"/>
+    </row>
+    <row r="15" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
+      <c r="B15" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" s="4">
+        <v>250</v>
+      </c>
+      <c r="D15" s="5">
+        <v>46093</v>
+      </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="4"/>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="4"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="4"/>
+    </row>
+    <row r="16" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B16" s="7">
-        <f>SUM(B4:B15)</f>
-        <v>2000</v>
-      </c>
-      <c r="C16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="7">
+        <f>SUM(C4:C15)</f>
+        <v>2250</v>
+      </c>
       <c r="D16" s="4"/>
-      <c r="E16" s="7">
-        <f>SUM(E3:E15)</f>
+      <c r="E16" s="4"/>
+      <c r="F16" s="7">
+        <f>SUM(F3:F15)</f>
         <v>1500</v>
       </c>
-      <c r="F16" s="4"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C160F21-F35A-4F24-B3B5-D49DC3B0EB77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBBBCB68-057D-4670-B035-67FD850FF9DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="102">
   <si>
     <t>S.No.</t>
   </si>
@@ -336,6 +336,12 @@
   </si>
   <si>
     <t>JK0145501 - JK0146250</t>
+  </si>
+  <si>
+    <t>146151-165250</t>
+  </si>
+  <si>
+    <t>Showkat Trag</t>
   </si>
 </sst>
 </file>
@@ -433,13 +439,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -447,25 +453,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="28">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -485,173 +472,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -811,6 +631,192 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -825,58 +831,58 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I16" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
-  <autoFilter ref="A2:I16" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I16">
-    <sortCondition ref="H2:H16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I20" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+  <autoFilter ref="A2:I20" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I20">
+    <sortCondition ref="H2:H20"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="15">
+    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="25">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="0"/>
-    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="14"/>
-    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="24"/>
+    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="23"/>
+    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="20"/>
+    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H28" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H28" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
   <autoFilter ref="A2:H28" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="25">
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="14">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="20"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="19"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}" name="Table1" displayName="Table1" ref="A1:E31" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}" name="Table1" displayName="Table1" ref="A1:E31" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A1:E31" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{1D31F252-7F75-4ACE-8E4E-970F96D5D0FB}" name="S.No." dataDxfId="5">
+    <tableColumn id="1" xr3:uid="{1D31F252-7F75-4ACE-8E4E-970F96D5D0FB}" name="S.No." dataDxfId="4">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{5C2AFA5C-CFD5-43A7-83E2-31A9A1E8AA6E}" name="NAME" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{194B191E-FB6F-4E26-9A5A-32D004AC4649}" name="DESIGNATION" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{C758F67A-2E84-46C0-BF1E-17717F5D79AC}" name="CONTACT" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{6C0116B5-2941-4E11-AD47-2ECED03BE947}" name="LOCATION" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{5C2AFA5C-CFD5-43A7-83E2-31A9A1E8AA6E}" name="NAME" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{194B191E-FB6F-4E26-9A5A-32D004AC4649}" name="DESIGNATION" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{C758F67A-2E84-46C0-BF1E-17717F5D79AC}" name="CONTACT" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{6C0116B5-2941-4E11-AD47-2ECED03BE947}" name="LOCATION" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1180,7 +1186,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7916C5D2-EBF3-44BC-AD33-13F607DA9441}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AA16"/>
+  <dimension ref="A1:AA20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -1207,17 +1213,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -1250,7 +1256,7 @@
     </row>
     <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
-        <f t="shared" ref="A3:A16" si="0">ROW()-2</f>
+        <f t="shared" ref="A3:A20" si="0">ROW()-2</f>
         <v>1</v>
       </c>
       <c r="B3" s="4"/>
@@ -1548,31 +1554,97 @@
       <c r="D15" s="5">
         <v>46093</v>
       </c>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="4"/>
+      <c r="E15" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F15" s="4">
+        <v>100</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" s="5">
+        <v>46095</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="16" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
-        <f t="shared" si="0"/>
+        <f>ROW()-2</f>
         <v>14</v>
       </c>
       <c r="B16" s="4"/>
-      <c r="C16" s="7">
-        <f>SUM(C4:C15)</f>
-        <v>2250</v>
-      </c>
-      <c r="D16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="5"/>
       <c r="E16" s="4"/>
-      <c r="F16" s="7">
-        <f>SUM(F3:F15)</f>
-        <v>1500</v>
-      </c>
+      <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="5"/>
       <c r="I16" s="4"/>
+    </row>
+    <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <f>ROW()-2</f>
+        <v>15</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="4"/>
+    </row>
+    <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <f>ROW()-2</f>
+        <v>16</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="4"/>
+    </row>
+    <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
+        <f>ROW()-2</f>
+        <v>17</v>
+      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="4"/>
+    </row>
+    <row r="20" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="7">
+        <f>SUM(C4:C15)</f>
+        <v>2250</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="7">
+        <f>SUM(F3:F15)</f>
+        <v>1600</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1600,16 +1672,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBBBCB68-057D-4670-B035-67FD850FF9DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1BDF968-6BD6-4915-8F3E-8B33CD7E9928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
     <sheet name="RC" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="106">
   <si>
     <t>S.No.</t>
   </si>
@@ -342,6 +342,18 @@
   </si>
   <si>
     <t>Showkat Trag</t>
+  </si>
+  <si>
+    <t>58001 -58100</t>
+  </si>
+  <si>
+    <t>jaz</t>
+  </si>
+  <si>
+    <t>607095-004-0462201</t>
+  </si>
+  <si>
+    <t>607095-004-0462250</t>
   </si>
 </sst>
 </file>
@@ -1578,11 +1590,21 @@
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="5"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="4"/>
+      <c r="E16" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F16" s="4">
+        <v>100</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="5">
+        <v>46100</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
@@ -2315,13 +2337,27 @@
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
+      <c r="B26" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F26" s="4">
+        <v>50</v>
+      </c>
+      <c r="G26" s="5">
+        <v>46100</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="4">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1BDF968-6BD6-4915-8F3E-8B33CD7E9928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2BD251C-2C78-4273-A0FE-BEFAF86AA601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
     <sheet name="RC" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="113">
   <si>
     <t>S.No.</t>
   </si>
@@ -354,6 +354,27 @@
   </si>
   <si>
     <t>607095-004-0462250</t>
+  </si>
+  <si>
+    <t>JK0128251 - JK0128350</t>
+  </si>
+  <si>
+    <t>YAWAR AT ARENA</t>
+  </si>
+  <si>
+    <t>Order 4</t>
+  </si>
+  <si>
+    <t>608268-006-0288700</t>
+  </si>
+  <si>
+    <t>607529-019-0422442</t>
+  </si>
+  <si>
+    <t>607529-019-0422491</t>
+  </si>
+  <si>
+    <t>JK0128251 - JK0128500</t>
   </si>
 </sst>
 </file>
@@ -451,13 +472,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -484,163 +505,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -829,6 +693,163 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -843,42 +864,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I20" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I20" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
   <autoFilter ref="A2:I20" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I20">
     <sortCondition ref="H2:H20"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="25">
+    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="15">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="24"/>
-    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="23"/>
-    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="20"/>
-    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H28" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="A2:H28" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H30" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+  <autoFilter ref="A2:H30" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="14">
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="25">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1225,17 +1246,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -1611,14 +1632,30 @@
         <f>ROW()-2</f>
         <v>15</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="4"/>
+      <c r="B17" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C17" s="4">
+        <v>250</v>
+      </c>
+      <c r="D17" s="5">
+        <v>46112</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F17" s="4">
+        <v>100</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H17" s="5">
+        <v>46112</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
@@ -1683,7 +1720,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56B532C1-7F8B-4592-901A-51A1E632DC96}">
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultColWidth="37.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -1694,16 +1731,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -2234,7 +2271,7 @@
     </row>
     <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
-        <f t="shared" ref="A22:A28" si="1">ROW()-2</f>
+        <f t="shared" ref="A22:A30" si="1">ROW()-2</f>
         <v>20</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -2364,12 +2401,24 @@
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
+      <c r="B27" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" s="4">
+        <v>200</v>
+      </c>
+      <c r="G27" s="5">
+        <v>46112</v>
+      </c>
       <c r="H27" s="4"/>
     </row>
     <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -2377,13 +2426,51 @@
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
+      <c r="B28" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F28" s="4">
+        <v>50</v>
+      </c>
+      <c r="G28" s="5">
+        <v>46112</v>
+      </c>
       <c r="H28" s="4"/>
+    </row>
+    <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="4">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+    </row>
+    <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="4">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2BD251C-2C78-4273-A0FE-BEFAF86AA601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1169770C-1932-47AC-9E56-928E226775D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="114">
   <si>
     <t>S.No.</t>
   </si>
@@ -375,6 +375,9 @@
   </si>
   <si>
     <t>JK0128251 - JK0128500</t>
+  </si>
+  <si>
+    <t>JK0128351 - JK0128500</t>
   </si>
 </sst>
 </file>
@@ -472,13 +475,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -505,6 +508,163 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -693,163 +853,6 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -864,42 +867,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I20" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I20" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
   <autoFilter ref="A2:I20" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I20">
     <sortCondition ref="H2:H20"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="15">
+    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="25">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="10"/>
-    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="24"/>
+    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="23"/>
+    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="20"/>
+    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H30" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H30" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
   <autoFilter ref="A2:H30" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="25">
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="14">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="20"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="19"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1246,17 +1249,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -1665,10 +1668,18 @@
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="5"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="5"/>
+      <c r="E18" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F18" s="4">
+        <v>150</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="5">
+        <v>46112</v>
+      </c>
       <c r="I18" s="4"/>
     </row>
     <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -1731,16 +1742,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1169770C-1932-47AC-9E56-928E226775D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF697C18-B3C6-4B3D-ADAA-69F51FAD3A00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="117">
   <si>
     <t>S.No.</t>
   </si>
@@ -378,6 +378,15 @@
   </si>
   <si>
     <t>JK0128351 - JK0128500</t>
+  </si>
+  <si>
+    <t>608268-006-0288899</t>
+  </si>
+  <si>
+    <t>608268-006-0288900</t>
+  </si>
+  <si>
+    <t>608268-006-0289099</t>
   </si>
 </sst>
 </file>
@@ -1639,7 +1648,7 @@
         <v>112</v>
       </c>
       <c r="C17" s="4">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="D17" s="5">
         <v>46112</v>
@@ -1703,14 +1712,14 @@
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="7">
-        <f>SUM(C4:C15)</f>
-        <v>2250</v>
+        <f>SUM(C4:C19)</f>
+        <v>2750</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="7">
-        <f>SUM(F3:F15)</f>
-        <v>1600</v>
+        <f>SUM(F3:F18)</f>
+        <v>1950</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="5"/>
@@ -2416,7 +2425,7 @@
         <v>109</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>108</v>
@@ -2462,12 +2471,24 @@
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
+      <c r="B29" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" s="4">
+        <v>200</v>
+      </c>
+      <c r="G29" s="5">
+        <v>46113</v>
+      </c>
       <c r="H29" s="4"/>
     </row>
     <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF697C18-B3C6-4B3D-ADAA-69F51FAD3A00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D2A8FF5-6324-4C01-8BBA-2A054C69BD21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="117">
   <si>
     <t>S.No.</t>
   </si>
@@ -248,9 +248,6 @@
     <t>2 TAGS</t>
   </si>
   <si>
-    <t>nexa</t>
-  </si>
-  <si>
     <t>NEXA</t>
   </si>
   <si>
@@ -387,6 +384,9 @@
   </si>
   <si>
     <t>608268-006-0289099</t>
+  </si>
+  <si>
+    <t>JK0158101 -JK0158150</t>
   </si>
 </sst>
 </file>
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>21</v>
@@ -1293,7 +1293,7 @@
         <v>38</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>22</v>
@@ -1424,7 +1424,7 @@
         <v>45983</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F8" s="4">
         <v>100</v>
@@ -1452,7 +1452,7 @@
         <v>46014</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F9" s="4">
         <v>150</v>
@@ -1464,7 +1464,7 @@
         <v>46025</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -1486,7 +1486,7 @@
         <v>150</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H10" s="5">
         <v>46027</v>
@@ -1499,7 +1499,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C11" s="4">
         <v>750</v>
@@ -1548,7 +1548,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F13" s="4">
         <v>250</v>
@@ -1560,7 +1560,7 @@
         <v>46042</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -1572,7 +1572,7 @@
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F14" s="4">
         <v>100</v>
@@ -1591,7 +1591,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C15" s="4">
         <v>250</v>
@@ -1600,7 +1600,7 @@
         <v>46093</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F15" s="4">
         <v>100</v>
@@ -1612,7 +1612,7 @@
         <v>46095</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -1624,7 +1624,7 @@
       <c r="C16" s="4"/>
       <c r="D16" s="5"/>
       <c r="E16" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F16" s="4">
         <v>100</v>
@@ -1636,7 +1636,7 @@
         <v>46100</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -1645,7 +1645,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C17" s="4">
         <v>500</v>
@@ -1654,7 +1654,7 @@
         <v>46112</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F17" s="4">
         <v>100</v>
@@ -1666,7 +1666,7 @@
         <v>46112</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -1678,7 +1678,7 @@
       <c r="C18" s="4"/>
       <c r="D18" s="5"/>
       <c r="E18" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F18" s="4">
         <v>150</v>
@@ -1699,10 +1699,18 @@
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="5"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="5"/>
+      <c r="E19" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F19" s="4">
+        <v>50</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H19" s="5">
+        <v>46128</v>
+      </c>
       <c r="I19" s="4"/>
     </row>
     <row r="20" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2056,10 +2064,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>82</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>83</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>67</v>
@@ -2074,7 +2082,7 @@
         <v>46027</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -2113,7 +2121,7 @@
         <v>57</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>67</v>
@@ -2128,7 +2136,7 @@
         <v>46042</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -2182,7 +2190,7 @@
         <v>46042</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -2218,7 +2226,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>58</v>
@@ -2243,10 +2251,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>85</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>67</v>
@@ -2270,13 +2278,13 @@
         <v>19</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>88</v>
-      </c>
       <c r="D21" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>13</v>
@@ -2295,13 +2303,13 @@
         <v>20</v>
       </c>
       <c r="B22" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>90</v>
-      </c>
       <c r="D22" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>16</v>
@@ -2320,13 +2328,13 @@
         <v>21</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>17</v>
@@ -2345,13 +2353,13 @@
         <v>22</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>17</v>
@@ -2370,13 +2378,13 @@
         <v>23</v>
       </c>
       <c r="B25" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>96</v>
-      </c>
       <c r="D25" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>17</v>
@@ -2395,13 +2403,13 @@
         <v>24</v>
       </c>
       <c r="B26" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C26" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>105</v>
-      </c>
       <c r="D26" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>16</v>
@@ -2413,7 +2421,7 @@
         <v>46100</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -2422,13 +2430,13 @@
         <v>25</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>16</v>
@@ -2447,13 +2455,13 @@
         <v>26</v>
       </c>
       <c r="B28" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C28" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="C28" s="6" t="s">
-        <v>111</v>
-      </c>
       <c r="D28" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>16</v>
@@ -2472,13 +2480,13 @@
         <v>27</v>
       </c>
       <c r="B29" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>116</v>
-      </c>
       <c r="D29" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>13</v>

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D2A8FF5-6324-4C01-8BBA-2A054C69BD21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C63FFC4-7AEF-47DD-97F7-1BB710B3923D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="118">
   <si>
     <t>S.No.</t>
   </si>
@@ -371,9 +371,6 @@
     <t>607529-019-0422491</t>
   </si>
   <si>
-    <t>JK0128251 - JK0128500</t>
-  </si>
-  <si>
     <t>JK0128351 - JK0128500</t>
   </si>
   <si>
@@ -387,6 +384,12 @@
   </si>
   <si>
     <t>JK0158101 -JK0158150</t>
+  </si>
+  <si>
+    <t>JK0128251 - JK0128750</t>
+  </si>
+  <si>
+    <t>JK0128501-JK0128600</t>
   </si>
 </sst>
 </file>
@@ -876,10 +879,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I20" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
-  <autoFilter ref="A2:I20" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I20">
-    <sortCondition ref="H2:H20"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I22" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+  <autoFilter ref="A2:I22" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I22">
+    <sortCondition ref="H2:H22"/>
   </sortState>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="25">
@@ -1231,7 +1234,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7916C5D2-EBF3-44BC-AD33-13F607DA9441}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AA20"/>
+  <dimension ref="A1:AA22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -1301,7 +1304,7 @@
     </row>
     <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
-        <f t="shared" ref="A3:A20" si="0">ROW()-2</f>
+        <f t="shared" ref="A3:A22" si="0">ROW()-2</f>
         <v>1</v>
       </c>
       <c r="B3" s="4"/>
@@ -1645,10 +1648,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C17" s="4">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="D17" s="5">
         <v>46112</v>
@@ -1678,7 +1681,7 @@
       <c r="C18" s="4"/>
       <c r="D18" s="5"/>
       <c r="E18" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F18" s="4">
         <v>150</v>
@@ -1700,7 +1703,7 @@
       <c r="C19" s="4"/>
       <c r="D19" s="5"/>
       <c r="E19" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F19" s="4">
         <v>50</v>
@@ -1715,23 +1718,61 @@
     </row>
     <row r="20" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
-        <f t="shared" si="0"/>
+        <f>ROW()-2</f>
         <v>18</v>
       </c>
       <c r="B20" s="4"/>
-      <c r="C20" s="7">
-        <f>SUM(C4:C19)</f>
-        <v>2750</v>
-      </c>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="7">
+      <c r="C20" s="4"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F20" s="4">
+        <v>100</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H20" s="5">
+        <v>46133</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
+        <f>ROW()-2</f>
+        <v>19</v>
+      </c>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="4"/>
+    </row>
+    <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B22" s="4"/>
+      <c r="C22" s="7">
+        <f>SUM(C4:C21)</f>
+        <v>3000</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="7">
         <f>SUM(F3:F18)</f>
         <v>1950</v>
       </c>
-      <c r="G20" s="4"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2433,7 +2474,7 @@
         <v>108</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>107</v>
@@ -2480,10 +2521,10 @@
         <v>27</v>
       </c>
       <c r="B29" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C29" s="6" t="s">
         <v>114</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>115</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>107</v>

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C63FFC4-7AEF-47DD-97F7-1BB710B3923D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17054E80-4500-4165-A87C-7CEA86647887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="122">
   <si>
     <t>S.No.</t>
   </si>
@@ -390,6 +390,18 @@
   </si>
   <si>
     <t>JK0128501-JK0128600</t>
+  </si>
+  <si>
+    <t>608268-006-0289100</t>
+  </si>
+  <si>
+    <t>608268-006-0289149</t>
+  </si>
+  <si>
+    <t>JK0128601-JK0128750</t>
+  </si>
+  <si>
+    <t>Hilal Sir GM</t>
   </si>
 </sst>
 </file>
@@ -487,13 +499,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -520,163 +532,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -865,6 +720,163 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -879,42 +891,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I22" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
-  <autoFilter ref="A2:I22" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I22">
-    <sortCondition ref="H2:H22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I25" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+  <autoFilter ref="A2:I25" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I25">
+    <sortCondition ref="H2:H25"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="25">
+    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="15">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="24"/>
-    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="23"/>
-    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="20"/>
-    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H30" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H30" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
   <autoFilter ref="A2:H30" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="14">
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="25">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1234,7 +1246,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7916C5D2-EBF3-44BC-AD33-13F607DA9441}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AA22"/>
+  <dimension ref="A1:AA25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -1261,17 +1273,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -1304,7 +1316,7 @@
     </row>
     <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
-        <f t="shared" ref="A3:A22" si="0">ROW()-2</f>
+        <f t="shared" ref="A3:A25" si="0">ROW()-2</f>
         <v>1</v>
       </c>
       <c r="B3" s="4"/>
@@ -1620,7 +1632,7 @@
     </row>
     <row r="16" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" ref="A16:A21" si="1">ROW()-2</f>
         <v>14</v>
       </c>
       <c r="B16" s="4"/>
@@ -1644,7 +1656,7 @@
     </row>
     <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -1674,7 +1686,7 @@
     </row>
     <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="B18" s="4"/>
@@ -1696,7 +1708,7 @@
     </row>
     <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="B19" s="4"/>
@@ -1718,7 +1730,7 @@
     </row>
     <row r="20" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="B20" s="4"/>
@@ -1742,37 +1754,89 @@
     </row>
     <row r="21" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="5"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="4"/>
+      <c r="E21" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F21" s="4">
+        <v>150</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" s="5">
+        <v>46134</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
-        <f t="shared" si="0"/>
+        <f>ROW()-2</f>
         <v>20</v>
       </c>
       <c r="B22" s="4"/>
-      <c r="C22" s="7">
-        <f>SUM(C4:C21)</f>
-        <v>3000</v>
-      </c>
-      <c r="D22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="5"/>
       <c r="E22" s="4"/>
-      <c r="F22" s="7">
-        <f>SUM(F3:F18)</f>
-        <v>1950</v>
-      </c>
+      <c r="F22" s="4"/>
       <c r="G22" s="4"/>
       <c r="H22" s="5"/>
       <c r="I22" s="4"/>
+    </row>
+    <row r="23" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="4">
+        <f>ROW()-2</f>
+        <v>21</v>
+      </c>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="4"/>
+    </row>
+    <row r="24" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
+        <f>ROW()-2</f>
+        <v>22</v>
+      </c>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="4"/>
+    </row>
+    <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="7">
+        <f>SUM(C4:C21)</f>
+        <v>3000</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="7">
+        <f>SUM(F3:F18)</f>
+        <v>1950</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1800,16 +1864,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -2545,12 +2609,24 @@
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
+      <c r="B30" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F30" s="4">
+        <v>50</v>
+      </c>
+      <c r="G30" s="5">
+        <v>46134</v>
+      </c>
       <c r="H30" s="4"/>
     </row>
   </sheetData>

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17054E80-4500-4165-A87C-7CEA86647887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDC0D910-3787-418F-9646-30815B05C403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
     <sheet name="RC" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="125">
   <si>
     <t>S.No.</t>
   </si>
@@ -402,6 +402,15 @@
   </si>
   <si>
     <t>Hilal Sir GM</t>
+  </si>
+  <si>
+    <t>608268-006-0416447</t>
+  </si>
+  <si>
+    <t>608268-006-0416499</t>
+  </si>
+  <si>
+    <t>Order 5</t>
   </si>
 </sst>
 </file>
@@ -499,13 +508,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -532,6 +541,163 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -720,163 +886,6 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -891,42 +900,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I25" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I25" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
   <autoFilter ref="A2:I25" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I25">
     <sortCondition ref="H2:H25"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="15">
+    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="25">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="10"/>
-    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="24"/>
+    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="23"/>
+    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="20"/>
+    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H30" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
-  <autoFilter ref="A2:H30" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H33" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A2:H33" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="25">
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="14">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="20"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="19"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1273,17 +1282,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -1853,7 +1862,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56B532C1-7F8B-4592-901A-51A1E632DC96}">
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultColWidth="37.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -1864,16 +1873,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -2404,7 +2413,7 @@
     </row>
     <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
-        <f t="shared" ref="A22:A30" si="1">ROW()-2</f>
+        <f t="shared" ref="A22:A33" si="1">ROW()-2</f>
         <v>20</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -2628,6 +2637,57 @@
         <v>46134</v>
       </c>
       <c r="H30" s="4"/>
+    </row>
+    <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="4">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F31" s="4">
+        <v>50</v>
+      </c>
+      <c r="G31" s="5">
+        <v>46146</v>
+      </c>
+      <c r="H31" s="4"/>
+    </row>
+    <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="4">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+    </row>
+    <row r="33" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="4">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDC0D910-3787-418F-9646-30815B05C403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{104A8221-AA5E-459B-BAC4-AFCEA1100EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
     <sheet name="RC" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="128">
   <si>
     <t>S.No.</t>
   </si>
@@ -411,6 +411,15 @@
   </si>
   <si>
     <t>Order 5</t>
+  </si>
+  <si>
+    <t>JK0111251 - JK0111750</t>
+  </si>
+  <si>
+    <t>JK0111401 - JK0111500</t>
+  </si>
+  <si>
+    <t>SHOWKAT TRAG</t>
   </si>
 </sst>
 </file>
@@ -508,13 +517,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -541,163 +550,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -886,6 +738,163 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -900,42 +909,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I25" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I25" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
   <autoFilter ref="A2:I25" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I25">
     <sortCondition ref="H2:H25"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="25">
+    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="15">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="24"/>
-    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="23"/>
-    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="20"/>
-    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H33" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H33" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
   <autoFilter ref="A2:H33" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="14">
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="25">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1282,17 +1291,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -1790,14 +1799,30 @@
         <f>ROW()-2</f>
         <v>20</v>
       </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="4"/>
+      <c r="B22" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C22" s="4">
+        <v>500</v>
+      </c>
+      <c r="D22" s="5">
+        <v>46158</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F22" s="4">
+        <v>100</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H22" s="5">
+        <v>46158</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="23" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
@@ -1873,16 +1898,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{104A8221-AA5E-459B-BAC4-AFCEA1100EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFAF04E7-6491-4352-93C0-E23F743C7729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
     <sheet name="RC" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="133">
   <si>
     <t>S.No.</t>
   </si>
@@ -420,6 +420,21 @@
   </si>
   <si>
     <t>SHOWKAT TRAG</t>
+  </si>
+  <si>
+    <t>JK0111251 - JK01117400</t>
+  </si>
+  <si>
+    <t>Manzoor sir</t>
+  </si>
+  <si>
+    <t>608268-006-0416500</t>
+  </si>
+  <si>
+    <t>Order 6</t>
+  </si>
+  <si>
+    <t>608268-006-0416649</t>
   </si>
 </sst>
 </file>
@@ -517,13 +532,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -550,6 +565,163 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -738,163 +910,6 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -909,42 +924,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I25" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I25" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
   <autoFilter ref="A2:I25" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I25">
     <sortCondition ref="H2:H25"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="15">
+    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="25">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="10"/>
-    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="24"/>
+    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="23"/>
+    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="20"/>
+    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H33" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H33" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
   <autoFilter ref="A2:H33" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="25">
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="14">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="20"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="19"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1291,17 +1306,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -1832,11 +1847,21 @@
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
       <c r="D23" s="5"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="4"/>
+      <c r="E23" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F23" s="4">
+        <v>150</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" s="5">
+        <v>46158</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="24" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
@@ -1898,16 +1923,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -2693,13 +2718,27 @@
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
+      <c r="B32" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" s="4">
+        <v>150</v>
+      </c>
+      <c r="G32" s="5">
+        <v>46161</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="33" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="4">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFAF04E7-6491-4352-93C0-E23F743C7729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E956398F-1276-44C9-9527-A19499934773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
@@ -441,7 +441,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -486,6 +486,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -513,7 +519,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -532,15 +538,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -565,163 +572,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -910,6 +760,163 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -924,42 +931,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I25" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I25" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
   <autoFilter ref="A2:I25" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I25">
     <sortCondition ref="H2:H25"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="25">
+    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="15">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="24"/>
-    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="23"/>
-    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="20"/>
-    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H33" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H33" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
   <autoFilter ref="A2:H33" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="14">
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="25">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1306,17 +1313,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -1912,7 +1919,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56B532C1-7F8B-4592-901A-51A1E632DC96}">
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr defaultColWidth="37.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -1923,16 +1930,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -2752,6 +2759,9 @@
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C38" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E956398F-1276-44C9-9527-A19499934773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0108017B-EDCC-489F-A88A-F9FAA7598491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
@@ -538,6 +538,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -547,7 +548,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1313,17 +1313,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -1930,16 +1930,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -2761,7 +2761,7 @@
       <c r="H33" s="4"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C38" s="11"/>
+      <c r="C38" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0108017B-EDCC-489F-A88A-F9FAA7598491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5BB1AB8-DE1C-4487-83D0-F3433E11D882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="135">
   <si>
     <t>S.No.</t>
   </si>
@@ -435,6 +435,12 @@
   </si>
   <si>
     <t>608268-006-0416649</t>
+  </si>
+  <si>
+    <t>608268-006-0416550</t>
+  </si>
+  <si>
+    <t>608268-006-0416699</t>
   </si>
 </sst>
 </file>
@@ -2752,12 +2758,24 @@
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
+      <c r="B33" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33" s="4">
+        <v>50</v>
+      </c>
+      <c r="G33" s="5">
+        <v>46165</v>
+      </c>
       <c r="H33" s="4"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5BB1AB8-DE1C-4487-83D0-F3433E11D882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D0ADE5F-36E1-4907-B864-A99E809FCF7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="3960" yWindow="90" windowWidth="20040" windowHeight="11715" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
     <sheet name="RC" sheetId="2" r:id="rId1"/>
-    <sheet name="FASTag" sheetId="4" r:id="rId2"/>
-    <sheet name="Contacts" sheetId="1" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId2"/>
+    <sheet name="FASTag" sheetId="4" r:id="rId3"/>
+    <sheet name="Contacts" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="137">
   <si>
     <t>S.No.</t>
   </si>
@@ -441,6 +442,12 @@
   </si>
   <si>
     <t>608268-006-0416699</t>
+  </si>
+  <si>
+    <t>JK0111511 - JK01111570</t>
+  </si>
+  <si>
+    <t>SELF</t>
   </si>
 </sst>
 </file>
@@ -545,13 +552,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -578,6 +585,163 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -766,163 +930,6 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -937,42 +944,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I25" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
-  <autoFilter ref="A2:I25" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I25">
-    <sortCondition ref="H2:H25"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I27" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+  <autoFilter ref="A2:I27" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I27">
+    <sortCondition ref="H2:H27"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="15">
+    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="25">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="10"/>
-    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="24"/>
+    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="23"/>
+    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="20"/>
+    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H33" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H33" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
   <autoFilter ref="A2:H33" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="25">
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="14">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="20"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="19"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1292,7 +1299,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7916C5D2-EBF3-44BC-AD33-13F607DA9441}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AA25"/>
+  <dimension ref="A1:AA27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -1319,17 +1326,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -1362,7 +1369,7 @@
     </row>
     <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
-        <f t="shared" ref="A3:A25" si="0">ROW()-2</f>
+        <f t="shared" ref="A3:A27" si="0">ROW()-2</f>
         <v>1</v>
       </c>
       <c r="B3" s="4"/>
@@ -1884,31 +1891,69 @@
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="5"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="4"/>
+      <c r="E24" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F24" s="4">
+        <v>70</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H24" s="5">
+        <v>46172</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
-        <f t="shared" si="0"/>
+        <f>ROW()-2</f>
         <v>23</v>
       </c>
       <c r="B25" s="4"/>
-      <c r="C25" s="7">
-        <f>SUM(C4:C21)</f>
-        <v>3000</v>
-      </c>
-      <c r="D25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="5"/>
       <c r="E25" s="4"/>
-      <c r="F25" s="7">
-        <f>SUM(F3:F18)</f>
-        <v>1950</v>
-      </c>
+      <c r="F25" s="4"/>
       <c r="G25" s="4"/>
       <c r="H25" s="5"/>
       <c r="I25" s="4"/>
+    </row>
+    <row r="26" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
+        <f>ROW()-2</f>
+        <v>24</v>
+      </c>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="4"/>
+    </row>
+    <row r="27" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="4">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B27" s="4"/>
+      <c r="C27" s="7">
+        <f>SUM(C4:C26)</f>
+        <v>3500</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="7">
+        <f>SUM(F3:F26)</f>
+        <v>2570</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1924,6 +1969,27 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F98680A-C8F8-4C2F-A264-80A3E6ED4AF5}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1">
+        <v>4900</v>
+      </c>
+      <c r="B1" s="3">
+        <v>46168</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56B532C1-7F8B-4592-901A-51A1E632DC96}">
   <dimension ref="A1:H38"/>
   <sheetFormatPr defaultColWidth="37.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1936,16 +2002,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -2792,7 +2858,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4093ECB5-009B-4A95-948D-B5418A73B4F4}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:E31"/>

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D0ADE5F-36E1-4907-B864-A99E809FCF7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{500EEB22-CA19-48DA-80BE-8279E1AB4B7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3960" yWindow="90" windowWidth="20040" windowHeight="11715" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
     <sheet name="RC" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId2"/>
-    <sheet name="FASTag" sheetId="4" r:id="rId3"/>
-    <sheet name="Contacts" sheetId="1" r:id="rId4"/>
+    <sheet name="FASTag" sheetId="4" r:id="rId2"/>
+    <sheet name="Contacts" sheetId="1" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="140">
   <si>
     <t>S.No.</t>
   </si>
@@ -448,6 +448,15 @@
   </si>
   <si>
     <t>SELF</t>
+  </si>
+  <si>
+    <t>608268-006-0416700</t>
+  </si>
+  <si>
+    <t>608268-006-0416799</t>
+  </si>
+  <si>
+    <t>Nasir Driver</t>
   </si>
 </sst>
 </file>
@@ -552,13 +561,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -585,163 +594,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -930,6 +782,163 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -944,42 +953,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I27" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I27" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
   <autoFilter ref="A2:I27" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I27">
     <sortCondition ref="H2:H27"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="25">
+    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="15">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="24"/>
-    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="23"/>
-    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="20"/>
-    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H33" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="A2:H33" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H37" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+  <autoFilter ref="A2:H37" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="14">
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="25">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1326,17 +1335,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -1969,27 +1978,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F98680A-C8F8-4C2F-A264-80A3E6ED4AF5}">
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1">
-        <v>4900</v>
-      </c>
-      <c r="B1" s="3">
-        <v>46168</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56B532C1-7F8B-4592-901A-51A1E632DC96}">
   <dimension ref="A1:H38"/>
   <sheetFormatPr defaultColWidth="37.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2002,16 +1990,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -2542,7 +2530,7 @@
     </row>
     <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
-        <f t="shared" ref="A22:A33" si="1">ROW()-2</f>
+        <f t="shared" ref="A22:A37" si="1">ROW()-2</f>
         <v>20</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -2843,6 +2831,72 @@
         <v>46165</v>
       </c>
       <c r="H33" s="4"/>
+    </row>
+    <row r="34" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="4">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" s="4">
+        <v>100</v>
+      </c>
+      <c r="G34" s="5">
+        <v>46173</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="4">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+    </row>
+    <row r="36" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="4">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+    </row>
+    <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="4">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C38" s="8"/>
@@ -2858,7 +2912,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4093ECB5-009B-4A95-948D-B5418A73B4F4}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:E31"/>
@@ -3221,4 +3275,25 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F98680A-C8F8-4C2F-A264-80A3E6ED4AF5}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1">
+        <v>4900</v>
+      </c>
+      <c r="B1" s="3">
+        <v>46168</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{500EEB22-CA19-48DA-80BE-8279E1AB4B7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F45C20B1-CA2F-49B5-A134-4AE6F5938474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
     <sheet name="RC" sheetId="2" r:id="rId1"/>
@@ -444,9 +444,6 @@
     <t>608268-006-0416699</t>
   </si>
   <si>
-    <t>JK0111511 - JK01111570</t>
-  </si>
-  <si>
     <t>SELF</t>
   </si>
   <si>
@@ -457,6 +454,9 @@
   </si>
   <si>
     <t>Nasir Driver</t>
+  </si>
+  <si>
+    <t>JK0111501 - JK0111600</t>
   </si>
 </sst>
 </file>
@@ -561,13 +561,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -594,6 +594,163 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -782,163 +939,6 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -953,42 +953,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I27" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I27" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
   <autoFilter ref="A2:I27" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I27">
     <sortCondition ref="H2:H27"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="15">
+    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="25">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="10"/>
-    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="24"/>
+    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="23"/>
+    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="20"/>
+    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H37" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H37" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
   <autoFilter ref="A2:H37" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="25">
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="14">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="20"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="19"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1335,17 +1335,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -1901,10 +1901,10 @@
       <c r="C24" s="4"/>
       <c r="D24" s="5"/>
       <c r="E24" s="4" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F24" s="4">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>70</v>
@@ -1913,7 +1913,7 @@
         <v>46172</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -1958,7 +1958,7 @@
       <c r="E27" s="4"/>
       <c r="F27" s="7">
         <f>SUM(F3:F26)</f>
-        <v>2570</v>
+        <v>2600</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="5"/>
@@ -1990,16 +1990,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -2838,10 +2838,10 @@
         <v>32</v>
       </c>
       <c r="B34" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C34" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>131</v>
@@ -2856,7 +2856,7 @@
         <v>46173</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F45C20B1-CA2F-49B5-A134-4AE6F5938474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39137A91-29A8-4412-9765-1DD123E49957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="142">
   <si>
     <t>S.No.</t>
   </si>
@@ -457,6 +457,12 @@
   </si>
   <si>
     <t>JK0111501 - JK0111600</t>
+  </si>
+  <si>
+    <t>JK0111601 - JK0111650</t>
+  </si>
+  <si>
+    <t>Mashooq Sir</t>
   </si>
 </sst>
 </file>
@@ -1924,11 +1930,21 @@
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="5"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="4"/>
+      <c r="E25" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F25" s="4">
+        <v>50</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H25" s="5">
+        <v>46175</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="26" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
@@ -1958,7 +1974,7 @@
       <c r="E27" s="4"/>
       <c r="F27" s="7">
         <f>SUM(F3:F26)</f>
-        <v>2600</v>
+        <v>2650</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="5"/>

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39137A91-29A8-4412-9765-1DD123E49957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0094241-A763-4A73-B42B-DB0703A57BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="144">
   <si>
     <t>S.No.</t>
   </si>
@@ -463,6 +463,12 @@
   </si>
   <si>
     <t>Mashooq Sir</t>
+  </si>
+  <si>
+    <t>JK0120304 - JK0120500</t>
+  </si>
+  <si>
+    <t>JK0120351 - JK0120500</t>
   </si>
 </sst>
 </file>
@@ -1927,9 +1933,15 @@
         <f>ROW()-2</f>
         <v>23</v>
       </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="5"/>
+      <c r="B25" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C25" s="4">
+        <v>197</v>
+      </c>
+      <c r="D25" s="5">
+        <v>46181</v>
+      </c>
       <c r="E25" s="4" t="s">
         <v>140</v>
       </c>
@@ -1954,7 +1966,9 @@
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="5"/>
-      <c r="E26" s="4"/>
+      <c r="E26" s="4" t="s">
+        <v>143</v>
+      </c>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="5"/>
@@ -1968,7 +1982,7 @@
       <c r="B27" s="4"/>
       <c r="C27" s="7">
         <f>SUM(C4:C26)</f>
-        <v>3500</v>
+        <v>3697</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0094241-A763-4A73-B42B-DB0703A57BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E25B760-D024-49E3-860A-5F15558F210D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="2" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
     <sheet name="RC" sheetId="2" r:id="rId1"/>
     <sheet name="FASTag" sheetId="4" r:id="rId2"/>
     <sheet name="Contacts" sheetId="1" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="145">
   <si>
     <t>S.No.</t>
   </si>
@@ -469,6 +468,9 @@
   </si>
   <si>
     <t>JK0120351 - JK0120500</t>
+  </si>
+  <si>
+    <t>LIYAQAT BARAMULLA</t>
   </si>
 </sst>
 </file>
@@ -3029,10 +3031,18 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="1">
+        <v>8899908693</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -3305,25 +3315,4 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F98680A-C8F8-4C2F-A264-80A3E6ED4AF5}">
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1">
-        <v>4900</v>
-      </c>
-      <c r="B1" s="3">
-        <v>46168</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E25B760-D024-49E3-860A-5F15558F210D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{695BF48B-CAC1-4F3F-B8B7-BEB6B4525A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="2" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
     <sheet name="RC" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="147">
   <si>
     <t>S.No.</t>
   </si>
@@ -471,6 +471,12 @@
   </si>
   <si>
     <t>LIYAQAT BARAMULLA</t>
+  </si>
+  <si>
+    <t>JK0111701 - JK0111745</t>
+  </si>
+  <si>
+    <t>JK0120304 - JK0120350</t>
   </si>
 </sst>
 </file>
@@ -588,26 +594,177 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
+  <dxfs count="37">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -953,6 +1110,27 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -967,58 +1145,58 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I27" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
-  <autoFilter ref="A2:I27" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I27">
-    <sortCondition ref="H2:H27"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I30" headerRowDxfId="29" dataDxfId="28">
+  <autoFilter ref="A2:I30" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I30">
+    <sortCondition ref="H2:H30"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="25">
+    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="27" totalsRowDxfId="8">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="24"/>
-    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="23"/>
-    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="20"/>
-    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="26" totalsRowDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="25" totalsRowDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="24" totalsRowDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="23" totalsRowDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="22" totalsRowDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="21" totalsRowDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="20" totalsRowDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="19" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H37" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H37" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
   <autoFilter ref="A2:H37" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="14">
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="16">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}" name="Table1" displayName="Table1" ref="A1:E31" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}" name="Table1" displayName="Table1" ref="A1:E31" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
   <autoFilter ref="A1:E31" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{1D31F252-7F75-4ACE-8E4E-970F96D5D0FB}" name="S.No." dataDxfId="4">
+    <tableColumn id="1" xr3:uid="{1D31F252-7F75-4ACE-8E4E-970F96D5D0FB}" name="S.No." dataDxfId="34">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{5C2AFA5C-CFD5-43A7-83E2-31A9A1E8AA6E}" name="NAME" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{194B191E-FB6F-4E26-9A5A-32D004AC4649}" name="DESIGNATION" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{C758F67A-2E84-46C0-BF1E-17717F5D79AC}" name="CONTACT" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{6C0116B5-2941-4E11-AD47-2ECED03BE947}" name="LOCATION" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{5C2AFA5C-CFD5-43A7-83E2-31A9A1E8AA6E}" name="NAME" dataDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{194B191E-FB6F-4E26-9A5A-32D004AC4649}" name="DESIGNATION" dataDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{C758F67A-2E84-46C0-BF1E-17717F5D79AC}" name="CONTACT" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{6C0116B5-2941-4E11-AD47-2ECED03BE947}" name="LOCATION" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1322,7 +1500,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7916C5D2-EBF3-44BC-AD33-13F607DA9441}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AA27"/>
+  <dimension ref="A1:AA30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -1392,7 +1570,7 @@
     </row>
     <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
-        <f t="shared" ref="A3:A27" si="0">ROW()-2</f>
+        <f t="shared" ref="A3:A30" si="0">ROW()-2</f>
         <v>1</v>
       </c>
       <c r="B3" s="4"/>
@@ -1971,30 +2149,98 @@
       <c r="E26" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="5"/>
+      <c r="F26" s="4">
+        <v>150</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H26" s="5">
+        <v>46181</v>
+      </c>
       <c r="I26" s="4"/>
     </row>
     <row r="27" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
-        <f t="shared" si="0"/>
+        <f>ROW()-2</f>
         <v>25</v>
       </c>
       <c r="B27" s="4"/>
-      <c r="C27" s="7">
+      <c r="C27" s="4"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="F27" s="4">
+        <v>45</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H27" s="5">
+        <v>46185</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="4">
+        <f>ROW()-2</f>
+        <v>26</v>
+      </c>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F28" s="4">
+        <v>47</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" s="5">
+        <v>46185</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="4">
+        <f>ROW()-2</f>
+        <v>27</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="4"/>
+    </row>
+    <row r="30" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="4">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B30" s="4"/>
+      <c r="C30" s="7">
         <f>SUM(C4:C26)</f>
         <v>3697</v>
       </c>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="7">
-        <f>SUM(F3:F26)</f>
-        <v>2650</v>
-      </c>
-      <c r="G27" s="4"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="7">
+        <f>SUM(F3:F28)</f>
+        <v>2892</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{695BF48B-CAC1-4F3F-B8B7-BEB6B4525A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50A9C5E6-5E0D-4950-8EE5-F25442AFB6F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="155">
   <si>
     <t>S.No.</t>
   </si>
@@ -477,6 +477,30 @@
   </si>
   <si>
     <t>JK0120304 - JK0120350</t>
+  </si>
+  <si>
+    <t>608268-006-0416825</t>
+  </si>
+  <si>
+    <t>608268-006-0416874</t>
+  </si>
+  <si>
+    <t>JK0111651 - JK0111700</t>
+  </si>
+  <si>
+    <t>Mirza Mudasir</t>
+  </si>
+  <si>
+    <t>608268-006-0416800</t>
+  </si>
+  <si>
+    <t>607529-019-0559120</t>
+  </si>
+  <si>
+    <t>607529-019-0559144</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
 </sst>
 </file>
@@ -581,13 +605,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -595,6 +619,97 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="37">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -631,7 +746,78 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -829,6 +1015,51 @@
     </dxf>
     <dxf>
       <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -924,213 +1155,6 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1145,58 +1169,58 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I30" headerRowDxfId="29" dataDxfId="28">
-  <autoFilter ref="A2:I30" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I30">
-    <sortCondition ref="H2:H30"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I31" headerRowDxfId="26" dataDxfId="25">
+  <autoFilter ref="A2:I31" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I31">
+    <sortCondition ref="H2:H31"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="27" totalsRowDxfId="8">
+    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="24" totalsRowDxfId="23">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="26" totalsRowDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="25" totalsRowDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="24" totalsRowDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="23" totalsRowDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="22" totalsRowDxfId="3"/>
-    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="21" totalsRowDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="20" totalsRowDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="19" totalsRowDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="22" totalsRowDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="20" totalsRowDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="18" totalsRowDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="16" totalsRowDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="14" totalsRowDxfId="13"/>
+    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="12" totalsRowDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="10" totalsRowDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="8" totalsRowDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H37" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
-  <autoFilter ref="A2:H37" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H39" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
+  <autoFilter ref="A2:H39" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="16">
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="34">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="32"/>
+    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="30"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="29"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}" name="Table1" displayName="Table1" ref="A1:E31" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}" name="Table1" displayName="Table1" ref="A1:E31" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A1:E31" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{1D31F252-7F75-4ACE-8E4E-970F96D5D0FB}" name="S.No." dataDxfId="34">
+    <tableColumn id="1" xr3:uid="{1D31F252-7F75-4ACE-8E4E-970F96D5D0FB}" name="S.No." dataDxfId="4">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{5C2AFA5C-CFD5-43A7-83E2-31A9A1E8AA6E}" name="NAME" dataDxfId="33"/>
-    <tableColumn id="3" xr3:uid="{194B191E-FB6F-4E26-9A5A-32D004AC4649}" name="DESIGNATION" dataDxfId="32"/>
-    <tableColumn id="6" xr3:uid="{C758F67A-2E84-46C0-BF1E-17717F5D79AC}" name="CONTACT" dataDxfId="31"/>
-    <tableColumn id="4" xr3:uid="{6C0116B5-2941-4E11-AD47-2ECED03BE947}" name="LOCATION" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{5C2AFA5C-CFD5-43A7-83E2-31A9A1E8AA6E}" name="NAME" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{194B191E-FB6F-4E26-9A5A-32D004AC4649}" name="DESIGNATION" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{C758F67A-2E84-46C0-BF1E-17717F5D79AC}" name="CONTACT" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{6C0116B5-2941-4E11-AD47-2ECED03BE947}" name="LOCATION" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1500,7 +1524,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7916C5D2-EBF3-44BC-AD33-13F607DA9441}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AA30"/>
+  <dimension ref="A1:AA31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -1527,17 +1551,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -1570,7 +1594,7 @@
     </row>
     <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
-        <f t="shared" ref="A3:A30" si="0">ROW()-2</f>
+        <f t="shared" ref="A3:A31" si="0">ROW()-2</f>
         <v>1</v>
       </c>
       <c r="B3" s="4"/>
@@ -2032,7 +2056,7 @@
     </row>
     <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" ref="A22:A30" si="2">ROW()-2</f>
         <v>20</v>
       </c>
       <c r="B22" s="4" t="s">
@@ -2062,7 +2086,7 @@
     </row>
     <row r="23" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="B23" s="4"/>
@@ -2086,7 +2110,7 @@
     </row>
     <row r="24" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
       <c r="B24" s="4"/>
@@ -2110,7 +2134,7 @@
     </row>
     <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>23</v>
       </c>
       <c r="B25" s="4" t="s">
@@ -2147,56 +2171,56 @@
       <c r="C26" s="4"/>
       <c r="D26" s="5"/>
       <c r="E26" s="4" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="F26" s="4">
+        <v>50</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" s="5">
+        <v>46176</v>
+      </c>
+      <c r="I26" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="G26" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H26" s="5">
-        <v>46181</v>
-      </c>
-      <c r="I26" s="4"/>
     </row>
     <row r="27" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>25</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
       <c r="D27" s="5"/>
       <c r="E27" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F27" s="4">
-        <v>45</v>
+        <v>150</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="H27" s="5">
-        <v>46185</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>129</v>
-      </c>
+        <v>46181</v>
+      </c>
+      <c r="I27" s="4"/>
     </row>
     <row r="28" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>26</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
       <c r="D28" s="5"/>
       <c r="E28" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F28" s="4">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>16</v>
@@ -2210,37 +2234,65 @@
     </row>
     <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>27</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
       <c r="D29" s="5"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="4"/>
+      <c r="E29" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F29" s="4">
+        <v>47</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H29" s="5">
+        <v>46185</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="30" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>28</v>
       </c>
       <c r="B30" s="4"/>
-      <c r="C30" s="7">
-        <f>SUM(C4:C26)</f>
-        <v>3697</v>
-      </c>
-      <c r="D30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="5"/>
       <c r="E30" s="4"/>
-      <c r="F30" s="7">
-        <f>SUM(F3:F28)</f>
-        <v>2892</v>
-      </c>
+      <c r="F30" s="4"/>
       <c r="G30" s="4"/>
       <c r="H30" s="5"/>
       <c r="I30" s="4"/>
+    </row>
+    <row r="31" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="4">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="C31" s="7">
+        <f>SUM(C4:C27)</f>
+        <v>3697</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="F31" s="7">
+        <f>SUM(F3:F29)</f>
+        <v>2942</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2257,7 +2309,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56B532C1-7F8B-4592-901A-51A1E632DC96}">
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr defaultColWidth="37.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2268,16 +2320,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -2808,7 +2860,7 @@
     </row>
     <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
-        <f t="shared" ref="A22:A37" si="1">ROW()-2</f>
+        <f t="shared" ref="A22:A39" si="1">ROW()-2</f>
         <v>20</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -3139,45 +3191,118 @@
     </row>
     <row r="35" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
-        <f t="shared" si="1"/>
+        <f>ROW()-2</f>
         <v>33</v>
       </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
+      <c r="B35" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F35" s="4">
+        <v>25</v>
+      </c>
+      <c r="G35" s="5">
+        <v>46176</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="36" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
-        <f t="shared" si="1"/>
+        <f>ROW()-2</f>
         <v>34</v>
       </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
+      <c r="B36" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F36" s="4">
+        <v>25</v>
+      </c>
+      <c r="G36" s="5">
+        <v>46176</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C38" s="8"/>
+      <c r="B37" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37" s="4">
+        <v>50</v>
+      </c>
+      <c r="G37" s="5">
+        <v>46186</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="4">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+    </row>
+    <row r="39" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="4">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="F39" s="7">
+        <f>SUM(F3:F37)</f>
+        <v>2376</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C40" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50A9C5E6-5E0D-4950-8EE5-F25442AFB6F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74380EE0-DC64-45EE-A85D-6FBBACF02BEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
     <sheet name="RC" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="160">
   <si>
     <t>S.No.</t>
   </si>
@@ -501,6 +501,21 @@
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>608268-006-0416875</t>
+  </si>
+  <si>
+    <t>608268-006-0416899</t>
+  </si>
+  <si>
+    <t>akhlaq</t>
+  </si>
+  <si>
+    <t>607529-019-0559168</t>
+  </si>
+  <si>
+    <t>607529-019-0559149</t>
   </si>
 </sst>
 </file>
@@ -605,13 +620,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -638,6 +653,163 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -998,163 +1170,6 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1169,42 +1184,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I31" headerRowDxfId="26" dataDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I31" headerRowDxfId="36" dataDxfId="35">
   <autoFilter ref="A2:I31" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I31">
     <sortCondition ref="H2:H31"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="24" totalsRowDxfId="23">
+    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="34" totalsRowDxfId="33">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="22" totalsRowDxfId="21"/>
-    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="20" totalsRowDxfId="19"/>
-    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="18" totalsRowDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="16" totalsRowDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="14" totalsRowDxfId="13"/>
-    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="12" totalsRowDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="10" totalsRowDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="8" totalsRowDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="32" totalsRowDxfId="31"/>
+    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="30" totalsRowDxfId="29"/>
+    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="28" totalsRowDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="26" totalsRowDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="24" totalsRowDxfId="23"/>
+    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="22" totalsRowDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="20" totalsRowDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="18" totalsRowDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H39" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
-  <autoFilter ref="A2:H39" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H42" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A2:H42" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="34">
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="14">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="33"/>
-    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="32"/>
-    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="31"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="30"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="29"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1551,17 +1566,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -2309,7 +2324,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56B532C1-7F8B-4592-901A-51A1E632DC96}">
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr defaultColWidth="37.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2320,16 +2335,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -2860,7 +2875,7 @@
     </row>
     <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
-        <f t="shared" ref="A22:A39" si="1">ROW()-2</f>
+        <f t="shared" ref="A22:A42" si="1">ROW()-2</f>
         <v>20</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -3275,34 +3290,101 @@
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
+      <c r="B38" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F38" s="4">
+        <v>25</v>
+      </c>
+      <c r="G38" s="5">
+        <v>46188</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="39" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
+        <f>ROW()-2</f>
+        <v>37</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F39" s="4">
+        <v>20</v>
+      </c>
+      <c r="G39" s="5">
+        <v>46188</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="4">
+        <f>ROW()-2</f>
+        <v>38</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="4"/>
+    </row>
+    <row r="41" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="4">
+        <f>ROW()-2</f>
+        <v>39</v>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="4"/>
+    </row>
+    <row r="42" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="4">
         <f t="shared" si="1"/>
-        <v>37</v>
-      </c>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="F39" s="7">
-        <f>SUM(F3:F37)</f>
-        <v>2376</v>
-      </c>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C40" s="8"/>
+      <c r="F42" s="7">
+        <f>SUM(F3:F39)</f>
+        <v>2421</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C43" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74380EE0-DC64-45EE-A85D-6FBBACF02BEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA978F7E-A199-4FE0-95F9-DE19FC8BC8F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
     <sheet name="RC" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="161">
   <si>
     <t>S.No.</t>
   </si>
@@ -516,6 +516,9 @@
   </si>
   <si>
     <t>607529-019-0559149</t>
+  </si>
+  <si>
+    <t>334001 - 334750</t>
   </si>
 </sst>
 </file>
@@ -620,13 +623,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -653,163 +656,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1170,6 +1016,163 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1184,42 +1187,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I31" headerRowDxfId="36" dataDxfId="35">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I31" headerRowDxfId="26" dataDxfId="25">
   <autoFilter ref="A2:I31" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I31">
     <sortCondition ref="H2:H31"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="34" totalsRowDxfId="33">
+    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="24" totalsRowDxfId="23">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="32" totalsRowDxfId="31"/>
-    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="30" totalsRowDxfId="29"/>
-    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="28" totalsRowDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="26" totalsRowDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="24" totalsRowDxfId="23"/>
-    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="22" totalsRowDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="20" totalsRowDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="18" totalsRowDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="22" totalsRowDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="20" totalsRowDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="18" totalsRowDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="16" totalsRowDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="14" totalsRowDxfId="13"/>
+    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="12" totalsRowDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="10" totalsRowDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="8" totalsRowDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H42" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H42" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
   <autoFilter ref="A2:H42" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="14">
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="34">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="32"/>
+    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="30"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="29"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1566,17 +1569,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -2252,9 +2255,15 @@
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="5"/>
+      <c r="B29" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C29" s="4">
+        <v>750</v>
+      </c>
+      <c r="D29" s="5">
+        <v>46189</v>
+      </c>
       <c r="E29" s="4" t="s">
         <v>146</v>
       </c>
@@ -2294,8 +2303,8 @@
         <v>154</v>
       </c>
       <c r="C31" s="7">
-        <f>SUM(C4:C27)</f>
-        <v>3697</v>
+        <f>SUM(C4:C30)</f>
+        <v>4447</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="7" t="s">
@@ -2335,16 +2344,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA978F7E-A199-4FE0-95F9-DE19FC8BC8F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6796503E-3359-400A-AE78-63CA56821BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="163">
   <si>
     <t>S.No.</t>
   </si>
@@ -519,6 +519,12 @@
   </si>
   <si>
     <t>334001 - 334750</t>
+  </si>
+  <si>
+    <t>334001 - 334250</t>
+  </si>
+  <si>
+    <t>Akhlaq</t>
   </si>
 </sst>
 </file>
@@ -623,13 +629,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -656,6 +662,163 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1016,163 +1179,6 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1187,42 +1193,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I31" headerRowDxfId="26" dataDxfId="25">
-  <autoFilter ref="A2:I31" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I31">
-    <sortCondition ref="H2:H31"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I34" headerRowDxfId="36" dataDxfId="35">
+  <autoFilter ref="A2:I34" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I34">
+    <sortCondition ref="H2:H34"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="24" totalsRowDxfId="23">
+    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="34" totalsRowDxfId="33">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="22" totalsRowDxfId="21"/>
-    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="20" totalsRowDxfId="19"/>
-    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="18" totalsRowDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="16" totalsRowDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="14" totalsRowDxfId="13"/>
-    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="12" totalsRowDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="10" totalsRowDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="8" totalsRowDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="32" totalsRowDxfId="31"/>
+    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="30" totalsRowDxfId="29"/>
+    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="28" totalsRowDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="26" totalsRowDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="24" totalsRowDxfId="23"/>
+    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="22" totalsRowDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="20" totalsRowDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="18" totalsRowDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H42" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H42" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
   <autoFilter ref="A2:H42" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="34">
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="14">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="33"/>
-    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="32"/>
-    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="31"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="30"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="29"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1542,7 +1548,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7916C5D2-EBF3-44BC-AD33-13F607DA9441}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AA31"/>
+  <dimension ref="A1:AA34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -1569,17 +1575,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -1612,7 +1618,7 @@
     </row>
     <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
-        <f t="shared" ref="A3:A31" si="0">ROW()-2</f>
+        <f t="shared" ref="A3:A34" si="0">ROW()-2</f>
         <v>1</v>
       </c>
       <c r="B3" s="4"/>
@@ -2288,35 +2294,87 @@
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
       <c r="D30" s="5"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="5"/>
-      <c r="I30" s="4"/>
+      <c r="E30" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="F30" s="4">
+        <v>250</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H30" s="5">
+        <v>46191</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="31" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
-        <f t="shared" si="0"/>
+        <f>ROW()-2</f>
         <v>29</v>
       </c>
-      <c r="B31" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="C31" s="7">
-        <f>SUM(C4:C30)</f>
-        <v>4447</v>
-      </c>
-      <c r="D31" s="4"/>
-      <c r="E31" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="F31" s="7">
-        <f>SUM(F3:F29)</f>
-        <v>2942</v>
-      </c>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
       <c r="G31" s="4"/>
       <c r="H31" s="5"/>
       <c r="I31" s="4"/>
+    </row>
+    <row r="32" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="4">
+        <f>ROW()-2</f>
+        <v>30</v>
+      </c>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="4"/>
+    </row>
+    <row r="33" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="4">
+        <f>ROW()-2</f>
+        <v>31</v>
+      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="4"/>
+    </row>
+    <row r="34" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="4">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="C34" s="7">
+        <f>SUM(C4:C30)</f>
+        <v>4447</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="F34" s="7">
+        <f>SUM(F3:F31)</f>
+        <v>3192</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2344,16 +2402,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6796503E-3359-400A-AE78-63CA56821BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CED74C44-958A-4CF1-9F3C-57AF0435FF1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
     <sheet name="RC" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="167">
   <si>
     <t>S.No.</t>
   </si>
@@ -525,6 +525,18 @@
   </si>
   <si>
     <t>Akhlaq</t>
+  </si>
+  <si>
+    <t>608268-006-0416868</t>
+  </si>
+  <si>
+    <t>608268-006-0416869</t>
+  </si>
+  <si>
+    <t>607529-019-0559145</t>
+  </si>
+  <si>
+    <t>607529-019-0559148</t>
   </si>
 </sst>
 </file>
@@ -1216,8 +1228,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H42" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="A2:H42" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H45" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A2:H45" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="14">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
@@ -2391,7 +2403,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56B532C1-7F8B-4592-901A-51A1E632DC96}">
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr defaultColWidth="37.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2942,7 +2954,7 @@
     </row>
     <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
-        <f t="shared" ref="A22:A42" si="1">ROW()-2</f>
+        <f t="shared" ref="A22:A45" si="1">ROW()-2</f>
         <v>20</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -3334,7 +3346,7 @@
         <v>147</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>131</v>
@@ -3343,7 +3355,7 @@
         <v>17</v>
       </c>
       <c r="F37" s="4">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G37" s="5">
         <v>46186</v>
@@ -3411,12 +3423,24 @@
         <f>ROW()-2</f>
         <v>38</v>
       </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="5"/>
+      <c r="B40" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F40" s="4">
+        <v>6</v>
+      </c>
+      <c r="G40" s="5">
+        <v>46200</v>
+      </c>
       <c r="H40" s="4"/>
     </row>
     <row r="41" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -3424,34 +3448,85 @@
         <f>ROW()-2</f>
         <v>39</v>
       </c>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="5"/>
+      <c r="B41" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F41" s="4">
+        <v>4</v>
+      </c>
+      <c r="G41" s="5">
+        <v>46200</v>
+      </c>
       <c r="H41" s="4"/>
     </row>
     <row r="42" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
-        <f t="shared" si="1"/>
+        <f>ROW()-2</f>
         <v>40</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
-      <c r="E42" s="7" t="s">
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="4"/>
+    </row>
+    <row r="43" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="4">
+        <f>ROW()-2</f>
+        <v>41</v>
+      </c>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="4"/>
+    </row>
+    <row r="44" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="4">
+        <f>ROW()-2</f>
+        <v>42</v>
+      </c>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="4"/>
+    </row>
+    <row r="45" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A45" s="4">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="F42" s="7">
-        <f>SUM(F3:F39)</f>
-        <v>2421</v>
-      </c>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C43" s="8"/>
+      <c r="F45" s="7">
+        <f>SUM(F3:F41)</f>
+        <v>2425</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C46" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CED74C44-958A-4CF1-9F3C-57AF0435FF1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C530A516-9A56-4EE5-A079-E4AD33803BF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
     <sheet name="RC" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="165">
   <si>
     <t>S.No.</t>
   </si>
@@ -482,9 +482,6 @@
     <t>608268-006-0416825</t>
   </si>
   <si>
-    <t>608268-006-0416874</t>
-  </si>
-  <si>
     <t>JK0111651 - JK0111700</t>
   </si>
   <si>
@@ -530,13 +527,10 @@
     <t>608268-006-0416868</t>
   </si>
   <si>
-    <t>608268-006-0416869</t>
-  </si>
-  <si>
-    <t>607529-019-0559145</t>
-  </si>
-  <si>
-    <t>607529-019-0559148</t>
+    <t>334500 - 334550</t>
+  </si>
+  <si>
+    <t>self</t>
   </si>
 </sst>
 </file>
@@ -641,13 +635,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -674,163 +668,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1191,6 +1028,163 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1205,42 +1199,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I34" headerRowDxfId="36" dataDxfId="35">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I34" headerRowDxfId="26" dataDxfId="25">
   <autoFilter ref="A2:I34" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I34">
     <sortCondition ref="H2:H34"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="34" totalsRowDxfId="33">
+    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="24" totalsRowDxfId="23">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="32" totalsRowDxfId="31"/>
-    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="30" totalsRowDxfId="29"/>
-    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="28" totalsRowDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="26" totalsRowDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="24" totalsRowDxfId="23"/>
-    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="22" totalsRowDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="20" totalsRowDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="18" totalsRowDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="22" totalsRowDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="20" totalsRowDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="18" totalsRowDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="16" totalsRowDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="14" totalsRowDxfId="13"/>
+    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="12" totalsRowDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="10" totalsRowDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="8" totalsRowDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H45" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H45" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
   <autoFilter ref="A2:H45" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="14">
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="34">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="32"/>
+    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="30"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="29"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1587,17 +1581,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -2207,7 +2201,7 @@
       <c r="C26" s="4"/>
       <c r="D26" s="5"/>
       <c r="E26" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F26" s="4">
         <v>50</v>
@@ -2219,7 +2213,7 @@
         <v>46176</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2274,7 +2268,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C29" s="4">
         <v>750</v>
@@ -2307,7 +2301,7 @@
       <c r="C30" s="4"/>
       <c r="D30" s="5"/>
       <c r="E30" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F30" s="4">
         <v>250</v>
@@ -2319,7 +2313,7 @@
         <v>46191</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2330,11 +2324,21 @@
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
       <c r="D31" s="5"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="4"/>
+      <c r="E31" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="F31" s="4">
+        <v>50</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H31" s="5">
+        <v>46202</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="32" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
@@ -2370,7 +2374,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C34" s="7">
         <f>SUM(C4:C30)</f>
@@ -2378,11 +2382,11 @@
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F34" s="7">
         <f>SUM(F3:F31)</f>
-        <v>3192</v>
+        <v>3242</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="5"/>
@@ -2414,16 +2418,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -3289,10 +3293,10 @@
         <v>33</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>131</v>
@@ -3307,7 +3311,7 @@
         <v>46176</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -3316,10 +3320,10 @@
         <v>34</v>
       </c>
       <c r="B36" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C36" s="6" t="s">
         <v>152</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>153</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>131</v>
@@ -3334,7 +3338,7 @@
         <v>46176</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -3346,7 +3350,7 @@
         <v>147</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>131</v>
@@ -3370,10 +3374,10 @@
         <v>36</v>
       </c>
       <c r="B38" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C38" s="6" t="s">
         <v>155</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>156</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>131</v>
@@ -3388,19 +3392,19 @@
         <v>46188</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" ref="A39:A44" si="2">ROW()-2</f>
         <v>37</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>131</v>
@@ -3415,62 +3419,38 @@
         <v>46188</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>38</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F40" s="4">
-        <v>6</v>
-      </c>
-      <c r="G40" s="5">
-        <v>46200</v>
-      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="5"/>
       <c r="H40" s="4"/>
     </row>
     <row r="41" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>39</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F41" s="4">
-        <v>4</v>
-      </c>
-      <c r="G41" s="5">
-        <v>46200</v>
-      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="5"/>
       <c r="H41" s="4"/>
     </row>
     <row r="42" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
       <c r="B42" s="6"/>
@@ -3483,7 +3463,7 @@
     </row>
     <row r="43" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>41</v>
       </c>
       <c r="B43" s="6"/>
@@ -3496,7 +3476,7 @@
     </row>
     <row r="44" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>42</v>
       </c>
       <c r="B44" s="6"/>
@@ -3516,11 +3496,11 @@
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
       <c r="E45" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F45" s="7">
         <f>SUM(F3:F41)</f>
-        <v>2425</v>
+        <v>2415</v>
       </c>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C530A516-9A56-4EE5-A079-E4AD33803BF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8463DD56-1334-4FC8-96A1-25932C5E4E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="189">
   <si>
     <t>S.No.</t>
   </si>
@@ -531,6 +531,78 @@
   </si>
   <si>
     <t>self</t>
+  </si>
+  <si>
+    <t>608268-005-0006891</t>
+  </si>
+  <si>
+    <t>608268-005-0006917</t>
+  </si>
+  <si>
+    <t>608268-005-0006868</t>
+  </si>
+  <si>
+    <t>608268-005-0006869</t>
+  </si>
+  <si>
+    <t>tfr</t>
+  </si>
+  <si>
+    <t>Send from other Dealer</t>
+  </si>
+  <si>
+    <t>608268-003-0040519</t>
+  </si>
+  <si>
+    <t>608268-003-0040718</t>
+  </si>
+  <si>
+    <t>Order 7</t>
+  </si>
+  <si>
+    <t>607529-020-0259158</t>
+  </si>
+  <si>
+    <t>607529-020-0259182</t>
+  </si>
+  <si>
+    <t>608268-003-0040719</t>
+  </si>
+  <si>
+    <t>607529-020-0259133</t>
+  </si>
+  <si>
+    <t>607529-020-0259148</t>
+  </si>
+  <si>
+    <t>608268-003-0040899</t>
+  </si>
+  <si>
+    <t>608268-003-0040478</t>
+  </si>
+  <si>
+    <t>608268-003-0040517</t>
+  </si>
+  <si>
+    <t>608268-003-0040905</t>
+  </si>
+  <si>
+    <t>608268-003-0040928</t>
+  </si>
+  <si>
+    <t>607529-020-0259149</t>
+  </si>
+  <si>
+    <t>607529-020-0259157</t>
+  </si>
+  <si>
+    <t>607529-020-0258829</t>
+  </si>
+  <si>
+    <t>607529-020-0258830</t>
+  </si>
+  <si>
+    <t>334251 - 334451</t>
   </si>
 </sst>
 </file>
@@ -1222,8 +1294,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H45" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
-  <autoFilter ref="A2:H45" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H53" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
+  <autoFilter ref="A2:H53" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="34">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
@@ -2348,11 +2420,21 @@
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
       <c r="D32" s="5"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="5"/>
-      <c r="I32" s="4"/>
+      <c r="E32" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="F32" s="4">
+        <v>200</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H32" s="5">
+        <v>46205</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="33" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
@@ -2385,8 +2467,8 @@
         <v>153</v>
       </c>
       <c r="F34" s="7">
-        <f>SUM(F3:F31)</f>
-        <v>3242</v>
+        <f>SUM(F3:F32)</f>
+        <v>3442</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="5"/>
@@ -2407,7 +2489,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56B532C1-7F8B-4592-901A-51A1E632DC96}">
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr defaultColWidth="37.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2958,7 +3040,7 @@
     </row>
     <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
-        <f t="shared" ref="A22:A45" si="1">ROW()-2</f>
+        <f t="shared" ref="A22:A53" si="1">ROW()-2</f>
         <v>20</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -3427,38 +3509,78 @@
         <f t="shared" si="2"/>
         <v>38</v>
       </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="4"/>
+      <c r="B40" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F40" s="4">
+        <v>27</v>
+      </c>
+      <c r="G40" s="5">
+        <v>46196</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="41" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <f t="shared" si="2"/>
         <v>39</v>
       </c>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="4"/>
+      <c r="B41" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F41" s="4">
+        <v>2</v>
+      </c>
+      <c r="G41" s="5">
+        <v>46196</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="42" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <f t="shared" si="2"/>
         <v>40</v>
       </c>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="5"/>
+      <c r="B42" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F42" s="4">
+        <v>200</v>
+      </c>
+      <c r="G42" s="5">
+        <v>46205</v>
+      </c>
       <c r="H42" s="4"/>
     </row>
     <row r="43" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -3466,12 +3588,24 @@
         <f t="shared" si="2"/>
         <v>41</v>
       </c>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="5"/>
+      <c r="B43" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F43" s="4">
+        <v>25</v>
+      </c>
+      <c r="G43" s="5">
+        <v>46205</v>
+      </c>
       <c r="H43" s="4"/>
     </row>
     <row r="44" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -3479,34 +3613,210 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="B44" s="6"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="5"/>
+      <c r="B44" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F44" s="4">
+        <v>185</v>
+      </c>
+      <c r="G44" s="5">
+        <v>46205</v>
+      </c>
       <c r="H44" s="4"/>
     </row>
     <row r="45" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
+        <f t="shared" ref="A45:A52" si="3">ROW()-2</f>
+        <v>43</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F45" s="4">
+        <v>15</v>
+      </c>
+      <c r="G45" s="5">
+        <v>46205</v>
+      </c>
+      <c r="H45" s="4"/>
+    </row>
+    <row r="46" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A46" s="4">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F46" s="4">
+        <v>41</v>
+      </c>
+      <c r="G46" s="5">
+        <v>46205</v>
+      </c>
+      <c r="H46" s="4"/>
+    </row>
+    <row r="47" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A47" s="4">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F47" s="4">
+        <v>24</v>
+      </c>
+      <c r="G47" s="5">
+        <v>46205</v>
+      </c>
+      <c r="H47" s="4"/>
+    </row>
+    <row r="48" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A48" s="4">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F48" s="4">
+        <v>8</v>
+      </c>
+      <c r="G48" s="5">
+        <v>46205</v>
+      </c>
+      <c r="H48" s="4"/>
+    </row>
+    <row r="49" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A49" s="4">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F49" s="4">
+        <v>2</v>
+      </c>
+      <c r="G49" s="5">
+        <v>46205</v>
+      </c>
+      <c r="H49" s="4"/>
+    </row>
+    <row r="50" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A50" s="4">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="4"/>
+    </row>
+    <row r="51" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A51" s="4">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="4"/>
+    </row>
+    <row r="52" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A52" s="4">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="B52" s="6"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="4"/>
+    </row>
+    <row r="53" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A53" s="4">
         <f t="shared" si="1"/>
-        <v>43</v>
-      </c>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B53" s="6"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="F45" s="7">
-        <f>SUM(F3:F41)</f>
-        <v>2415</v>
-      </c>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C46" s="8"/>
+      <c r="F53" s="7">
+        <f>SUM(F3:F49)</f>
+        <v>2944</v>
+      </c>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C54" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8463DD56-1334-4FC8-96A1-25932C5E4E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD8300B3-B03B-4C73-AC68-3287A4B9C94E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="2" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
     <sheet name="RC" sheetId="2" r:id="rId1"/>
     <sheet name="FASTag" sheetId="4" r:id="rId2"/>
-    <sheet name="Contacts" sheetId="1" r:id="rId3"/>
+    <sheet name="FASTag Stock" sheetId="5" r:id="rId3"/>
+    <sheet name="Contacts" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="198">
   <si>
     <t>S.No.</t>
   </si>
@@ -603,13 +604,40 @@
   </si>
   <si>
     <t>334251 - 334451</t>
+  </si>
+  <si>
+    <t>Opening Stock</t>
+  </si>
+  <si>
+    <t>Closing Stock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Activated </t>
+  </si>
+  <si>
+    <t>Order Received</t>
+  </si>
+  <si>
+    <t>Order Shift</t>
+  </si>
+  <si>
+    <t>ARENA SRINAGAR</t>
+  </si>
+  <si>
+    <t>ANANTNAG</t>
+  </si>
+  <si>
+    <t>NEXA SRINAGAR</t>
+  </si>
+  <si>
+    <t>Tags Utilised</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -660,8 +688,21 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Bahnschrift"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="48"/>
+      <color theme="1"/>
+      <name val="Bahnschrift"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -671,6 +712,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -687,7 +734,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -707,7 +754,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -716,30 +769,190 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="37">
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
+  <dxfs count="67">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1101,160 +1314,96 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
@@ -1271,48 +1420,99 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I34" headerRowDxfId="26" dataDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I34" headerRowDxfId="36" dataDxfId="35">
   <autoFilter ref="A2:I34" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I34">
     <sortCondition ref="H2:H34"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="24" totalsRowDxfId="23">
+    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="34" totalsRowDxfId="33">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="22" totalsRowDxfId="21"/>
-    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="20" totalsRowDxfId="19"/>
-    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="18" totalsRowDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="16" totalsRowDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="14" totalsRowDxfId="13"/>
-    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="12" totalsRowDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="10" totalsRowDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="8" totalsRowDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="32" totalsRowDxfId="31"/>
+    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="30" totalsRowDxfId="29"/>
+    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="28" totalsRowDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="26" totalsRowDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="24" totalsRowDxfId="23"/>
+    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="22" totalsRowDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="20" totalsRowDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="18" totalsRowDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H53" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H53" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
   <autoFilter ref="A2:H53" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="34">
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="14">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="33"/>
-    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="32"/>
-    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="31"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="30"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="29"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6B19EA76-FE33-4EDA-96A5-FB5AB6842877}" name="Arena" displayName="Arena" ref="A2:H18" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65">
+  <autoFilter ref="A2:H18" xr:uid="{6B19EA76-FE33-4EDA-96A5-FB5AB6842877}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{205B1937-36C2-4A79-ADEE-67B939CC6350}" name="Dated" dataDxfId="64"/>
+    <tableColumn id="2" xr3:uid="{FC4A4194-EC0B-4123-AA2A-047F801393F9}" name="Opening Stock" dataDxfId="63"/>
+    <tableColumn id="3" xr3:uid="{B9BA259A-905C-4F48-9EF9-1D3A771CDF0D}" name="Activated " dataDxfId="62"/>
+    <tableColumn id="4" xr3:uid="{6B90C7CC-E86F-4D69-8B7A-1A5106E7671C}" name="Order Received" dataDxfId="61"/>
+    <tableColumn id="5" xr3:uid="{52A7379A-F21F-428A-AC09-8DDD0314565C}" name="Closing Stock" dataDxfId="60"/>
+    <tableColumn id="6" xr3:uid="{2D5B9A13-3A69-4B89-9385-0118C6E503AA}" name="Order Shift" dataDxfId="59"/>
+    <tableColumn id="8" xr3:uid="{7A6C60CE-7C65-462E-936E-BEBFB199EEEA}" name="Tags Utilised" dataDxfId="58"/>
+    <tableColumn id="7" xr3:uid="{3B8303E5-7229-40E9-B595-7FD79C903530}" name="Remarks" dataDxfId="57"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F5BFC800-1EAF-4967-B61B-9184746587CB}" name="Table46" displayName="Table46" ref="K2:R18" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
+  <autoFilter ref="K2:R18" xr:uid="{F5BFC800-1EAF-4967-B61B-9184746587CB}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{EE8E16B4-53D2-438F-BDFF-22C4417244D7}" name="Dated" dataDxfId="54"/>
+    <tableColumn id="2" xr3:uid="{4ED05A2F-B065-41B5-B1FC-755636A3BA21}" name="Opening Stock" dataDxfId="53"/>
+    <tableColumn id="3" xr3:uid="{57285520-2C9E-4091-953B-03FBAFD5574E}" name="Activated " dataDxfId="52"/>
+    <tableColumn id="4" xr3:uid="{26808A5F-3F95-45FD-91EE-BFADD8DB9C6A}" name="Order Received" dataDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{A95C8869-A6DD-4A00-8782-9276336A5840}" name="Closing Stock" dataDxfId="50"/>
+    <tableColumn id="6" xr3:uid="{F683981E-ECFB-47E9-88E2-60A6694123E4}" name="Order Shift" dataDxfId="49"/>
+    <tableColumn id="9" xr3:uid="{4862D1DC-BC5E-473F-B5F4-E4EDDBFBAEA8}" name="Tags Utilised" dataDxfId="48"/>
+    <tableColumn id="7" xr3:uid="{59E58FF5-FBE8-4EA3-8C27-FDBB5D8347D8}" name="Remarks" dataDxfId="47"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{C16732A9-DC14-4F77-B928-B2EA21A17DE3}" name="Table467" displayName="Table467" ref="U2:AB18" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45">
+  <autoFilter ref="U2:AB18" xr:uid="{C16732A9-DC14-4F77-B928-B2EA21A17DE3}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{863EE3B3-D99D-40AA-9A97-8B87E908A619}" name="Dated" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{7EBF6231-0A46-4C5A-8F44-07F6E8D58BD8}" name="Opening Stock" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{7302BA2D-23E3-4355-A732-13358849E25E}" name="Activated " dataDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{C353FB1F-2706-4110-9F4C-867233885BE5}" name="Order Received" dataDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{1C608AFD-D32B-49BA-B588-B75035E109DA}" name="Closing Stock" dataDxfId="40"/>
+    <tableColumn id="6" xr3:uid="{FF5D1709-231D-4967-81E2-C12033E82768}" name="Order Shift" dataDxfId="39"/>
+    <tableColumn id="9" xr3:uid="{ABB4B85D-962C-4A1F-8D08-7E53D211DBB3}" name="Tags Utilised" dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{918E2430-DED3-4A6B-A818-8CD1C7AAFAEA}" name="Remarks" dataDxfId="37"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}" name="Table1" displayName="Table1" ref="A1:E31" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A1:E31" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}"/>
   <tableColumns count="5">
@@ -1653,17 +1853,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -2500,16 +2700,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -3830,6 +4030,606 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBDF3EDB-09FD-4268-A85C-2BE01E602CBE}">
+  <dimension ref="A1:AB18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" customWidth="1"/>
+    <col min="6" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="26" customWidth="1"/>
+    <col min="11" max="11" width="15" customWidth="1"/>
+    <col min="12" max="12" width="19.140625" customWidth="1"/>
+    <col min="13" max="13" width="17.85546875" customWidth="1"/>
+    <col min="14" max="14" width="19.140625" customWidth="1"/>
+    <col min="15" max="15" width="18.28515625" customWidth="1"/>
+    <col min="16" max="17" width="18.42578125" customWidth="1"/>
+    <col min="18" max="18" width="21.42578125" customWidth="1"/>
+    <col min="21" max="21" width="12.85546875" customWidth="1"/>
+    <col min="22" max="22" width="19.42578125" customWidth="1"/>
+    <col min="23" max="23" width="16.28515625" customWidth="1"/>
+    <col min="24" max="24" width="20.5703125" customWidth="1"/>
+    <col min="25" max="25" width="17.7109375" customWidth="1"/>
+    <col min="26" max="26" width="18.7109375" customWidth="1"/>
+    <col min="27" max="27" width="17.42578125" customWidth="1"/>
+    <col min="28" max="28" width="22.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" ht="58.5" x14ac:dyDescent="0.7">
+      <c r="A1" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="K1" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="U1" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="V1" s="10"/>
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="10"/>
+      <c r="Z1" s="10"/>
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="10"/>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A3" s="9">
+        <v>46205</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1">
+        <v>129</v>
+      </c>
+      <c r="D3" s="1">
+        <v>200</v>
+      </c>
+      <c r="E3" s="1">
+        <v>200</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1">
+        <v>129</v>
+      </c>
+      <c r="H3" s="1"/>
+      <c r="K3" s="9">
+        <v>46205</v>
+      </c>
+      <c r="L3" s="1">
+        <v>0</v>
+      </c>
+      <c r="M3" s="1">
+        <v>239</v>
+      </c>
+      <c r="N3" s="1">
+        <v>220</v>
+      </c>
+      <c r="O3" s="1">
+        <v>220</v>
+      </c>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1">
+        <v>239</v>
+      </c>
+      <c r="R3" s="1"/>
+      <c r="U3" s="9">
+        <v>46205</v>
+      </c>
+      <c r="V3" s="1">
+        <v>0</v>
+      </c>
+      <c r="W3" s="1">
+        <v>1920</v>
+      </c>
+      <c r="X3" s="1">
+        <v>75</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>75</v>
+      </c>
+      <c r="Z3" s="1"/>
+      <c r="AA3" s="1"/>
+      <c r="AB3" s="1"/>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A4" s="9"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="1"/>
+      <c r="W4" s="1"/>
+      <c r="X4" s="1"/>
+      <c r="Y4" s="1"/>
+      <c r="Z4" s="1"/>
+      <c r="AA4" s="1"/>
+      <c r="AB4" s="1"/>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A5" s="9"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="1"/>
+      <c r="W5" s="1"/>
+      <c r="X5" s="1"/>
+      <c r="Y5" s="1"/>
+      <c r="Z5" s="1"/>
+      <c r="AA5" s="1"/>
+      <c r="AB5" s="1"/>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A6" s="9"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="U6" s="9"/>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+      <c r="X6" s="1"/>
+      <c r="Y6" s="1"/>
+      <c r="Z6" s="1"/>
+      <c r="AA6" s="1"/>
+      <c r="AB6" s="1"/>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A7" s="9"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
+      <c r="X7" s="1"/>
+      <c r="Y7" s="1"/>
+      <c r="Z7" s="1"/>
+      <c r="AA7" s="1"/>
+      <c r="AB7" s="1"/>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A8" s="9"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="U8" s="9"/>
+      <c r="V8" s="1"/>
+      <c r="W8" s="1"/>
+      <c r="X8" s="1"/>
+      <c r="Y8" s="1"/>
+      <c r="Z8" s="1"/>
+      <c r="AA8" s="1"/>
+      <c r="AB8" s="1"/>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A9" s="9"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="U9" s="9"/>
+      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+      <c r="X9" s="1"/>
+      <c r="Y9" s="1"/>
+      <c r="Z9" s="1"/>
+      <c r="AA9" s="1"/>
+      <c r="AB9" s="1"/>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A10" s="9"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="U10" s="9"/>
+      <c r="V10" s="1"/>
+      <c r="W10" s="1"/>
+      <c r="X10" s="1"/>
+      <c r="Y10" s="1"/>
+      <c r="Z10" s="1"/>
+      <c r="AA10" s="1"/>
+      <c r="AB10" s="1"/>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A11" s="9"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="U11" s="9"/>
+      <c r="V11" s="1"/>
+      <c r="W11" s="1"/>
+      <c r="X11" s="1"/>
+      <c r="Y11" s="1"/>
+      <c r="Z11" s="1"/>
+      <c r="AA11" s="1"/>
+      <c r="AB11" s="1"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A12" s="9"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="U12" s="9"/>
+      <c r="V12" s="1"/>
+      <c r="W12" s="1"/>
+      <c r="X12" s="1"/>
+      <c r="Y12" s="1"/>
+      <c r="Z12" s="1"/>
+      <c r="AA12" s="1"/>
+      <c r="AB12" s="1"/>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A13" s="9"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="U13" s="9"/>
+      <c r="V13" s="1"/>
+      <c r="W13" s="1"/>
+      <c r="X13" s="1"/>
+      <c r="Y13" s="1"/>
+      <c r="Z13" s="1"/>
+      <c r="AA13" s="1"/>
+      <c r="AB13" s="1"/>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A14" s="9"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="U14" s="9"/>
+      <c r="V14" s="1"/>
+      <c r="W14" s="1"/>
+      <c r="X14" s="1"/>
+      <c r="Y14" s="1"/>
+      <c r="Z14" s="1"/>
+      <c r="AA14" s="1"/>
+      <c r="AB14" s="1"/>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A15" s="9"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="U15" s="9"/>
+      <c r="V15" s="1"/>
+      <c r="W15" s="1"/>
+      <c r="X15" s="1"/>
+      <c r="Y15" s="1"/>
+      <c r="Z15" s="1"/>
+      <c r="AA15" s="1"/>
+      <c r="AB15" s="1"/>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A16" s="9"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+      <c r="U16" s="9"/>
+      <c r="V16" s="1"/>
+      <c r="W16" s="1"/>
+      <c r="X16" s="1"/>
+      <c r="Y16" s="1"/>
+      <c r="Z16" s="1"/>
+      <c r="AA16" s="1"/>
+      <c r="AB16" s="1"/>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A17" s="9"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+      <c r="U17" s="9"/>
+      <c r="V17" s="1"/>
+      <c r="W17" s="1"/>
+      <c r="X17" s="1"/>
+      <c r="Y17" s="1"/>
+      <c r="Z17" s="1"/>
+      <c r="AA17" s="1"/>
+      <c r="AB17" s="1"/>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A18" s="9"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
+      <c r="U18" s="9"/>
+      <c r="V18" s="1"/>
+      <c r="W18" s="1"/>
+      <c r="X18" s="1"/>
+      <c r="Y18" s="1"/>
+      <c r="Z18" s="1"/>
+      <c r="AA18" s="1"/>
+      <c r="AB18" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="K1:R1"/>
+    <mergeCell ref="U1:AB1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="3">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4093ECB5-009B-4A95-948D-B5418A73B4F4}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:E31"/>

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD8300B3-B03B-4C73-AC68-3287A4B9C94E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3DB6C79-86B1-43FA-B74A-EFFE61FD7A16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="2" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
     <sheet name="RC" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="199">
   <si>
     <t>S.No.</t>
   </si>
@@ -631,6 +631,9 @@
   </si>
   <si>
     <t>Tags Utilised</t>
+  </si>
+  <si>
+    <t>334701 - 334750</t>
   </si>
 </sst>
 </file>
@@ -1420,10 +1423,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I34" headerRowDxfId="36" dataDxfId="35">
-  <autoFilter ref="A2:I34" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I34">
-    <sortCondition ref="H2:H34"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I37" headerRowDxfId="36" dataDxfId="35">
+  <autoFilter ref="A2:I37" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I37">
+    <sortCondition ref="H2:H37"/>
   </sortState>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="34" totalsRowDxfId="33">
@@ -1826,7 +1829,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7916C5D2-EBF3-44BC-AD33-13F607DA9441}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AA34"/>
+  <dimension ref="A1:AA37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -1896,7 +1899,7 @@
     </row>
     <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
-        <f t="shared" ref="A3:A34" si="0">ROW()-2</f>
+        <f t="shared" ref="A3:A37" si="0">ROW()-2</f>
         <v>1</v>
       </c>
       <c r="B3" s="4"/>
@@ -2644,35 +2647,85 @@
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="5"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="5"/>
+      <c r="E33" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F33" s="4">
+        <v>50</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H33" s="5">
+        <v>46216</v>
+      </c>
       <c r="I33" s="4"/>
     </row>
     <row r="34" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
-        <f t="shared" si="0"/>
+        <f>ROW()-2</f>
         <v>32</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="C34" s="7">
-        <f>SUM(C4:C30)</f>
-        <v>4447</v>
-      </c>
-      <c r="D34" s="4"/>
-      <c r="E34" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="F34" s="7">
-        <f>SUM(F3:F32)</f>
-        <v>3442</v>
-      </c>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
       <c r="G34" s="4"/>
       <c r="H34" s="5"/>
       <c r="I34" s="4"/>
+    </row>
+    <row r="35" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="4">
+        <f>ROW()-2</f>
+        <v>33</v>
+      </c>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="4"/>
+    </row>
+    <row r="36" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="4">
+        <f>ROW()-2</f>
+        <v>34</v>
+      </c>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="4"/>
+    </row>
+    <row r="37" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="4">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="C37" s="7">
+        <f>SUM(C4:C30)</f>
+        <v>4447</v>
+      </c>
+      <c r="D37" s="4"/>
+      <c r="E37" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="F37" s="7">
+        <f>SUM(F3:F33)</f>
+        <v>3492</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3DB6C79-86B1-43FA-B74A-EFFE61FD7A16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0B499AB-A421-4F13-98A0-D13B55AF76B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
     <sheet name="RC" sheetId="2" r:id="rId1"/>
@@ -760,12 +760,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -775,6 +769,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -793,6 +793,99 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1316,99 +1409,6 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1423,93 +1423,93 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I37" headerRowDxfId="36" dataDxfId="35">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I37" headerRowDxfId="66" dataDxfId="65">
   <autoFilter ref="A2:I37" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I37">
     <sortCondition ref="H2:H37"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="34" totalsRowDxfId="33">
+    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="64" totalsRowDxfId="63">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="32" totalsRowDxfId="31"/>
-    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="30" totalsRowDxfId="29"/>
-    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="28" totalsRowDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="26" totalsRowDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="24" totalsRowDxfId="23"/>
-    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="22" totalsRowDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="20" totalsRowDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="18" totalsRowDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="62" totalsRowDxfId="61"/>
+    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="60" totalsRowDxfId="59"/>
+    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="58" totalsRowDxfId="57"/>
+    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="56" totalsRowDxfId="55"/>
+    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="54" totalsRowDxfId="53"/>
+    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="52" totalsRowDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="50" totalsRowDxfId="49"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="48" totalsRowDxfId="47"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H53" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H53" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45">
   <autoFilter ref="A2:H53" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="14">
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="44">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="42"/>
+    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="39"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="37"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6B19EA76-FE33-4EDA-96A5-FB5AB6842877}" name="Arena" displayName="Arena" ref="A2:H18" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6B19EA76-FE33-4EDA-96A5-FB5AB6842877}" name="Arena" displayName="Arena" ref="A2:H18" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
   <autoFilter ref="A2:H18" xr:uid="{6B19EA76-FE33-4EDA-96A5-FB5AB6842877}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{205B1937-36C2-4A79-ADEE-67B939CC6350}" name="Dated" dataDxfId="64"/>
-    <tableColumn id="2" xr3:uid="{FC4A4194-EC0B-4123-AA2A-047F801393F9}" name="Opening Stock" dataDxfId="63"/>
-    <tableColumn id="3" xr3:uid="{B9BA259A-905C-4F48-9EF9-1D3A771CDF0D}" name="Activated " dataDxfId="62"/>
-    <tableColumn id="4" xr3:uid="{6B90C7CC-E86F-4D69-8B7A-1A5106E7671C}" name="Order Received" dataDxfId="61"/>
-    <tableColumn id="5" xr3:uid="{52A7379A-F21F-428A-AC09-8DDD0314565C}" name="Closing Stock" dataDxfId="60"/>
-    <tableColumn id="6" xr3:uid="{2D5B9A13-3A69-4B89-9385-0118C6E503AA}" name="Order Shift" dataDxfId="59"/>
-    <tableColumn id="8" xr3:uid="{7A6C60CE-7C65-462E-936E-BEBFB199EEEA}" name="Tags Utilised" dataDxfId="58"/>
-    <tableColumn id="7" xr3:uid="{3B8303E5-7229-40E9-B595-7FD79C903530}" name="Remarks" dataDxfId="57"/>
+    <tableColumn id="1" xr3:uid="{205B1937-36C2-4A79-ADEE-67B939CC6350}" name="Dated" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{FC4A4194-EC0B-4123-AA2A-047F801393F9}" name="Opening Stock" dataDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{B9BA259A-905C-4F48-9EF9-1D3A771CDF0D}" name="Activated " dataDxfId="32"/>
+    <tableColumn id="4" xr3:uid="{6B90C7CC-E86F-4D69-8B7A-1A5106E7671C}" name="Order Received" dataDxfId="31"/>
+    <tableColumn id="5" xr3:uid="{52A7379A-F21F-428A-AC09-8DDD0314565C}" name="Closing Stock" dataDxfId="30"/>
+    <tableColumn id="6" xr3:uid="{2D5B9A13-3A69-4B89-9385-0118C6E503AA}" name="Order Shift" dataDxfId="29"/>
+    <tableColumn id="8" xr3:uid="{7A6C60CE-7C65-462E-936E-BEBFB199EEEA}" name="Tags Utilised" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{3B8303E5-7229-40E9-B595-7FD79C903530}" name="Remarks" dataDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F5BFC800-1EAF-4967-B61B-9184746587CB}" name="Table46" displayName="Table46" ref="K2:R18" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F5BFC800-1EAF-4967-B61B-9184746587CB}" name="Table46" displayName="Table46" ref="K2:R18" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
   <autoFilter ref="K2:R18" xr:uid="{F5BFC800-1EAF-4967-B61B-9184746587CB}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{EE8E16B4-53D2-438F-BDFF-22C4417244D7}" name="Dated" dataDxfId="54"/>
-    <tableColumn id="2" xr3:uid="{4ED05A2F-B065-41B5-B1FC-755636A3BA21}" name="Opening Stock" dataDxfId="53"/>
-    <tableColumn id="3" xr3:uid="{57285520-2C9E-4091-953B-03FBAFD5574E}" name="Activated " dataDxfId="52"/>
-    <tableColumn id="4" xr3:uid="{26808A5F-3F95-45FD-91EE-BFADD8DB9C6A}" name="Order Received" dataDxfId="51"/>
-    <tableColumn id="5" xr3:uid="{A95C8869-A6DD-4A00-8782-9276336A5840}" name="Closing Stock" dataDxfId="50"/>
-    <tableColumn id="6" xr3:uid="{F683981E-ECFB-47E9-88E2-60A6694123E4}" name="Order Shift" dataDxfId="49"/>
-    <tableColumn id="9" xr3:uid="{4862D1DC-BC5E-473F-B5F4-E4EDDBFBAEA8}" name="Tags Utilised" dataDxfId="48"/>
-    <tableColumn id="7" xr3:uid="{59E58FF5-FBE8-4EA3-8C27-FDBB5D8347D8}" name="Remarks" dataDxfId="47"/>
+    <tableColumn id="1" xr3:uid="{EE8E16B4-53D2-438F-BDFF-22C4417244D7}" name="Dated" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{4ED05A2F-B065-41B5-B1FC-755636A3BA21}" name="Opening Stock" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{57285520-2C9E-4091-953B-03FBAFD5574E}" name="Activated " dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{26808A5F-3F95-45FD-91EE-BFADD8DB9C6A}" name="Order Received" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{A95C8869-A6DD-4A00-8782-9276336A5840}" name="Closing Stock" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{F683981E-ECFB-47E9-88E2-60A6694123E4}" name="Order Shift" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{4862D1DC-BC5E-473F-B5F4-E4EDDBFBAEA8}" name="Tags Utilised" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{59E58FF5-FBE8-4EA3-8C27-FDBB5D8347D8}" name="Remarks" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{C16732A9-DC14-4F77-B928-B2EA21A17DE3}" name="Table467" displayName="Table467" ref="U2:AB18" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{C16732A9-DC14-4F77-B928-B2EA21A17DE3}" name="Table467" displayName="Table467" ref="U2:AB18" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
   <autoFilter ref="U2:AB18" xr:uid="{C16732A9-DC14-4F77-B928-B2EA21A17DE3}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{863EE3B3-D99D-40AA-9A97-8B87E908A619}" name="Dated" dataDxfId="44"/>
-    <tableColumn id="2" xr3:uid="{7EBF6231-0A46-4C5A-8F44-07F6E8D58BD8}" name="Opening Stock" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{7302BA2D-23E3-4355-A732-13358849E25E}" name="Activated " dataDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{C353FB1F-2706-4110-9F4C-867233885BE5}" name="Order Received" dataDxfId="41"/>
-    <tableColumn id="5" xr3:uid="{1C608AFD-D32B-49BA-B588-B75035E109DA}" name="Closing Stock" dataDxfId="40"/>
-    <tableColumn id="6" xr3:uid="{FF5D1709-231D-4967-81E2-C12033E82768}" name="Order Shift" dataDxfId="39"/>
-    <tableColumn id="9" xr3:uid="{ABB4B85D-962C-4A1F-8D08-7E53D211DBB3}" name="Tags Utilised" dataDxfId="38"/>
-    <tableColumn id="7" xr3:uid="{918E2430-DED3-4A6B-A818-8CD1C7AAFAEA}" name="Remarks" dataDxfId="37"/>
+    <tableColumn id="1" xr3:uid="{863EE3B3-D99D-40AA-9A97-8B87E908A619}" name="Dated" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{7EBF6231-0A46-4C5A-8F44-07F6E8D58BD8}" name="Opening Stock" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{7302BA2D-23E3-4355-A732-13358849E25E}" name="Activated " dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{C353FB1F-2706-4110-9F4C-867233885BE5}" name="Order Received" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{1C608AFD-D32B-49BA-B588-B75035E109DA}" name="Closing Stock" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{FF5D1709-231D-4967-81E2-C12033E82768}" name="Order Shift" dataDxfId="9"/>
+    <tableColumn id="9" xr3:uid="{ABB4B85D-962C-4A1F-8D08-7E53D211DBB3}" name="Tags Utilised" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{918E2430-DED3-4A6B-A818-8CD1C7AAFAEA}" name="Remarks" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1856,17 +1856,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -2593,7 +2593,7 @@
     </row>
     <row r="31" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" ref="A31:A36" si="3">ROW()-2</f>
         <v>29</v>
       </c>
       <c r="B31" s="4"/>
@@ -2617,7 +2617,7 @@
     </row>
     <row r="32" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="B32" s="4"/>
@@ -2641,7 +2641,7 @@
     </row>
     <row r="33" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="B33" s="4"/>
@@ -2663,7 +2663,7 @@
     </row>
     <row r="34" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="3"/>
         <v>32</v>
       </c>
       <c r="B34" s="4"/>
@@ -2677,7 +2677,7 @@
     </row>
     <row r="35" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="3"/>
         <v>33</v>
       </c>
       <c r="B35" s="4"/>
@@ -2691,7 +2691,7 @@
     </row>
     <row r="36" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="3"/>
         <v>34</v>
       </c>
       <c r="B36" s="4"/>
@@ -2753,16 +2753,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -4112,36 +4112,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="58.5" x14ac:dyDescent="0.7">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="K1" s="10" t="s">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="K1" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="11"/>
-      <c r="U1" s="10" t="s">
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="U1" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="V1" s="10"/>
-      <c r="W1" s="10"/>
-      <c r="X1" s="10"/>
-      <c r="Y1" s="10"/>
-      <c r="Z1" s="10"/>
-      <c r="AA1" s="10"/>
-      <c r="AB1" s="10"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="13"/>
+      <c r="AB1" s="13"/>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0B499AB-A421-4F13-98A0-D13B55AF76B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{756A6E29-10DF-4380-9B69-C986CEC9B15C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
     <sheet name="RC" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="201">
   <si>
     <t>S.No.</t>
   </si>
@@ -634,6 +634,12 @@
   </si>
   <si>
     <t>334701 - 334750</t>
+  </si>
+  <si>
+    <t>334601 - 334700</t>
+  </si>
+  <si>
+    <t>Fazil</t>
   </si>
 </sst>
 </file>
@@ -2669,11 +2675,21 @@
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
       <c r="D34" s="5"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="5"/>
-      <c r="I34" s="4"/>
+      <c r="E34" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="F34" s="4">
+        <v>100</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H34" s="5">
+        <v>46220</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="35" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
@@ -2720,8 +2736,8 @@
         <v>153</v>
       </c>
       <c r="F37" s="7">
-        <f>SUM(F3:F33)</f>
-        <v>3492</v>
+        <f>SUM(F3:F34)</f>
+        <v>3592</v>
       </c>
       <c r="G37" s="4"/>
       <c r="H37" s="5"/>

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{756A6E29-10DF-4380-9B69-C986CEC9B15C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2559B287-792F-4613-951A-F14256B9E6A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
     <sheet name="RC" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="202">
   <si>
     <t>S.No.</t>
   </si>
@@ -640,6 +640,9 @@
   </si>
   <si>
     <t>Fazil</t>
+  </si>
+  <si>
+    <t>returnd - 520-530</t>
   </si>
 </sst>
 </file>
@@ -3850,7 +3853,9 @@
       <c r="G42" s="5">
         <v>46205</v>
       </c>
-      <c r="H42" s="4"/>
+      <c r="H42" s="4" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="43" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="4">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2559B287-792F-4613-951A-F14256B9E6A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40AADF75-95B3-4CD4-8CC3-45B3F7F9A3B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="205">
   <si>
     <t>S.No.</t>
   </si>
@@ -643,6 +643,15 @@
   </si>
   <si>
     <t>returnd - 520-530</t>
+  </si>
+  <si>
+    <t>Order 8</t>
+  </si>
+  <si>
+    <t>608268-005-0204086</t>
+  </si>
+  <si>
+    <t>608268-005-0204285</t>
   </si>
 </sst>
 </file>
@@ -769,13 +778,13 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -901,6 +910,364 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1060,364 +1427,6 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1432,42 +1441,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I37" headerRowDxfId="66" dataDxfId="65">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I37" headerRowDxfId="56" dataDxfId="55">
   <autoFilter ref="A2:I37" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I37">
     <sortCondition ref="H2:H37"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="64" totalsRowDxfId="63">
+    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="54" totalsRowDxfId="53">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="62" totalsRowDxfId="61"/>
-    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="60" totalsRowDxfId="59"/>
-    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="58" totalsRowDxfId="57"/>
-    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="56" totalsRowDxfId="55"/>
-    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="54" totalsRowDxfId="53"/>
-    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="52" totalsRowDxfId="51"/>
-    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="50" totalsRowDxfId="49"/>
-    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="48" totalsRowDxfId="47"/>
+    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="52" totalsRowDxfId="51"/>
+    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="50" totalsRowDxfId="49"/>
+    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="48" totalsRowDxfId="47"/>
+    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="46" totalsRowDxfId="45"/>
+    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="44" totalsRowDxfId="43"/>
+    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="42" totalsRowDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="40" totalsRowDxfId="39"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="38" totalsRowDxfId="37"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H53" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H53" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65">
   <autoFilter ref="A2:H53" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="44">
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="64">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="42"/>
-    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="40"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="39"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="38"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="63"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="62"/>
+    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="61"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="60"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="59"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="58"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="57"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1865,17 +1874,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -2772,16 +2781,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -4037,12 +4046,24 @@
         <f t="shared" si="3"/>
         <v>48</v>
       </c>
-      <c r="B50" s="6"/>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="5"/>
+      <c r="B50" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="F50" s="4">
+        <v>200</v>
+      </c>
+      <c r="G50" s="5">
+        <v>46227</v>
+      </c>
       <c r="H50" s="4"/>
     </row>
     <row r="51" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -4083,8 +4104,8 @@
         <v>153</v>
       </c>
       <c r="F53" s="7">
-        <f>SUM(F3:F49)</f>
-        <v>2944</v>
+        <f>SUM(F3:F50)</f>
+        <v>3144</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40AADF75-95B3-4CD4-8CC3-45B3F7F9A3B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47724332-402A-491D-9E50-FE1ED2F8E223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47724332-402A-491D-9E50-FE1ED2F8E223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F728AF7-D50C-4E0F-AEF3-9410E1608207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
     <sheet name="RC" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="207">
   <si>
     <t>S.No.</t>
   </si>
@@ -652,6 +652,12 @@
   </si>
   <si>
     <t>608268-005-0204285</t>
+  </si>
+  <si>
+    <t>377501 - 38000</t>
+  </si>
+  <si>
+    <t>372751 - 373000</t>
   </si>
 </sst>
 </file>
@@ -2684,9 +2690,15 @@
         <f t="shared" si="3"/>
         <v>32</v>
       </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="5"/>
+      <c r="B34" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C34" s="4">
+        <v>500</v>
+      </c>
+      <c r="D34" s="5">
+        <v>46240</v>
+      </c>
       <c r="E34" s="4" t="s">
         <v>199</v>
       </c>
@@ -2708,9 +2720,15 @@
         <f t="shared" si="3"/>
         <v>33</v>
       </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="5"/>
+      <c r="B35" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C35" s="4">
+        <v>250</v>
+      </c>
+      <c r="D35" s="5">
+        <v>46240</v>
+      </c>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F728AF7-D50C-4E0F-AEF3-9410E1608207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC86344E-B82E-4B13-83D3-D66E81A95A9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="2" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
     <sheet name="RC" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="208">
   <si>
     <t>S.No.</t>
   </si>
@@ -658,6 +658,9 @@
   </si>
   <si>
     <t>372751 - 373000</t>
+  </si>
+  <si>
+    <t>377501  - 377750</t>
   </si>
 </sst>
 </file>
@@ -784,13 +787,13 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -916,6 +919,163 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1276,163 +1436,6 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1447,42 +1450,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I37" headerRowDxfId="56" dataDxfId="55">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I37" headerRowDxfId="66" dataDxfId="65">
   <autoFilter ref="A2:I37" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I37">
     <sortCondition ref="H2:H37"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="54" totalsRowDxfId="53">
+    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="64" totalsRowDxfId="63">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="52" totalsRowDxfId="51"/>
-    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="50" totalsRowDxfId="49"/>
-    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="48" totalsRowDxfId="47"/>
-    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="46" totalsRowDxfId="45"/>
-    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="44" totalsRowDxfId="43"/>
-    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="42" totalsRowDxfId="41"/>
-    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="40" totalsRowDxfId="39"/>
-    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="38" totalsRowDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="62" totalsRowDxfId="61"/>
+    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="60" totalsRowDxfId="59"/>
+    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="58" totalsRowDxfId="57"/>
+    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="56" totalsRowDxfId="55"/>
+    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="54" totalsRowDxfId="53"/>
+    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="52" totalsRowDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="50" totalsRowDxfId="49"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="48" totalsRowDxfId="47"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H53" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H53" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45">
   <autoFilter ref="A2:H53" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="64">
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="44">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="63"/>
-    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="62"/>
-    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="61"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="60"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="59"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="58"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="57"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="42"/>
+    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="39"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="37"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1880,17 +1883,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -2729,11 +2732,21 @@
       <c r="D35" s="5">
         <v>46240</v>
       </c>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="5"/>
-      <c r="I35" s="4"/>
+      <c r="E35" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="F35" s="4">
+        <v>250</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H35" s="5">
+        <v>46240</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="36" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
@@ -2766,8 +2779,8 @@
         <v>153</v>
       </c>
       <c r="F37" s="7">
-        <f>SUM(F3:F34)</f>
-        <v>3592</v>
+        <f>SUM(F3:F35)</f>
+        <v>3842</v>
       </c>
       <c r="G37" s="4"/>
       <c r="H37" s="5"/>
@@ -2799,16 +2812,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC86344E-B82E-4B13-83D3-D66E81A95A9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CE2A44B-C735-4A5F-90D6-F6ABE3C9445D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="2" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
     <sheet name="RC" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="211">
   <si>
     <t>S.No.</t>
   </si>
@@ -661,6 +661,15 @@
   </si>
   <si>
     <t>377501  - 377750</t>
+  </si>
+  <si>
+    <t>608268-005-0204286</t>
+  </si>
+  <si>
+    <t>608268-005-0204436</t>
+  </si>
+  <si>
+    <t>Anees</t>
   </si>
 </sst>
 </file>
@@ -787,6 +796,12 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -796,12 +811,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -820,99 +829,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1436,6 +1352,99 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1450,93 +1459,93 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I37" headerRowDxfId="66" dataDxfId="65">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I37" headerRowDxfId="36" dataDxfId="35">
   <autoFilter ref="A2:I37" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I37">
     <sortCondition ref="H2:H37"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="64" totalsRowDxfId="63">
+    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="34" totalsRowDxfId="33">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="62" totalsRowDxfId="61"/>
-    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="60" totalsRowDxfId="59"/>
-    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="58" totalsRowDxfId="57"/>
-    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="56" totalsRowDxfId="55"/>
-    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="54" totalsRowDxfId="53"/>
-    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="52" totalsRowDxfId="51"/>
-    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="50" totalsRowDxfId="49"/>
-    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="48" totalsRowDxfId="47"/>
+    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="32" totalsRowDxfId="31"/>
+    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="30" totalsRowDxfId="29"/>
+    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="28" totalsRowDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="26" totalsRowDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="24" totalsRowDxfId="23"/>
+    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="22" totalsRowDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="20" totalsRowDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="18" totalsRowDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H53" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H53" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
   <autoFilter ref="A2:H53" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="44">
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="14">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="42"/>
-    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="40"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="39"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="38"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6B19EA76-FE33-4EDA-96A5-FB5AB6842877}" name="Arena" displayName="Arena" ref="A2:H18" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6B19EA76-FE33-4EDA-96A5-FB5AB6842877}" name="Arena" displayName="Arena" ref="A2:H18" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65">
   <autoFilter ref="A2:H18" xr:uid="{6B19EA76-FE33-4EDA-96A5-FB5AB6842877}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{205B1937-36C2-4A79-ADEE-67B939CC6350}" name="Dated" dataDxfId="34"/>
-    <tableColumn id="2" xr3:uid="{FC4A4194-EC0B-4123-AA2A-047F801393F9}" name="Opening Stock" dataDxfId="33"/>
-    <tableColumn id="3" xr3:uid="{B9BA259A-905C-4F48-9EF9-1D3A771CDF0D}" name="Activated " dataDxfId="32"/>
-    <tableColumn id="4" xr3:uid="{6B90C7CC-E86F-4D69-8B7A-1A5106E7671C}" name="Order Received" dataDxfId="31"/>
-    <tableColumn id="5" xr3:uid="{52A7379A-F21F-428A-AC09-8DDD0314565C}" name="Closing Stock" dataDxfId="30"/>
-    <tableColumn id="6" xr3:uid="{2D5B9A13-3A69-4B89-9385-0118C6E503AA}" name="Order Shift" dataDxfId="29"/>
-    <tableColumn id="8" xr3:uid="{7A6C60CE-7C65-462E-936E-BEBFB199EEEA}" name="Tags Utilised" dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{3B8303E5-7229-40E9-B595-7FD79C903530}" name="Remarks" dataDxfId="27"/>
+    <tableColumn id="1" xr3:uid="{205B1937-36C2-4A79-ADEE-67B939CC6350}" name="Dated" dataDxfId="64"/>
+    <tableColumn id="2" xr3:uid="{FC4A4194-EC0B-4123-AA2A-047F801393F9}" name="Opening Stock" dataDxfId="63"/>
+    <tableColumn id="3" xr3:uid="{B9BA259A-905C-4F48-9EF9-1D3A771CDF0D}" name="Activated " dataDxfId="62"/>
+    <tableColumn id="4" xr3:uid="{6B90C7CC-E86F-4D69-8B7A-1A5106E7671C}" name="Order Received" dataDxfId="61"/>
+    <tableColumn id="5" xr3:uid="{52A7379A-F21F-428A-AC09-8DDD0314565C}" name="Closing Stock" dataDxfId="60"/>
+    <tableColumn id="6" xr3:uid="{2D5B9A13-3A69-4B89-9385-0118C6E503AA}" name="Order Shift" dataDxfId="59"/>
+    <tableColumn id="8" xr3:uid="{7A6C60CE-7C65-462E-936E-BEBFB199EEEA}" name="Tags Utilised" dataDxfId="58"/>
+    <tableColumn id="7" xr3:uid="{3B8303E5-7229-40E9-B595-7FD79C903530}" name="Remarks" dataDxfId="57"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F5BFC800-1EAF-4967-B61B-9184746587CB}" name="Table46" displayName="Table46" ref="K2:R18" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F5BFC800-1EAF-4967-B61B-9184746587CB}" name="Table46" displayName="Table46" ref="K2:R18" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
   <autoFilter ref="K2:R18" xr:uid="{F5BFC800-1EAF-4967-B61B-9184746587CB}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{EE8E16B4-53D2-438F-BDFF-22C4417244D7}" name="Dated" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{4ED05A2F-B065-41B5-B1FC-755636A3BA21}" name="Opening Stock" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{57285520-2C9E-4091-953B-03FBAFD5574E}" name="Activated " dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{26808A5F-3F95-45FD-91EE-BFADD8DB9C6A}" name="Order Received" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{A95C8869-A6DD-4A00-8782-9276336A5840}" name="Closing Stock" dataDxfId="20"/>
-    <tableColumn id="6" xr3:uid="{F683981E-ECFB-47E9-88E2-60A6694123E4}" name="Order Shift" dataDxfId="19"/>
-    <tableColumn id="9" xr3:uid="{4862D1DC-BC5E-473F-B5F4-E4EDDBFBAEA8}" name="Tags Utilised" dataDxfId="18"/>
-    <tableColumn id="7" xr3:uid="{59E58FF5-FBE8-4EA3-8C27-FDBB5D8347D8}" name="Remarks" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{EE8E16B4-53D2-438F-BDFF-22C4417244D7}" name="Dated" dataDxfId="54"/>
+    <tableColumn id="2" xr3:uid="{4ED05A2F-B065-41B5-B1FC-755636A3BA21}" name="Opening Stock" dataDxfId="53"/>
+    <tableColumn id="3" xr3:uid="{57285520-2C9E-4091-953B-03FBAFD5574E}" name="Activated " dataDxfId="52"/>
+    <tableColumn id="4" xr3:uid="{26808A5F-3F95-45FD-91EE-BFADD8DB9C6A}" name="Order Received" dataDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{A95C8869-A6DD-4A00-8782-9276336A5840}" name="Closing Stock" dataDxfId="50"/>
+    <tableColumn id="6" xr3:uid="{F683981E-ECFB-47E9-88E2-60A6694123E4}" name="Order Shift" dataDxfId="49"/>
+    <tableColumn id="9" xr3:uid="{4862D1DC-BC5E-473F-B5F4-E4EDDBFBAEA8}" name="Tags Utilised" dataDxfId="48"/>
+    <tableColumn id="7" xr3:uid="{59E58FF5-FBE8-4EA3-8C27-FDBB5D8347D8}" name="Remarks" dataDxfId="47"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{C16732A9-DC14-4F77-B928-B2EA21A17DE3}" name="Table467" displayName="Table467" ref="U2:AB18" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{C16732A9-DC14-4F77-B928-B2EA21A17DE3}" name="Table467" displayName="Table467" ref="U2:AB18" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45">
   <autoFilter ref="U2:AB18" xr:uid="{C16732A9-DC14-4F77-B928-B2EA21A17DE3}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{863EE3B3-D99D-40AA-9A97-8B87E908A619}" name="Dated" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{7EBF6231-0A46-4C5A-8F44-07F6E8D58BD8}" name="Opening Stock" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{7302BA2D-23E3-4355-A732-13358849E25E}" name="Activated " dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{C353FB1F-2706-4110-9F4C-867233885BE5}" name="Order Received" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{1C608AFD-D32B-49BA-B588-B75035E109DA}" name="Closing Stock" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{FF5D1709-231D-4967-81E2-C12033E82768}" name="Order Shift" dataDxfId="9"/>
-    <tableColumn id="9" xr3:uid="{ABB4B85D-962C-4A1F-8D08-7E53D211DBB3}" name="Tags Utilised" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{918E2430-DED3-4A6B-A818-8CD1C7AAFAEA}" name="Remarks" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{863EE3B3-D99D-40AA-9A97-8B87E908A619}" name="Dated" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{7EBF6231-0A46-4C5A-8F44-07F6E8D58BD8}" name="Opening Stock" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{7302BA2D-23E3-4355-A732-13358849E25E}" name="Activated " dataDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{C353FB1F-2706-4110-9F4C-867233885BE5}" name="Order Received" dataDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{1C608AFD-D32B-49BA-B588-B75035E109DA}" name="Closing Stock" dataDxfId="40"/>
+    <tableColumn id="6" xr3:uid="{FF5D1709-231D-4967-81E2-C12033E82768}" name="Order Shift" dataDxfId="39"/>
+    <tableColumn id="9" xr3:uid="{ABB4B85D-962C-4A1F-8D08-7E53D211DBB3}" name="Tags Utilised" dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{918E2430-DED3-4A6B-A818-8CD1C7AAFAEA}" name="Remarks" dataDxfId="37"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1883,17 +1892,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -2812,16 +2821,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -4102,13 +4111,27 @@
         <f t="shared" si="3"/>
         <v>49</v>
       </c>
-      <c r="B51" s="6"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="4"/>
+      <c r="B51" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F51" s="4">
+        <v>150</v>
+      </c>
+      <c r="G51" s="5">
+        <v>46253</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="52" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
@@ -4135,8 +4158,8 @@
         <v>153</v>
       </c>
       <c r="F53" s="7">
-        <f>SUM(F3:F50)</f>
-        <v>3144</v>
+        <f>SUM(F3:F51)</f>
+        <v>3294</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
@@ -4185,36 +4208,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="58.5" x14ac:dyDescent="0.7">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="K1" s="13" t="s">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="K1" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
-      <c r="U1" s="13" t="s">
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="U1" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="V1" s="13"/>
-      <c r="W1" s="13"/>
-      <c r="X1" s="13"/>
-      <c r="Y1" s="13"/>
-      <c r="Z1" s="13"/>
-      <c r="AA1" s="13"/>
-      <c r="AB1" s="13"/>
+      <c r="V1" s="10"/>
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="10"/>
+      <c r="Z1" s="10"/>
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="10"/>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CE2A44B-C735-4A5F-90D6-F6ABE3C9445D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A4C385-35BD-4A12-92AF-787ABFB08E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="214">
   <si>
     <t>S.No.</t>
   </si>
@@ -670,6 +670,15 @@
   </si>
   <si>
     <t>Anees</t>
+  </si>
+  <si>
+    <t>608268-005-0204535</t>
+  </si>
+  <si>
+    <t>608268-005-0204536</t>
+  </si>
+  <si>
+    <t>608268-005-0204585</t>
   </si>
 </sst>
 </file>
@@ -796,10 +805,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -808,7 +814,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -835,6 +844,457 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -994,457 +1454,6 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1459,93 +1468,93 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I37" headerRowDxfId="36" dataDxfId="35">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I37" headerRowDxfId="56" dataDxfId="55">
   <autoFilter ref="A2:I37" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I37">
     <sortCondition ref="H2:H37"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="34" totalsRowDxfId="33">
+    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="54" totalsRowDxfId="53">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="32" totalsRowDxfId="31"/>
-    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="30" totalsRowDxfId="29"/>
-    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="28" totalsRowDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="26" totalsRowDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="24" totalsRowDxfId="23"/>
-    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="22" totalsRowDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="20" totalsRowDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="18" totalsRowDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="52" totalsRowDxfId="51"/>
+    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="50" totalsRowDxfId="49"/>
+    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="48" totalsRowDxfId="47"/>
+    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="46" totalsRowDxfId="45"/>
+    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="44" totalsRowDxfId="43"/>
+    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="42" totalsRowDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="40" totalsRowDxfId="39"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="38" totalsRowDxfId="37"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H53" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="A2:H53" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H56" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65">
+  <autoFilter ref="A2:H56" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="14">
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="64">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="63"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="62"/>
+    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="61"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="60"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="59"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="58"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="57"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6B19EA76-FE33-4EDA-96A5-FB5AB6842877}" name="Arena" displayName="Arena" ref="A2:H18" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6B19EA76-FE33-4EDA-96A5-FB5AB6842877}" name="Arena" displayName="Arena" ref="A2:H18" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
   <autoFilter ref="A2:H18" xr:uid="{6B19EA76-FE33-4EDA-96A5-FB5AB6842877}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{205B1937-36C2-4A79-ADEE-67B939CC6350}" name="Dated" dataDxfId="64"/>
-    <tableColumn id="2" xr3:uid="{FC4A4194-EC0B-4123-AA2A-047F801393F9}" name="Opening Stock" dataDxfId="63"/>
-    <tableColumn id="3" xr3:uid="{B9BA259A-905C-4F48-9EF9-1D3A771CDF0D}" name="Activated " dataDxfId="62"/>
-    <tableColumn id="4" xr3:uid="{6B90C7CC-E86F-4D69-8B7A-1A5106E7671C}" name="Order Received" dataDxfId="61"/>
-    <tableColumn id="5" xr3:uid="{52A7379A-F21F-428A-AC09-8DDD0314565C}" name="Closing Stock" dataDxfId="60"/>
-    <tableColumn id="6" xr3:uid="{2D5B9A13-3A69-4B89-9385-0118C6E503AA}" name="Order Shift" dataDxfId="59"/>
-    <tableColumn id="8" xr3:uid="{7A6C60CE-7C65-462E-936E-BEBFB199EEEA}" name="Tags Utilised" dataDxfId="58"/>
-    <tableColumn id="7" xr3:uid="{3B8303E5-7229-40E9-B595-7FD79C903530}" name="Remarks" dataDxfId="57"/>
+    <tableColumn id="1" xr3:uid="{205B1937-36C2-4A79-ADEE-67B939CC6350}" name="Dated" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{FC4A4194-EC0B-4123-AA2A-047F801393F9}" name="Opening Stock" dataDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{B9BA259A-905C-4F48-9EF9-1D3A771CDF0D}" name="Activated " dataDxfId="32"/>
+    <tableColumn id="4" xr3:uid="{6B90C7CC-E86F-4D69-8B7A-1A5106E7671C}" name="Order Received" dataDxfId="31"/>
+    <tableColumn id="5" xr3:uid="{52A7379A-F21F-428A-AC09-8DDD0314565C}" name="Closing Stock" dataDxfId="30"/>
+    <tableColumn id="6" xr3:uid="{2D5B9A13-3A69-4B89-9385-0118C6E503AA}" name="Order Shift" dataDxfId="29"/>
+    <tableColumn id="8" xr3:uid="{7A6C60CE-7C65-462E-936E-BEBFB199EEEA}" name="Tags Utilised" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{3B8303E5-7229-40E9-B595-7FD79C903530}" name="Remarks" dataDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F5BFC800-1EAF-4967-B61B-9184746587CB}" name="Table46" displayName="Table46" ref="K2:R18" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F5BFC800-1EAF-4967-B61B-9184746587CB}" name="Table46" displayName="Table46" ref="K2:R18" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
   <autoFilter ref="K2:R18" xr:uid="{F5BFC800-1EAF-4967-B61B-9184746587CB}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{EE8E16B4-53D2-438F-BDFF-22C4417244D7}" name="Dated" dataDxfId="54"/>
-    <tableColumn id="2" xr3:uid="{4ED05A2F-B065-41B5-B1FC-755636A3BA21}" name="Opening Stock" dataDxfId="53"/>
-    <tableColumn id="3" xr3:uid="{57285520-2C9E-4091-953B-03FBAFD5574E}" name="Activated " dataDxfId="52"/>
-    <tableColumn id="4" xr3:uid="{26808A5F-3F95-45FD-91EE-BFADD8DB9C6A}" name="Order Received" dataDxfId="51"/>
-    <tableColumn id="5" xr3:uid="{A95C8869-A6DD-4A00-8782-9276336A5840}" name="Closing Stock" dataDxfId="50"/>
-    <tableColumn id="6" xr3:uid="{F683981E-ECFB-47E9-88E2-60A6694123E4}" name="Order Shift" dataDxfId="49"/>
-    <tableColumn id="9" xr3:uid="{4862D1DC-BC5E-473F-B5F4-E4EDDBFBAEA8}" name="Tags Utilised" dataDxfId="48"/>
-    <tableColumn id="7" xr3:uid="{59E58FF5-FBE8-4EA3-8C27-FDBB5D8347D8}" name="Remarks" dataDxfId="47"/>
+    <tableColumn id="1" xr3:uid="{EE8E16B4-53D2-438F-BDFF-22C4417244D7}" name="Dated" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{4ED05A2F-B065-41B5-B1FC-755636A3BA21}" name="Opening Stock" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{57285520-2C9E-4091-953B-03FBAFD5574E}" name="Activated " dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{26808A5F-3F95-45FD-91EE-BFADD8DB9C6A}" name="Order Received" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{A95C8869-A6DD-4A00-8782-9276336A5840}" name="Closing Stock" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{F683981E-ECFB-47E9-88E2-60A6694123E4}" name="Order Shift" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{4862D1DC-BC5E-473F-B5F4-E4EDDBFBAEA8}" name="Tags Utilised" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{59E58FF5-FBE8-4EA3-8C27-FDBB5D8347D8}" name="Remarks" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{C16732A9-DC14-4F77-B928-B2EA21A17DE3}" name="Table467" displayName="Table467" ref="U2:AB18" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{C16732A9-DC14-4F77-B928-B2EA21A17DE3}" name="Table467" displayName="Table467" ref="U2:AB18" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
   <autoFilter ref="U2:AB18" xr:uid="{C16732A9-DC14-4F77-B928-B2EA21A17DE3}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{863EE3B3-D99D-40AA-9A97-8B87E908A619}" name="Dated" dataDxfId="44"/>
-    <tableColumn id="2" xr3:uid="{7EBF6231-0A46-4C5A-8F44-07F6E8D58BD8}" name="Opening Stock" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{7302BA2D-23E3-4355-A732-13358849E25E}" name="Activated " dataDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{C353FB1F-2706-4110-9F4C-867233885BE5}" name="Order Received" dataDxfId="41"/>
-    <tableColumn id="5" xr3:uid="{1C608AFD-D32B-49BA-B588-B75035E109DA}" name="Closing Stock" dataDxfId="40"/>
-    <tableColumn id="6" xr3:uid="{FF5D1709-231D-4967-81E2-C12033E82768}" name="Order Shift" dataDxfId="39"/>
-    <tableColumn id="9" xr3:uid="{ABB4B85D-962C-4A1F-8D08-7E53D211DBB3}" name="Tags Utilised" dataDxfId="38"/>
-    <tableColumn id="7" xr3:uid="{918E2430-DED3-4A6B-A818-8CD1C7AAFAEA}" name="Remarks" dataDxfId="37"/>
+    <tableColumn id="1" xr3:uid="{863EE3B3-D99D-40AA-9A97-8B87E908A619}" name="Dated" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{7EBF6231-0A46-4C5A-8F44-07F6E8D58BD8}" name="Opening Stock" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{7302BA2D-23E3-4355-A732-13358849E25E}" name="Activated " dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{C353FB1F-2706-4110-9F4C-867233885BE5}" name="Order Received" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{1C608AFD-D32B-49BA-B588-B75035E109DA}" name="Closing Stock" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{FF5D1709-231D-4967-81E2-C12033E82768}" name="Order Shift" dataDxfId="9"/>
+    <tableColumn id="9" xr3:uid="{ABB4B85D-962C-4A1F-8D08-7E53D211DBB3}" name="Tags Utilised" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{918E2430-DED3-4A6B-A818-8CD1C7AAFAEA}" name="Remarks" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1892,17 +1901,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -2810,7 +2819,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56B532C1-7F8B-4592-901A-51A1E632DC96}">
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr defaultColWidth="37.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2821,16 +2830,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -3361,7 +3370,7 @@
     </row>
     <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
-        <f t="shared" ref="A22:A53" si="1">ROW()-2</f>
+        <f t="shared" ref="A22:A56" si="1">ROW()-2</f>
         <v>20</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -4138,34 +4147,99 @@
         <f t="shared" si="3"/>
         <v>50</v>
       </c>
-      <c r="B52" s="6"/>
-      <c r="C52" s="6"/>
-      <c r="D52" s="6"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="5"/>
+      <c r="B52" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F52" s="4">
+        <v>100</v>
+      </c>
+      <c r="G52" s="5">
+        <v>46262</v>
+      </c>
       <c r="H52" s="4"/>
     </row>
     <row r="53" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
+        <f>ROW()-2</f>
+        <v>51</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="F53" s="4">
+        <v>50</v>
+      </c>
+      <c r="G53" s="5">
+        <v>46262</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A54" s="4">
+        <f>ROW()-2</f>
+        <v>52</v>
+      </c>
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="4"/>
+    </row>
+    <row r="55" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A55" s="4">
+        <f>ROW()-2</f>
+        <v>53</v>
+      </c>
+      <c r="B55" s="6"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="4"/>
+    </row>
+    <row r="56" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A56" s="4">
         <f t="shared" si="1"/>
-        <v>51</v>
-      </c>
-      <c r="B53" s="6"/>
-      <c r="C53" s="6"/>
-      <c r="D53" s="6"/>
-      <c r="E53" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B56" s="6"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="6"/>
+      <c r="E56" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="F53" s="7">
-        <f>SUM(F3:F51)</f>
-        <v>3294</v>
-      </c>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C54" s="8"/>
+      <c r="F56" s="7">
+        <f>SUM(F3:F53)</f>
+        <v>3444</v>
+      </c>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C57" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4208,36 +4282,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="58.5" x14ac:dyDescent="0.7">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="K1" s="10" t="s">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="K1" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="11"/>
-      <c r="U1" s="10" t="s">
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="U1" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="V1" s="10"/>
-      <c r="W1" s="10"/>
-      <c r="X1" s="10"/>
-      <c r="Y1" s="10"/>
-      <c r="Z1" s="10"/>
-      <c r="AA1" s="10"/>
-      <c r="AB1" s="10"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="13"/>
+      <c r="AB1" s="13"/>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A4C385-35BD-4A12-92AF-787ABFB08E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEFA6E76-6C03-4F61-82BC-0778FE1EA27C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="215">
   <si>
     <t>S.No.</t>
   </si>
@@ -679,6 +679,9 @@
   </si>
   <si>
     <t>608268-005-0204585</t>
+  </si>
+  <si>
+    <t>372901 - 3723000</t>
   </si>
 </sst>
 </file>
@@ -2774,11 +2777,21 @@
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
       <c r="D36" s="5"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="4"/>
+      <c r="E36" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="F36" s="4">
+        <v>100</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H36" s="5">
+        <v>46263</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="37" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
@@ -2797,8 +2810,8 @@
         <v>153</v>
       </c>
       <c r="F37" s="7">
-        <f>SUM(F3:F35)</f>
-        <v>3842</v>
+        <f>SUM(F3:F36)</f>
+        <v>3942</v>
       </c>
       <c r="G37" s="4"/>
       <c r="H37" s="5"/>
@@ -4191,7 +4204,7 @@
         <v>46262</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEFA6E76-6C03-4F61-82BC-0778FE1EA27C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C68D55E-2450-4962-A578-1B3977ABD031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="216">
   <si>
     <t>S.No.</t>
   </si>
@@ -682,6 +682,9 @@
   </si>
   <si>
     <t>372901 - 3723000</t>
+  </si>
+  <si>
+    <t>608268-005-0204516</t>
   </si>
 </sst>
 </file>
@@ -4212,12 +4215,24 @@
         <f>ROW()-2</f>
         <v>52</v>
       </c>
-      <c r="B54" s="6"/>
-      <c r="C54" s="6"/>
-      <c r="D54" s="6"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="5"/>
+      <c r="B54" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="F54" s="4">
+        <v>20</v>
+      </c>
+      <c r="G54" s="5">
+        <v>46267</v>
+      </c>
       <c r="H54" s="4"/>
     </row>
     <row r="55" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -4245,8 +4260,8 @@
         <v>153</v>
       </c>
       <c r="F56" s="7">
-        <f>SUM(F3:F53)</f>
-        <v>3444</v>
+        <f>SUM(F3:F54)</f>
+        <v>3464</v>
       </c>
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
